--- a/teeccino-retail-price-list-new-prices.xlsx
+++ b/teeccino-retail-price-list-new-prices.xlsx
@@ -559,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A8:F135"/>
+  <dimension ref="A8:F116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.4" customWidth="1" min="1" max="1"/>
@@ -626,17 +626,17 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>80040</t>
+          <t>80030</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>795239800407</t>
+          <t>795239800308</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Blood Orange - Herbal Coffee (APG)</t>
+          <t>Almond Amaretto - Herbal Coffee</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -645,26 +645,26 @@
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>16.99</v>
+        <v>17.99</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>18.49</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>82050</t>
+          <t>82070</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>795239820504</t>
+          <t>795239820702</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gingerbread Chicory - Herbal Coffee</t>
+          <t>Candy Cane Chicory - Herbal Coffee</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -673,26 +673,26 @@
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>16.99</v>
+        <v>17.99</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>18.49</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>82060</t>
+          <t>80020</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>795239820603</t>
+          <t>795239800209</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Maple Pecan - Herbal Coffee</t>
+          <t>Chocolate Mint - Herbal Coffee</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -701,26 +701,26 @@
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>16.99</v>
+        <v>17.99</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>18.49</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>82130</t>
+          <t>82120</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>795239821303</t>
+          <t>795239821204</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mexican Chocolate Chicory - Herbal Coffee</t>
+          <t>Chocolate Raspberry - Herbal Coffee</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -729,26 +729,26 @@
         </is>
       </c>
       <c r="E14" s="6" t="n">
-        <v>16.99</v>
+        <v>17.99</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>18.49</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>82010</t>
+          <t>80050</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>795239820108</t>
+          <t>795239800506</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pumpkin Spice - Herbal Coffee</t>
+          <t>English Toffee - Herbal Coffee</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -757,26 +757,26 @@
         </is>
       </c>
       <c r="E15" s="6" t="n">
-        <v>16.99</v>
+        <v>17.99</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>18.49</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>80089</t>
+          <t>80110</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>795239800896</t>
+          <t>795239801107</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Raspberry Mocha - Herbal Coffee</t>
+          <t>French Roast - Herbal Coffee</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -785,26 +785,26 @@
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>16.99</v>
+        <v>17.99</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>18.99</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>82040</t>
+          <t>80060</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>795239820405</t>
+          <t>795239800605</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Snickerdoodle Chicory - Herbal Coffee</t>
+          <t>Hazelnut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -813,26 +813,26 @@
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>16.99</v>
+        <v>17.99</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>18.49</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>80030</t>
+          <t>82080</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>795239800308</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Almond Amaretto - Herbal Coffee</t>
+          <t>Irish Cream - Herbal Coffee</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -850,17 +850,17 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>82070</t>
+          <t>80070</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>795239820702</t>
+          <t>795239800704</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Candy Cane Chicory - Herbal Coffee</t>
+          <t>Java - Herbal Coffee</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -878,17 +878,17 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>80020</t>
+          <t>80130</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>795239800209</t>
+          <t>795239801305</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chocolate Mint - Herbal Coffee</t>
+          <t>Maca Chocolate - Herbal Coffee</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -906,17 +906,17 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>82120</t>
+          <t>80080</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>795239821204</t>
+          <t>795239800803</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chocolate Raspberry - Herbal Coffee</t>
+          <t>Mocha - Herbal Coffee</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -934,17 +934,17 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>80050</t>
+          <t>80010</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>795239800506</t>
+          <t>795239800100</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>English Toffee - Herbal Coffee</t>
+          <t>Vanilla Nut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -959,228 +959,204 @@
         <v>19.49</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>80110</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>795239801107</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>French Roast - Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>11oz bag</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>19.49</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>80060</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>795239800605</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Hazelnut - Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>11oz bag</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>19.49</v>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Item #</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>UPC:</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>10oz All-purpose Grind:</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Packaging Size:</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Unit Price:</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>MSRP:</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>82080</t>
+          <t>85020</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>795239850204</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irish Cream - Herbal Coffee</t>
+          <t>Chaga Ashwagandha Butterscotch Cream - Herbal Coffee</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>11oz bag</t>
+          <t>10oz bag</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>17.99</v>
+        <v>19.99</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>19.49</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>80070</t>
+          <t>83220</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>795239800704</t>
+          <t>795239832200</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Java - Herbal Coffee</t>
+          <t>Dandelion Caramel Nut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>11oz bag</t>
+          <t>10oz bag</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>17.99</v>
+        <v>19.99</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>19.49</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>80130</t>
+          <t>85030</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>795239801305</t>
+          <t>795239850303</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Maca Chocolate - Herbal Coffee</t>
+          <t>Lion's Mane Rhodiola Rose Mushroom - Herbal Coffee</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>11oz bag</t>
+          <t>10oz bag</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>17.99</v>
+        <v>19.99</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>19.49</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>80080</t>
+          <t>85050</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>795239800803</t>
+          <t>795239850501</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mocha - Herbal Coffee</t>
+          <t>Turkey Tail Astragalus Toasted Maple - Herbal Coffee</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>11oz bag</t>
+          <t>10oz bag</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>17.99</v>
+        <v>19.99</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>19.49</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>80010</t>
+          <t>85070</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>795239800100</t>
+          <t>795239850709</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Vanilla Nut - Herbal Coffee</t>
+          <t>Adapt &amp; Protect - Herbal Coffee</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>11oz bag</t>
+          <t>10oz bag</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>17.99</v>
+        <v>21.99</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>19.49</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>82110</t>
+          <t>86010</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>795239821105</t>
+          <t>795239860104</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>French Vanilla - Herbal Coffee</t>
+          <t>Dark Chocolate - Herbal Coffee</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>11oz bag</t>
+          <t>10oz bag</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>18.49</v>
+        <v>21.99</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>20.49</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1196,7 +1172,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>10oz All-purpose Grind:</t>
+          <t>500g All-purpose Grind:</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -1218,632 +1194,632 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>83370</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>795239833702</t>
+          <t>795239801169</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Blueberry Vanilla - Herbal Coffee</t>
+          <t>French Roast - Herbal Coffee</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>10oz bag</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>18.99</v>
+        <v>27.99</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>20.99</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>83340</t>
+          <t>80066</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>795239833405</t>
+          <t>795239800667</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dandelion Coconut - Herbal Coffee</t>
+          <t>Hazelnut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>10oz bag</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>18.99</v>
+        <v>27.99</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>20.99</v>
+        <v>30.49</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>83110</t>
+          <t>80086</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>795239831104</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dandelion Dark Roast - Herbal Coffee</t>
+          <t>Mocha - Herbal Coffee</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>10oz bag</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>18.99</v>
+        <v>27.99</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>20.99</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>83080</t>
+          <t>80016</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>795239830800</t>
+          <t>795239800162</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dandelion Mocha - Herbal Coffee</t>
+          <t>Vanilla Nut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>10oz bag</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>18.99</v>
+        <v>27.99</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>20.99</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>83310</t>
+          <t>83226</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>795239833108</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dandelion Mocha Mint - Herbal Coffee</t>
+          <t>Dandelion Caramel Nut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>10oz bag</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>18.99</v>
+        <v>34.99</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>20.99</v>
+        <v>38.49</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>83116</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>795239833207</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dandelion Red Chai - Herbal Coffee</t>
+          <t>Dandelion Dark Roast - Herbal Coffee</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>10oz bag</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>18.99</v>
+        <v>34.99</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>20.99</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>83330</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>795239833306</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Dandelion Turmeric - Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>10oz bag</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="n">
-        <v>18.99</v>
-      </c>
-      <c r="F39" s="6" t="n">
-        <v>20.99</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>83010</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>795239830107</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Dandelion Vanilla Nut - Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>10oz bag</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="n">
-        <v>18.99</v>
-      </c>
-      <c r="F40" s="6" t="n">
-        <v>20.99</v>
+        <v>38.49</v>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Item #</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>UPC:</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>5lb Bulk Bags:</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Packaging Size:</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Unit Price:</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>MSRP:</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>83360</t>
+          <t>60030</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>795239833603</t>
+          <t>795239600304</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Holiday Eggnog - Herbal Coffee</t>
+          <t>Almond Amaretto - Herbal Coffee</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>10oz bag</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>18.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>20.99</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>85010</t>
+          <t>62070</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>795239850105</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Reishi Eleuthero French Roast Mushroom - Herbal Coffee</t>
+          <t>Candy Cane Chicory - Herbal Coffee</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>10oz bag</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>18.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>20.99</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>85060</t>
+          <t>60020</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>795239850600</t>
+          <t>795239600205</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tremella Tulsi Cardamom Mushroom - Herbal Coffee</t>
+          <t>Chocolate Mint - Herbal Coffee</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>10oz bag</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>18.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>20.99</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>85020</t>
+          <t>62120</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>795239850204</t>
+          <t>795239621200</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chaga Ashwagandha Butterscotch Cream - Herbal Coffee</t>
+          <t>Chocolate Raspberry Chicory - Herbal Coffee</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>10oz bag</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E44" s="6" t="n">
-        <v>19.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>21.99</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>83220</t>
+          <t>60110</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>795239832200</t>
+          <t>795239601103</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dandelion Caramel Nut - Herbal Coffee</t>
+          <t>French Roast - Herbal Coffee</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>10oz bag</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>19.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>21.99</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>85030</t>
+          <t>62050</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>795239850303</t>
+          <t>795239620500</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lion's Mane Rhodiola Rose Mushroom - Herbal Coffee</t>
+          <t>Gingerbread Chicory - Herbal Coffee</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>10oz bag</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
-        <v>19.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>21.99</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>85050</t>
+          <t>60060</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>795239850501</t>
+          <t>795239600601</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey Tail Astragalus Toasted Maple - Herbal Coffee</t>
+          <t>Hazelnut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>10oz bag</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
-        <v>19.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>21.99</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>85070</t>
+          <t>60070</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>795239850709</t>
+          <t>795239600700</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Adapt &amp; Protect - Herbal Coffee</t>
+          <t>Java - Herbal Coffee</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>10oz bag</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
-        <v>21.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>23.99</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>86010</t>
+          <t>60130</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>795239860104</t>
+          <t>795239601301</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dark Chocolate - Herbal Coffee</t>
+          <t>Maca Chocolate - Herbal Coffee</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>10oz bag</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>21.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>Item #</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>UPC:</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>500g All-purpose Grind:</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>Packaging Size:</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>Unit Price:</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>MSRP:</t>
-        </is>
+        <v>98.98999999999999</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>62060</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>795239620609</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Maple Pecan - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>5lb bag</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>89.98999999999999</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>98.98999999999999</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>60080</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>795239600809</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Mocha - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>5lb bag</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>89.98999999999999</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>80116</t>
+          <t>62010</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>795239801169</t>
+          <t>795239620104</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>French Roast - Herbal Coffee</t>
+          <t>Pumpkin Spice - Herbal Coffee</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>27.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>30.99</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>80066</t>
+          <t>62040</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>795239800667</t>
+          <t>795239620401</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hazelnut - Herbal Coffee</t>
+          <t>Snickerdoodle Chicory - Herbal Coffee</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>27.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>30.49</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>80086</t>
+          <t>60010</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>795239600106</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Mocha - Herbal Coffee</t>
+          <t>Vanilla Nut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E54" s="6" t="n">
-        <v>27.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>30.99</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>80016</t>
+          <t>65020</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>795239800162</t>
+          <t>795239650200</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Vanilla Nut - Herbal Coffee</t>
+          <t>Chaga Ashwagandha Butterscotch Cream - Herbal Coffee</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>27.99</v>
+        <v>114.99</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>30.99</v>
+        <v>126.49</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>83226</t>
+          <t>63220</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>795239632206</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1853,90 +1829,114 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E56" s="6" t="n">
-        <v>34.99</v>
+        <v>114.99</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>38.49</v>
+        <v>126.49</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>83116</t>
+          <t>63340</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>795239633401</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>Dandelion Coconut - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>5lb bag</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>114.99</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>126.49</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>63110</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>795239631100</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
           <t>Dandelion Dark Roast - Herbal Coffee</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>500g</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="n">
-        <v>34.99</v>
-      </c>
-      <c r="F57" s="6" t="n">
-        <v>38.49</v>
-      </c>
-    </row>
-    <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>Item #</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>UPC:</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>5lb Bulk Bags:</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>Packaging Size:</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>Unit Price:</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>MSRP:</t>
-        </is>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>5lb bag</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>114.99</v>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>126.49</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>63080</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>795239630806</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Dandelion Mocha - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>5lb bag</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>114.99</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>126.49</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>60030</t>
+          <t>63310</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>795239600304</t>
+          <t>795239633104</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Almond Amaretto - Herbal Coffee</t>
+          <t>Dandelion Mocha Mint - Herbal Coffee</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -1945,26 +1945,26 @@
         </is>
       </c>
       <c r="E60" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>114.99</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>126.49</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>62070</t>
+          <t>63010</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>795239630103</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Candy Cane Chicory - Herbal Coffee</t>
+          <t>Dandelion Vanilla Nut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -1973,26 +1973,26 @@
         </is>
       </c>
       <c r="E61" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>114.99</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>126.49</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>60020</t>
+          <t>65010</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>795239600205</t>
+          <t>795239650101</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chocolate Mint - Herbal Coffee</t>
+          <t>Reishi Eleuthero French Roast Mushroom - Herbal Coffee</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -2001,26 +2001,26 @@
         </is>
       </c>
       <c r="E62" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>114.99</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>126.49</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>62120</t>
+          <t>65050</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>795239621200</t>
+          <t>795239650507</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chocolate Raspberry Chicory - Herbal Coffee</t>
+          <t>Turkey Tail Astragalus Toasted Maple - Herbal Coffee</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -2029,26 +2029,26 @@
         </is>
       </c>
       <c r="E63" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>114.99</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>126.49</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>60110</t>
+          <t>66010</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>795239601103</t>
+          <t>795239660100</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>French Roast - Herbal Coffee</t>
+          <t>Dark Chocolate - Herbal Coffee</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -2057,590 +2057,590 @@
         </is>
       </c>
       <c r="E64" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>139.99</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>98.98999999999999</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>62050</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>795239620500</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Gingerbread Chicory - Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>5lb bag</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="n">
-        <v>89.98999999999999</v>
-      </c>
-      <c r="F65" s="6" t="n">
-        <v>98.98999999999999</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>60060</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>795239600601</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Hazelnut - Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>5lb bag</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="n">
-        <v>89.98999999999999</v>
-      </c>
-      <c r="F66" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>153.99</v>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Item #</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>UPC:</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Trial Size Packets:</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Packaging Size:</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Unit Price:</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>MSRP:</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>60070</t>
+          <t>52030</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>795239600700</t>
+          <t>795239520305</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Java - Herbal Coffee</t>
+          <t>Southern Pecan - Herbal Coffee</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E67" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>1.43</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>60130</t>
+          <t>50030</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>795239601301</t>
+          <t>795239500307</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Maca Chocolate - Herbal Coffee</t>
+          <t>Almond Amaretto - Herbal Coffee</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E68" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>62060</t>
+          <t>50020</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>795239620609</t>
+          <t>795239500208</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Maple Pecan - Herbal Coffee</t>
+          <t>Chocolate Mint - Herbal Coffee</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E69" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>60080</t>
+          <t>50110</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>795239600809</t>
+          <t>795239501106</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Mocha - Herbal Coffee</t>
+          <t>French Roast - Herbal Coffee</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E70" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>62010</t>
+          <t>52050</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>795239620104</t>
+          <t>795239520503</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pumpkin Spice - Herbal Coffee</t>
+          <t>Gingerbread Chicory - Herbal Coffee</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E71" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>62040</t>
+          <t>50060</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>795239620401</t>
+          <t>795239500604</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Snickerdoodle Chicory - Herbal Coffee</t>
+          <t>Hazelnut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E72" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>60010</t>
+          <t>50070</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>795239600106</t>
+          <t>795239500703</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Vanilla Nut - Herbal Coffee</t>
+          <t>Java - Herbal Coffee</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E73" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>65020</t>
+          <t>50130</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>795239650200</t>
+          <t>795239501304</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chaga Ashwagandha Butterscotch Cream - Herbal Coffee</t>
+          <t>Maca Chocolate - Herbal Coffee</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E74" s="6" t="n">
-        <v>114.99</v>
+        <v>3.5</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>126.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>63220</t>
+          <t>52060</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>795239632206</t>
+          <t>795239520602</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dandelion Caramel Nut - Herbal Coffee</t>
+          <t>Maple Pecan - Herbal Coffee</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E75" s="6" t="n">
-        <v>114.99</v>
+        <v>3.5</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>126.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>63340</t>
+          <t>50080</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>795239633401</t>
+          <t>795239500802</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dandelion Coconut - Herbal Coffee</t>
+          <t>Mocha - Herbal Coffee</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E76" s="6" t="n">
-        <v>114.99</v>
+        <v>3.5</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>126.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>63110</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>795239631100</t>
+          <t>795239520107</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dandelion Dark Roast - Herbal Coffee</t>
+          <t>Pumpkin Spice - Herbal Coffee</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E77" s="6" t="n">
-        <v>114.99</v>
+        <v>3.5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>126.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>63080</t>
+          <t>52040</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>795239630806</t>
+          <t>795239520404</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dandelion Mocha - Herbal Coffee</t>
+          <t>Snickerdoodle Chicory - Herbal Coffee</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E78" s="6" t="n">
-        <v>114.99</v>
+        <v>3.5</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>126.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>63310</t>
+          <t>50010</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>795239633104</t>
+          <t>795239500109</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dandelion Mocha Mint - Herbal Coffee</t>
+          <t>Vanilla Nut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E79" s="6" t="n">
-        <v>114.99</v>
+        <v>3.5</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>126.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>63010</t>
+          <t>53220</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>795239630103</t>
+          <t>795239532209</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dandelion Vanilla Nut - Herbal Coffee</t>
+          <t>Dandelion Caramel Nut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E80" s="6" t="n">
-        <v>114.99</v>
+        <v>3.99</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>126.49</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>65010</t>
+          <t>53340</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>795239650101</t>
+          <t>795239533404</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Reishi Eleuthero French Roast Mushroom - Herbal Coffee</t>
+          <t>Dandelion Coconut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E81" s="6" t="n">
-        <v>114.99</v>
+        <v>3.99</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>126.49</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>65050</t>
+          <t>53110</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>795239650507</t>
+          <t>795239531103</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Turkey Tail Astragalus Toasted Maple - Herbal Coffee</t>
+          <t>Dandelion Dark Roast - Herbal Coffee</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E82" s="6" t="n">
-        <v>114.99</v>
+        <v>3.99</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>126.49</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>66010</t>
+          <t>53080</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>795239660100</t>
+          <t>795239530809</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dark Chocolate - Herbal Coffee</t>
+          <t>Dandelion Mocha - Herbal Coffee</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E83" s="6" t="n">
-        <v>139.99</v>
+        <v>3.99</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>153.99</v>
-      </c>
-    </row>
-    <row r="85" ht="22" customHeight="1">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>Item #</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>UPC:</t>
-        </is>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>Trial Size Packets:</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>Packaging Size:</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>Unit Price:</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t>MSRP:</t>
-        </is>
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>53310</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>795239533107</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Dandelion Mocha Mint - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>1.05oz packet</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="F84" s="6" t="n">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>53010</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>795239530106</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Dandelion Vanilla Nut - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>1.05oz packet</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="F85" s="6" t="n">
+        <v>4.49</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>52030</t>
+          <t>53360</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>795239520305</t>
+          <t>795239533503</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Southern Pecan - Herbal Coffee</t>
+          <t>Holiday Eggnog - Herbal Coffee</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -2649,26 +2649,26 @@
         </is>
       </c>
       <c r="E86" s="6" t="n">
-        <v>1.43</v>
+        <v>3.99</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>1.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>50030</t>
+          <t>55020</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>795239500307</t>
+          <t>795239550203</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Almond Amaretto - Herbal Coffee</t>
+          <t>Chaga Ashwagandha Butterscotch Cream - Herbal Coffee</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -2677,26 +2677,26 @@
         </is>
       </c>
       <c r="E87" s="6" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>3.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>50020</t>
+          <t>56010</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>795239500208</t>
+          <t>795239560103</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chocolate Mint - Herbal Coffee</t>
+          <t>Dark Chocolate - Herbal Coffee</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -2705,26 +2705,26 @@
         </is>
       </c>
       <c r="E88" s="6" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>3.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>50110</t>
+          <t>55030</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>795239501106</t>
+          <t>795239550302</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>French Roast - Herbal Coffee</t>
+          <t>Lion's Mane Rhodiola Rose Mushroom - Herbal Coffee</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -2733,26 +2733,26 @@
         </is>
       </c>
       <c r="E89" s="6" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>3.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>52050</t>
+          <t>55010</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>795239520503</t>
+          <t>795239550104</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Gingerbread Chicory - Herbal Coffee</t>
+          <t>Reishi Eleuthero French Roast Mushroom - Herbal Coffee</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -2761,26 +2761,26 @@
         </is>
       </c>
       <c r="E90" s="6" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>3.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>50060</t>
+          <t>55050</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>795239500604</t>
+          <t>795239550500</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hazelnut - Herbal Coffee</t>
+          <t>Turkey Tail Astragalus Toasted Maple - Herbal Coffee</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -2789,1023 +2789,491 @@
         </is>
       </c>
       <c r="E91" s="6" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>50070</t>
-        </is>
-      </c>
-      <c r="B92" s="5" t="inlineStr">
-        <is>
-          <t>795239500703</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Java - Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
-        <is>
-          <t>1.05oz packet</t>
-        </is>
-      </c>
-      <c r="E92" s="6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F92" s="6" t="n">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>50130</t>
-        </is>
-      </c>
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t>795239501304</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Maca Chocolate - Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
-        <is>
-          <t>1.05oz packet</t>
-        </is>
-      </c>
-      <c r="E93" s="6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F93" s="6" t="n">
-        <v>3.99</v>
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>Item #</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>UPC:</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>Instant Herbal Coffee:</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>Packaging Size:</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>Unit Price:</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>MSRP:</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>52060</t>
+          <t>30008</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>795239520602</t>
+          <t>795239300082</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Maple Pecan - Herbal Coffee</t>
+          <t>French Roast - Instant Herbal Coffee</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>3.53oz bag</t>
         </is>
       </c>
       <c r="E94" s="6" t="n">
-        <v>3.5</v>
+        <v>16.99</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>3.99</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>50080</t>
+          <t>30010</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>795239500802</t>
+          <t>795239300105</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Mocha - Herbal Coffee</t>
+          <t>Hazelnut - Instant Herbal Coffee</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>3.53oz bag</t>
         </is>
       </c>
       <c r="E95" s="6" t="n">
-        <v>3.5</v>
+        <v>16.99</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>3.99</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>52010</t>
+          <t>30011</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>795239520107</t>
+          <t>795239300112</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Pumpkin Spice - Herbal Coffee</t>
+          <t>Mocha - Instant Herbal Coffee</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>3.53oz bag</t>
         </is>
       </c>
       <c r="E96" s="6" t="n">
-        <v>3.5</v>
+        <v>16.99</v>
       </c>
       <c r="F96" s="6" t="n">
-        <v>3.99</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>52040</t>
+          <t>30009</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>795239520404</t>
+          <t>795239300099</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Snickerdoodle Chicory - Herbal Coffee</t>
+          <t>Vanilla Nut - Instant Herbal Coffee</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>3.53oz bag</t>
         </is>
       </c>
       <c r="E97" s="6" t="n">
-        <v>3.5</v>
+        <v>16.99</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>3.99</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>50010</t>
+          <t>30007</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>795239500109</t>
+          <t>795239300075</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Vanilla Nut - Herbal Coffee</t>
+          <t>Adapt &amp; Protect - Instant Herbal Coffee</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>3.95oz bag</t>
         </is>
       </c>
       <c r="E98" s="6" t="n">
-        <v>3.5</v>
+        <v>22.99</v>
       </c>
       <c r="F98" s="6" t="n">
-        <v>3.99</v>
+        <v>25.49</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>53220</t>
+          <t>30005</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>795239532209</t>
+          <t>795239300051</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dandelion Caramel Nut - Herbal Coffee</t>
+          <t>Dandelion - Instant Herbal Coffee</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>3.53oz bag</t>
         </is>
       </c>
       <c r="E99" s="6" t="n">
-        <v>3.99</v>
+        <v>29.99</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>4.49</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t>53340</t>
-        </is>
-      </c>
-      <c r="B100" s="5" t="inlineStr">
-        <is>
-          <t>795239533404</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Dandelion Coconut - Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D100" s="5" t="inlineStr">
-        <is>
-          <t>1.05oz packet</t>
-        </is>
-      </c>
-      <c r="E100" s="6" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="F100" s="6" t="n">
-        <v>4.49</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>53110</t>
-        </is>
-      </c>
-      <c r="B101" s="5" t="inlineStr">
-        <is>
-          <t>795239531103</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Dandelion Dark Roast - Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D101" s="5" t="inlineStr">
-        <is>
-          <t>1.05oz packet</t>
-        </is>
-      </c>
-      <c r="E101" s="6" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="F101" s="6" t="n">
-        <v>4.49</v>
+        <v>32.99</v>
+      </c>
+    </row>
+    <row r="101" ht="22" customHeight="1">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>Item #</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>UPC:</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>Instant Herbal Lattes:</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>Packaging Size:</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>Unit Price:</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>MSRP:</t>
+        </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>53080</t>
+          <t>31008</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>795239530809</t>
+          <t>795239310081</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Dandelion Mocha - Herbal Coffee</t>
+          <t>French Roast - Instant Herbal Latte</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>7.9oz bag</t>
         </is>
       </c>
       <c r="E102" s="6" t="n">
-        <v>3.99</v>
+        <v>21.99</v>
       </c>
       <c r="F102" s="6" t="n">
-        <v>4.49</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>53310</t>
+          <t>31010</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>795239533107</t>
+          <t>795239310104</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dandelion Mocha Mint - Herbal Coffee</t>
+          <t>Hazelnut - Instant Herbal Latte</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>7.9oz bag</t>
         </is>
       </c>
       <c r="E103" s="6" t="n">
-        <v>3.99</v>
+        <v>21.99</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>4.49</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>53010</t>
+          <t>31011</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>795239530106</t>
+          <t>795239310111</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Dandelion Vanilla Nut - Herbal Coffee</t>
+          <t>Mocha - Instant Herbal Latte</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>7.9oz bag</t>
         </is>
       </c>
       <c r="E104" s="6" t="n">
-        <v>3.99</v>
+        <v>21.99</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>4.49</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>53360</t>
+          <t>31009</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>795239533503</t>
+          <t>795239310098</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Holiday Eggnog - Herbal Coffee</t>
+          <t>Vanilla Nut - Instant Herbal Latte</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>7.9oz bag</t>
         </is>
       </c>
       <c r="E105" s="6" t="n">
-        <v>3.99</v>
+        <v>21.99</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>4.49</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>55020</t>
+          <t>30013</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>795239550203</t>
+          <t>795239300136</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chaga Ashwagandha Butterscotch Cream - Herbal Coffee</t>
+          <t>Cacao + 5 - Instant Herbal Coffee</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>4.76oz bag</t>
         </is>
       </c>
       <c r="E106" s="6" t="n">
-        <v>4</v>
+        <v>22.99</v>
       </c>
       <c r="F106" s="6" t="n">
-        <v>4.49</v>
+        <v>25.49</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>56010</t>
+          <t>31007</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>795239560103</t>
+          <t>795239310074</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Dark Chocolate - Herbal Coffee</t>
+          <t>Adapt &amp; Protect - Instant Herbal Latte</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>7.9oz bag</t>
         </is>
       </c>
       <c r="E107" s="6" t="n">
-        <v>4</v>
+        <v>24.99</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>4.49</v>
+        <v>27.49</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>55030</t>
+          <t>31005</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>795239550302</t>
+          <t>795239310050</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Lion's Mane Rhodiola Rose Mushroom - Herbal Coffee</t>
+          <t>Dandelion - Instant Herbal Latte</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>7.9oz bag</t>
         </is>
       </c>
       <c r="E108" s="6" t="n">
-        <v>4</v>
+        <v>24.99</v>
       </c>
       <c r="F108" s="6" t="n">
-        <v>4.49</v>
+        <v>27.49</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>55010</t>
+          <t>31014</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>795239550104</t>
+          <t>795239310142</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Reishi Eleuthero French Roast Mushroom - Herbal Coffee</t>
+          <t>Matcha Latte - Instant Herbal Latte</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>8.9oz bag</t>
         </is>
       </c>
       <c r="E109" s="6" t="n">
-        <v>4</v>
+        <v>29.99</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>4.49</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="5" t="inlineStr">
-        <is>
-          <t>55050</t>
-        </is>
-      </c>
-      <c r="B110" s="5" t="inlineStr">
-        <is>
-          <t>795239550500</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Turkey Tail Astragalus Toasted Maple - Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D110" s="5" t="inlineStr">
-        <is>
-          <t>1.05oz packet</t>
-        </is>
-      </c>
-      <c r="E110" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F110" s="6" t="n">
-        <v>4.49</v>
-      </c>
-    </row>
-    <row r="112" ht="22" customHeight="1">
-      <c r="A112" s="3" t="inlineStr">
-        <is>
-          <t>Item #</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>UPC:</t>
-        </is>
-      </c>
-      <c r="C112" s="4" t="inlineStr">
-        <is>
-          <t>Instant Herbal Coffee:</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>Packaging Size:</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>Unit Price:</t>
-        </is>
-      </c>
-      <c r="F112" s="3" t="inlineStr">
-        <is>
-          <t>MSRP:</t>
+        <v>35.49</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t>Copies of All Certifications Available Upon Request</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="inlineStr">
-        <is>
-          <t>30008</t>
-        </is>
-      </c>
-      <c r="B113" s="5" t="inlineStr">
-        <is>
-          <t>795239300082</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>French Roast - Instant Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D113" s="5" t="inlineStr">
-        <is>
-          <t>3.53oz bag</t>
-        </is>
-      </c>
-      <c r="E113" s="6" t="n">
-        <v>16.99</v>
-      </c>
-      <c r="F113" s="6" t="n">
-        <v>18.49</v>
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>All prices are FOB, Oxnard, California USA with no minimum.</t>
+        </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t>30010</t>
-        </is>
-      </c>
-      <c r="B114" s="5" t="inlineStr">
-        <is>
-          <t>795239300105</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Hazelnut - Instant Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D114" s="5" t="inlineStr">
-        <is>
-          <t>3.53oz bag</t>
-        </is>
-      </c>
-      <c r="E114" s="6" t="n">
-        <v>16.99</v>
-      </c>
-      <c r="F114" s="6" t="n">
-        <v>18.49</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t>30011</t>
-        </is>
-      </c>
-      <c r="B115" s="5" t="inlineStr">
-        <is>
-          <t>795239300112</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Mocha - Instant Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D115" s="5" t="inlineStr">
-        <is>
-          <t>3.53oz bag</t>
-        </is>
-      </c>
-      <c r="E115" s="6" t="n">
-        <v>16.99</v>
-      </c>
-      <c r="F115" s="6" t="n">
-        <v>18.49</v>
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>Order lead time - 5 business days</t>
+        </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t>30009</t>
-        </is>
-      </c>
-      <c r="B116" s="5" t="inlineStr">
-        <is>
-          <t>795239300099</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Vanilla Nut - Instant Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D116" s="5" t="inlineStr">
-        <is>
-          <t>3.53oz bag</t>
-        </is>
-      </c>
-      <c r="E116" s="6" t="n">
-        <v>16.99</v>
-      </c>
-      <c r="F116" s="6" t="n">
-        <v>18.49</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="5" t="inlineStr">
-        <is>
-          <t>30007</t>
-        </is>
-      </c>
-      <c r="B117" s="5" t="inlineStr">
-        <is>
-          <t>795239300075</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Adapt &amp; Protect - Instant Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D117" s="5" t="inlineStr">
-        <is>
-          <t>3.95oz bag</t>
-        </is>
-      </c>
-      <c r="E117" s="6" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="F117" s="6" t="n">
-        <v>25.49</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="5" t="inlineStr">
-        <is>
-          <t>30005</t>
-        </is>
-      </c>
-      <c r="B118" s="5" t="inlineStr">
-        <is>
-          <t>795239300051</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Dandelion - Instant Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D118" s="5" t="inlineStr">
-        <is>
-          <t>3.53oz bag</t>
-        </is>
-      </c>
-      <c r="E118" s="6" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="F118" s="6" t="n">
-        <v>32.99</v>
-      </c>
-    </row>
-    <row r="120" ht="22" customHeight="1">
-      <c r="A120" s="3" t="inlineStr">
-        <is>
-          <t>Item #</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>UPC:</t>
-        </is>
-      </c>
-      <c r="C120" s="4" t="inlineStr">
-        <is>
-          <t>Instant Herbal Lattes:</t>
-        </is>
-      </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>Packaging Size:</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>Unit Price:</t>
-        </is>
-      </c>
-      <c r="F120" s="3" t="inlineStr">
-        <is>
-          <t>MSRP:</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="5" t="inlineStr">
-        <is>
-          <t>31008</t>
-        </is>
-      </c>
-      <c r="B121" s="5" t="inlineStr">
-        <is>
-          <t>795239310081</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>French Roast - Instant Herbal Latte</t>
-        </is>
-      </c>
-      <c r="D121" s="5" t="inlineStr">
-        <is>
-          <t>7.9oz bag</t>
-        </is>
-      </c>
-      <c r="E121" s="6" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F121" s="6" t="n">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>31010</t>
-        </is>
-      </c>
-      <c r="B122" s="5" t="inlineStr">
-        <is>
-          <t>795239310104</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Hazelnut - Instant Herbal Latte</t>
-        </is>
-      </c>
-      <c r="D122" s="5" t="inlineStr">
-        <is>
-          <t>7.9oz bag</t>
-        </is>
-      </c>
-      <c r="E122" s="6" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F122" s="6" t="n">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="5" t="inlineStr">
-        <is>
-          <t>31011</t>
-        </is>
-      </c>
-      <c r="B123" s="5" t="inlineStr">
-        <is>
-          <t>795239310111</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Mocha - Instant Herbal Latte</t>
-        </is>
-      </c>
-      <c r="D123" s="5" t="inlineStr">
-        <is>
-          <t>7.9oz bag</t>
-        </is>
-      </c>
-      <c r="E123" s="6" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F123" s="6" t="n">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="5" t="inlineStr">
-        <is>
-          <t>31009</t>
-        </is>
-      </c>
-      <c r="B124" s="5" t="inlineStr">
-        <is>
-          <t>795239310098</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Vanilla Nut - Instant Herbal Latte</t>
-        </is>
-      </c>
-      <c r="D124" s="5" t="inlineStr">
-        <is>
-          <t>7.9oz bag</t>
-        </is>
-      </c>
-      <c r="E124" s="6" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F124" s="6" t="n">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>30013</t>
-        </is>
-      </c>
-      <c r="B125" s="5" t="inlineStr">
-        <is>
-          <t>795239300136</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Cacao + 5 - Instant Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D125" s="5" t="inlineStr">
-        <is>
-          <t>4.76oz bag</t>
-        </is>
-      </c>
-      <c r="E125" s="6" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="F125" s="6" t="n">
-        <v>25.49</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="5" t="inlineStr">
-        <is>
-          <t>31007</t>
-        </is>
-      </c>
-      <c r="B126" s="5" t="inlineStr">
-        <is>
-          <t>795239310074</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Adapt &amp; Protect - Instant Herbal Latte</t>
-        </is>
-      </c>
-      <c r="D126" s="5" t="inlineStr">
-        <is>
-          <t>7.9oz bag</t>
-        </is>
-      </c>
-      <c r="E126" s="6" t="n">
-        <v>24.99</v>
-      </c>
-      <c r="F126" s="6" t="n">
-        <v>27.49</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="5" t="inlineStr">
-        <is>
-          <t>31005</t>
-        </is>
-      </c>
-      <c r="B127" s="5" t="inlineStr">
-        <is>
-          <t>795239310050</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Dandelion - Instant Herbal Latte</t>
-        </is>
-      </c>
-      <c r="D127" s="5" t="inlineStr">
-        <is>
-          <t>7.9oz bag</t>
-        </is>
-      </c>
-      <c r="E127" s="6" t="n">
-        <v>24.99</v>
-      </c>
-      <c r="F127" s="6" t="n">
-        <v>27.49</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="5" t="inlineStr">
-        <is>
-          <t>31014</t>
-        </is>
-      </c>
-      <c r="B128" s="5" t="inlineStr">
-        <is>
-          <t>795239310142</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Matcha Latte - Instant Herbal Latte</t>
-        </is>
-      </c>
-      <c r="D128" s="5" t="inlineStr">
-        <is>
-          <t>8.9oz bag</t>
-        </is>
-      </c>
-      <c r="E128" s="6" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="F128" s="6" t="n">
-        <v>35.49</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="7" t="inlineStr">
-        <is>
-          <t>Copies of All Certifications Available Upon Request</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="7" t="inlineStr">
-        <is>
-          <t>All prices are FOB, Oxnard, California USA with no minimum.</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="7" t="inlineStr">
-        <is>
-          <t>Order lead time - 5 business days</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="8" t="inlineStr">
+      <c r="A116" s="8" t="inlineStr">
         <is>
           <t>Teeccino Caffé, Inc.  |  P: (800) 498-3434  |  F: (805) 966-0522  |  sales@teeccino.com  |  teeccino.com</t>
         </is>
@@ -3813,12 +3281,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A132:F132"/>
-    <mergeCell ref="A133:F133"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A112:F112"/>
+    <mergeCell ref="A116:F116"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A135:F135"/>
-    <mergeCell ref="A131:F131"/>
+    <mergeCell ref="A114:F114"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToWidth="1"/>
@@ -3832,7 +3300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A8:F92"/>
+  <dimension ref="A8:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.4" customWidth="1" min="1" max="1"/>
@@ -3899,17 +3367,17 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>40110</t>
+          <t>40030</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>795239401109</t>
+          <t>795239400300</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>French Roast - Herbal Tea</t>
+          <t>Almond Amaretto - Herbal Tea</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -3918,26 +3386,26 @@
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>8.99</v>
+        <v>9.99</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>9.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>40030</t>
+          <t>40060</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>795239400300</t>
+          <t>795239400607</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Almond Amaretto - Herbal Tea</t>
+          <t>Hazelnut - Herbal Tea</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -3955,17 +3423,17 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>43340</t>
+          <t>42080</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>795239433407</t>
+          <t>795239420803</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dandelion Coconut - Herbal Tea</t>
+          <t>Irish Cream - Herbal Tea</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -3983,17 +3451,17 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>43310</t>
+          <t>40130</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>795239433100</t>
+          <t>795239401307</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dandelion Mocha Mint - Herbal Tea</t>
+          <t>Maca Chocolate - Herbal Tea</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -4011,22 +3479,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>43320</t>
+          <t>42040</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>795239433209</t>
+          <t>795239420407</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dandelion Red Chai - Herbal Tea</t>
+          <t>Snickerdoodle Chicory - Herbal Tea</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>10ct</t>
+          <t>10ct box</t>
         </is>
       </c>
       <c r="E15" s="6" t="n">
@@ -4039,45 +3507,45 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>43330</t>
+          <t>40010</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>795239433308</t>
+          <t>795239400102</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dandelion Turmeric - Herbal Tea</t>
+          <t>Vanilla Nut - Herbal Tea</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>10ct</t>
+          <t>10ct box</t>
         </is>
       </c>
       <c r="E16" s="6" t="n">
         <v>9.99</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>10.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>40060</t>
+          <t>45020</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>795239400607</t>
+          <t>795239450206</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hazelnut - Herbal Tea</t>
+          <t>Chaga Ashwagandha Butterscotch Cream Mushroom - Herbal Tea</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -4086,26 +3554,26 @@
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>9.99</v>
+        <v>10.99</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>10.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>42080</t>
+          <t>43370</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>795239420803</t>
+          <t>795239433704</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irish Cream - Herbal Tea</t>
+          <t>Dandelion Blueberry Vanilla - Herbal Tea</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -4114,26 +3582,28 @@
         </is>
       </c>
       <c r="E18" s="6" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="F18" s="6" t="n">
         <v>10.99</v>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>40130</t>
+          <t>43220</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>795239401307</t>
+          <t>795239432202</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Maca Chocolate - Herbal Tea</t>
+          <t>Dandelion Caramel Nut - Herbal Tea</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -4142,26 +3612,26 @@
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>9.99</v>
+        <v>10.99</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>10.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>42040</t>
+          <t>43110</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>795239420407</t>
+          <t>795239431106</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Snickerdoodle Chicory - Herbal Tea</t>
+          <t>Dandelion Dark Roast - Herbal Tea</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -4170,26 +3640,26 @@
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>9.99</v>
+        <v>10.99</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>10.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>40010</t>
+          <t>45030</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>795239400102</t>
+          <t>795239450305</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Vanilla Nut - Herbal Tea</t>
+          <t>Lion's Mane Rhodiola Rose - Herbal Tea</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -4198,7 +3668,7 @@
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>9.99</v>
+        <v>10.99</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>11.99</v>
@@ -4207,17 +3677,17 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>45020</t>
+          <t>45010</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>795239450206</t>
+          <t>795239450107</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chaga Ashwagandha Butterscotch Cream Mushroom - Herbal Tea</t>
+          <t>Reishi Eleuthero French Roast Mushroom - Herbal Tea</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -4235,17 +3705,17 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>43370</t>
+          <t>45050</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>795239433704</t>
+          <t>795239450503</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dandelion Blueberry Vanilla - Herbal Tea</t>
+          <t>Turkey Tail Astragalus Toasted Maple Mushroom - Herbal Tea</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -4256,26 +3726,24 @@
       <c r="E23" s="6" t="n">
         <v>10.99</v>
       </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="F23" s="6" t="n">
+        <v>11.99</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>43220</t>
+          <t>45070</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>795239432202</t>
+          <t>795239450701</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dandelion Caramel Nut - Herbal Tea</t>
+          <t>Adapt &amp; Protect - Herbal Tea</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -4284,26 +3752,28 @@
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="F24" s="6" t="n">
         <v>11.99</v>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>43110</t>
+          <t>46010</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>795239431106</t>
+          <t>795239460106</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dandelion Dark Roast - Herbal Tea</t>
+          <t>Dark Chocolate Prebiotic SuperBoost - Herbal Tea</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -4312,400 +3782,398 @@
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>10.99</v>
+        <v>11.99</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>11.99</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>45030</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>795239450305</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Lion's Mane Rhodiola Rose - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>10ct box</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>11.99</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>46020</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>795239460205</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Macadamia Nut Prebiotic SuperBoost - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>10ct box</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>11.99</v>
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Item #</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>UPC:</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>12ct Tea Bag Boxes:</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Packaging Size:</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Unit Price:</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>MSRP:</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>45010</t>
+          <t>40001</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>795239450107</t>
+          <t>795239400010</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Reishi Eleuthero French Roast Mushroom - Herbal Tea</t>
+          <t>Classic - Herbal Tea</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>10ct box</t>
+          <t>12ct box</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>10.99</v>
+        <v>11.99</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>11.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>45050</t>
+          <t>12251</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>795239450503</t>
+          <t>795239122516</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey Tail Astragalus Toasted Maple Mushroom - Herbal Tea</t>
+          <t>Holiday Tea - Herbal Tea</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>10ct box</t>
+          <t>12ct box</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>10.99</v>
+        <v>11.99</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>11.99</v>
+        <v>13.49</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>45070</t>
+          <t>43001</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>795239450701</t>
+          <t>795239430017</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Adapt &amp; Protect - Herbal Tea</t>
+          <t>Dandelion - Herbal Tea</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>10ct box</t>
+          <t>12ct box</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>12.99</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>13.99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>46010</t>
+          <t>45001</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>795239460106</t>
+          <t>795239450015</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dark Chocolate Prebiotic SuperBoost - Herbal Tea</t>
+          <t>Mushroom Adaptogen - Herbal Tea</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>10ct box</t>
+          <t>12ct box</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>11.99</v>
+        <v>12.99</v>
       </c>
       <c r="F31" s="6" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>46001</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>795239460014</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Prebiotic Superboost - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>12ct</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="n">
         <v>12.99</v>
       </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="F32" s="6" t="n">
+        <v>14.49</v>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>Item #</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>UPC:</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>12ct Tea Bag Boxes:</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>25ct Tea Bag Boxes:</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Packaging Size:</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>Unit Price:</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>MSRP:</t>
         </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>40001</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>795239400010</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Classic - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>12ct box</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="F34" s="6" t="n">
-        <v>12.99</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>12251</t>
+          <t>42071</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>795239122516</t>
+          <t>795239420711</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Holiday Tea - Herbal Tea</t>
+          <t>Candy Cane Chicory - Herbal Tea</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>12ct box</t>
+          <t>25ct</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>11.99</v>
+        <v>17.99</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>13.49</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>43001</t>
+          <t>42121</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>795239430017</t>
+          <t>795239421213</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dandelion - Herbal Tea</t>
+          <t>Chocolate Raspberry Chicory - Herbal Tea</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>12ct box</t>
+          <t>25ct box</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>12.99</v>
+        <v>17.99</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>13.99</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>45001</t>
+          <t>40051</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>795239450015</t>
+          <t>795239420117</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mushroom Adaptogen - Herbal Tea</t>
+          <t>English Toffee - Herbal Tea</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>12ct box</t>
+          <t>25ct box</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>12.99</v>
+        <v>17.99</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>13.99</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>46001</t>
+          <t>40111</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>795239460014</t>
+          <t>795239401116</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Prebiotic Superboost - Herbal Tea</t>
+          <t>French Roast - Herbal Tea</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>12ct</t>
+          <t>25ct box</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>12.99</v>
+        <v>17.99</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>14.49</v>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Item #</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>UPC:</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>25ct Tea Bag Boxes:</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Packaging Size:</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>Unit Price:</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>MSRP:</t>
-        </is>
+        <v>19.49</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>42051</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>795239420513</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Gingerbread Chicory - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>25ct box</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>19.49</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>40081</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>795239400812</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Mocha - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>25ct box</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>19.49</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>40031</t>
+          <t>40011</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>795239400317</t>
+          <t>795239400119</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Almond Amaretto - Herbal Tea</t>
+          <t>Vanilla Nut - Herbal Tea</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -4714,26 +4182,26 @@
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>16.99</v>
+        <v>17.99</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>18.49</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>40041</t>
+          <t>43221</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>795239400416</t>
+          <t>795239432219</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Blood Orange - Herbal Tea</t>
+          <t>Dandelion Caramel Nut - Herbal Tea</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -4742,26 +4210,26 @@
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>16.99</v>
+        <v>19.99</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>18.49</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>40021</t>
+          <t>43341</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>795239400218</t>
+          <t>795239433414</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chocolate Peppermint - Herbal Tea</t>
+          <t>Dandelion Coconut - Herbal Tea</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -4770,26 +4238,26 @@
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>16.99</v>
+        <v>19.99</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>18.49</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>40061</t>
+          <t>43011</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>795239400614</t>
+          <t>795239430116</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hazelnut - Herbal Tea</t>
+          <t>Dandelion Vanilla Nut - Herbal Tea</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -4798,26 +4266,26 @@
         </is>
       </c>
       <c r="E44" s="6" t="n">
-        <v>16.99</v>
+        <v>19.99</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>18.49</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>42081</t>
+          <t>43361</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>795239420810</t>
+          <t>795239433612</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Irish Cream - Herbal Tea</t>
+          <t>Holiday Eggnog - Herbal Tea</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -4826,26 +4294,26 @@
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>16.99</v>
+        <v>19.99</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>18.49</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>40071</t>
+          <t>45031</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>795239400713</t>
+          <t>795239450312</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Java - Herbal Tea</t>
+          <t>Lion's Mane Rhodiola Rose - Herbal Tea</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -4854,26 +4322,26 @@
         </is>
       </c>
       <c r="E46" s="6" t="n">
-        <v>16.99</v>
+        <v>19.99</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>18.49</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>40132</t>
+          <t>45051</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>795239401321</t>
+          <t>795239450510</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Maca Chocolate - Herbal Tea</t>
+          <t>Turkey Tail Astragalus Toasted Maple Mushroom - Herbal Tea</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -4882,1075 +4350,263 @@
         </is>
       </c>
       <c r="E47" s="6" t="n">
-        <v>16.99</v>
+        <v>19.99</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>18.49</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>42061</t>
+          <t>45071</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>795239420612</t>
+          <t>795239450718</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Maple Pecan - Herbal Tea</t>
+          <t>Adapt &amp; Protect - Herbal Tea</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>25ct box</t>
+          <t>25ct</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
-        <v>16.99</v>
+        <v>21.99</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>18.49</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>40131</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>795239401314</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Mexican Chocolate Chicory - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>25ct box</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="n">
-        <v>16.99</v>
-      </c>
-      <c r="F49" s="6" t="n">
-        <v>18.49</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>42011</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>795239420117</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Pumpkin Spice - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>25ct box</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="n">
-        <v>16.99</v>
-      </c>
-      <c r="F50" s="6" t="n">
-        <v>18.49</v>
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Item #</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>UPC:</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>50ct Tagless Tea Bags:</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Packaging Size:</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Unit Price:</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>MSRP:</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>42041</t>
+          <t>40116</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>795239420414</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Snickerdoodle Chicory - Herbal Tea</t>
+          <t>French Roast - Herbal Tea</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>25ct box</t>
+          <t>50ct</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>16.99</v>
+        <v>23.99</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>18.49</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>42071</t>
+          <t>40066</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>795239420711</t>
+          <t>795239400669</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Candy Cane Chicory - Herbal Tea</t>
+          <t>Hazelnut - Herbal Tea</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>25ct</t>
+          <t>50ct</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>17.99</v>
+        <v>23.99</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>19.49</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>42121</t>
+          <t>40086</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>795239421213</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chocolate Raspberry Chicory - Herbal Tea</t>
+          <t>Mocha - Herbal Tea</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>25ct box</t>
+          <t>50ct</t>
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>17.99</v>
+        <v>23.99</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>19.49</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>40051</t>
+          <t>40016</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>795239420117</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>English Toffee - Herbal Tea</t>
+          <t>Vanilla Nut - Herbal Tea</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>25ct box</t>
+          <t>50ct</t>
         </is>
       </c>
       <c r="E54" s="6" t="n">
-        <v>17.99</v>
+        <v>23.99</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>19.49</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>40111</t>
+          <t>43226</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>795239401116</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>French Roast - Herbal Tea</t>
+          <t>Dandelion Caramel Nut - Herbal Tea</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>25ct box</t>
+          <t>50ct</t>
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>17.99</v>
+        <v>32.99</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>19.49</v>
+        <v>36.49</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>42051</t>
+          <t>43116</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>795239420513</t>
+          <t>795239431168</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Gingerbread Chicory - Herbal Tea</t>
+          <t>Dandelion Dark Roast - Herbal Tea</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>25ct box</t>
+          <t>50ct</t>
         </is>
       </c>
       <c r="E56" s="6" t="n">
-        <v>17.99</v>
+        <v>32.99</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>19.49</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>40081</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>795239400812</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Mocha - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>25ct box</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="F57" s="6" t="n">
-        <v>19.49</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>40011</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>795239400119</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Vanilla Nut - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>25ct box</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="F58" s="6" t="n">
-        <v>19.49</v>
+        <v>36.49</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>42111</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>795239421114</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>French Vanilla - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>25ct box</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="n">
-        <v>18.49</v>
-      </c>
-      <c r="F59" s="6" t="n">
-        <v>20.49</v>
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>Copies of All Certifications Available Upon Request</t>
+        </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>45021</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>795239450213</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Chaga Ashwagandha Butterscotch Cream Mushroom - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>25ct box</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="n">
-        <v>18.99</v>
-      </c>
-      <c r="F60" s="6" t="n">
-        <v>20.99</v>
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>All prices are FOB, Oxnard, California USA with no minimum.</t>
+        </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>43371</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>795239433711</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Dandelion Blueberry Vanilla - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>25ct box</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="n">
-        <v>18.99</v>
-      </c>
-      <c r="F61" s="6" t="n">
-        <v>20.99</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>43111</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>795239431113</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Dandelion Dark Roast - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>25ct box</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="n">
-        <v>18.99</v>
-      </c>
-      <c r="F62" s="6" t="n">
-        <v>20.99</v>
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>Order lead time - 5 business days</t>
+        </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>43081</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>795239430819</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Dandelion Mocha - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>25ct box</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="n">
-        <v>18.99</v>
-      </c>
-      <c r="F63" s="6" t="n">
-        <v>20.99</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>43311</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>795239433117</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Dandelion Mocha Mint - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>25ct box</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="n">
-        <v>18.99</v>
-      </c>
-      <c r="F64" s="6" t="n">
-        <v>20.99</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>43351</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>795239433513</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Dandelion Passionfruit Peach - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>25ct box</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="n">
-        <v>18.99</v>
-      </c>
-      <c r="F65" s="6" t="n">
-        <v>20.99</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>43321</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>795239433216</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Dandelion Red Chai - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>25ct box</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="n">
-        <v>18.99</v>
-      </c>
-      <c r="F66" s="6" t="n">
-        <v>20.99</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>43331</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>795239433315</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Dandelion Turmeric - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>25ct box</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="n">
-        <v>18.99</v>
-      </c>
-      <c r="F67" s="6" t="n">
-        <v>20.99</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>45011</t>
-        </is>
-      </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>795239450114</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Reishi Eleuthero French Roast Mushroom - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>25ct box</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="n">
-        <v>18.99</v>
-      </c>
-      <c r="F68" s="6" t="n">
-        <v>20.99</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>45061</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>795239450619</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Tremella Tulsi Cardamom Mushroom - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>25ct box</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="n">
-        <v>18.99</v>
-      </c>
-      <c r="F69" s="6" t="n">
-        <v>20.99</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>43221</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>795239432219</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Dandelion Caramel Nut - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>25ct box</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="F70" s="6" t="n">
-        <v>21.99</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>43341</t>
-        </is>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>795239433414</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Dandelion Coconut - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="inlineStr">
-        <is>
-          <t>25ct box</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="F71" s="6" t="n">
-        <v>21.99</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>43011</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>795239430116</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Dandelion Vanilla Nut - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>25ct box</t>
-        </is>
-      </c>
-      <c r="E72" s="6" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="F72" s="6" t="n">
-        <v>21.99</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>46011</t>
-        </is>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>795239460113</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Dark Chocolate Prebiotic SuperBoost - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>25ct box</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="F73" s="6" t="n">
-        <v>21.99</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>43361</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>795239433612</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Holiday Eggnog - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>25ct</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="F74" s="6" t="n">
-        <v>21.99</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>45031</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>795239450312</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Lion's Mane Rhodiola Rose - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="inlineStr">
-        <is>
-          <t>25ct box</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="F75" s="6" t="n">
-        <v>21.99</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>45051</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>795239450510</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Turkey Tail Astragalus Toasted Maple Mushroom - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>25ct box</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="F76" s="6" t="n">
-        <v>21.99</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>45071</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>795239450718</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Adapt &amp; Protect - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="inlineStr">
-        <is>
-          <t>25ct</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F77" s="6" t="n">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>Item #</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>UPC:</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>50ct Tagless Tea Bags:</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>Packaging Size:</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="inlineStr">
-        <is>
-          <t>Unit Price:</t>
-        </is>
-      </c>
-      <c r="F79" s="3" t="inlineStr">
-        <is>
-          <t>MSRP:</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>40116</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>French Roast - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>50ct</t>
-        </is>
-      </c>
-      <c r="E80" s="6" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="F80" s="6" t="n">
-        <v>25.99</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>40066</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>795239400669</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Hazelnut - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>50ct</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="F81" s="6" t="n">
-        <v>25.99</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>40086</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Mocha - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>50ct</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="F82" s="6" t="n">
-        <v>25.99</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>40016</t>
-        </is>
-      </c>
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Vanilla Nut - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D83" s="5" t="inlineStr">
-        <is>
-          <t>50ct</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="F83" s="6" t="n">
-        <v>25.99</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>43226</t>
-        </is>
-      </c>
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Dandelion Caramel Nut - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="inlineStr">
-        <is>
-          <t>50ct</t>
-        </is>
-      </c>
-      <c r="E84" s="6" t="n">
-        <v>32.99</v>
-      </c>
-      <c r="F84" s="6" t="n">
-        <v>36.49</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>43116</t>
-        </is>
-      </c>
-      <c r="B85" s="5" t="inlineStr">
-        <is>
-          <t>795239431168</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Dandelion Dark Roast - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D85" s="5" t="inlineStr">
-        <is>
-          <t>50ct</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="n">
-        <v>32.99</v>
-      </c>
-      <c r="F85" s="6" t="n">
-        <v>36.49</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="7" t="inlineStr">
-        <is>
-          <t>Copies of All Certifications Available Upon Request</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="7" t="inlineStr">
-        <is>
-          <t>All prices are FOB, Oxnard, California USA with no minimum.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="7" t="inlineStr">
-        <is>
-          <t>Order lead time - 5 business days</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="8" t="inlineStr">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>Teeccino Caffé, Inc.  |  P: (800) 498-3434  |  F: (805) 966-0522  |  sales@teeccino.com  |  teeccino.com</t>
         </is>
@@ -5958,12 +4614,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A90:F90"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A60:F60"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A89:F89"/>
-    <mergeCell ref="A88:F88"/>
-    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A59:F59"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToWidth="1"/>

--- a/teeccino-retail-price-list-new-prices.xlsx
+++ b/teeccino-retail-price-list-new-prices.xlsx
@@ -559,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A8:F116"/>
+  <dimension ref="A8:F135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.4" customWidth="1" min="1" max="1"/>
@@ -626,17 +626,17 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>80030</t>
+          <t>80040</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>795239800308</t>
+          <t>795239800407</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Almond Amaretto - Herbal Coffee</t>
+          <t>Blood Orange - Herbal Coffee (APG)</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -645,26 +645,26 @@
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>17.99</v>
+        <v>16.99</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>19.49</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>82070</t>
+          <t>82050</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>795239820702</t>
+          <t>795239820504</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Candy Cane Chicory - Herbal Coffee</t>
+          <t>Gingerbread Chicory - Herbal Coffee</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -673,26 +673,26 @@
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>17.99</v>
+        <v>16.99</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>19.49</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>80020</t>
+          <t>82060</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>795239800209</t>
+          <t>795239820603</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chocolate Mint - Herbal Coffee</t>
+          <t>Maple Pecan - Herbal Coffee</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -701,26 +701,26 @@
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>17.99</v>
+        <v>16.99</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>19.49</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>82120</t>
+          <t>82130</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>795239821204</t>
+          <t>795239821303</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chocolate Raspberry - Herbal Coffee</t>
+          <t>Mexican Chocolate Chicory - Herbal Coffee</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -729,26 +729,26 @@
         </is>
       </c>
       <c r="E14" s="6" t="n">
-        <v>17.99</v>
+        <v>16.99</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>19.49</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>80050</t>
+          <t>82010</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>795239800506</t>
+          <t>795239820108</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>English Toffee - Herbal Coffee</t>
+          <t>Pumpkin Spice - Herbal Coffee</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -757,26 +757,26 @@
         </is>
       </c>
       <c r="E15" s="6" t="n">
-        <v>17.99</v>
+        <v>16.99</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>19.49</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>80110</t>
+          <t>80089</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>795239801107</t>
+          <t>795239800896</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>French Roast - Herbal Coffee</t>
+          <t>Raspberry Mocha - Herbal Coffee</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -785,26 +785,26 @@
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>17.99</v>
+        <v>16.99</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>19.49</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>80060</t>
+          <t>82040</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>795239800605</t>
+          <t>795239820405</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hazelnut - Herbal Coffee</t>
+          <t>Snickerdoodle Chicory - Herbal Coffee</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -813,26 +813,26 @@
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>17.99</v>
+        <v>16.99</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>19.49</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>82080</t>
+          <t>80030</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>795239800308</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irish Cream - Herbal Coffee</t>
+          <t>Almond Amaretto - Herbal Coffee</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -850,17 +850,17 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>80070</t>
+          <t>82070</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>795239800704</t>
+          <t>795239820702</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Java - Herbal Coffee</t>
+          <t>Candy Cane Chicory - Herbal Coffee</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -878,17 +878,17 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>80130</t>
+          <t>80020</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>795239801305</t>
+          <t>795239800209</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Maca Chocolate - Herbal Coffee</t>
+          <t>Chocolate Mint - Herbal Coffee</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -906,17 +906,17 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>80080</t>
+          <t>82120</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>795239800803</t>
+          <t>795239821204</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mocha - Herbal Coffee</t>
+          <t>Chocolate Raspberry - Herbal Coffee</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -934,17 +934,17 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>80010</t>
+          <t>80050</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>795239800100</t>
+          <t>795239800506</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Vanilla Nut - Herbal Coffee</t>
+          <t>English Toffee - Herbal Coffee</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -959,204 +959,228 @@
         <v>19.49</v>
       </c>
     </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Item #</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>UPC:</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>10oz All-purpose Grind:</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Packaging Size:</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Unit Price:</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>MSRP:</t>
-        </is>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>80110</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>795239801107</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>French Roast - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>11oz bag</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>19.49</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>80060</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>795239800605</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Hazelnut - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>11oz bag</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>19.49</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>85020</t>
+          <t>82080</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>795239850204</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chaga Ashwagandha Butterscotch Cream - Herbal Coffee</t>
+          <t>Irish Cream - Herbal Coffee</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>10oz bag</t>
+          <t>11oz bag</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>19.99</v>
+        <v>17.99</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>21.99</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>83220</t>
+          <t>80070</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>795239832200</t>
+          <t>795239800704</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dandelion Caramel Nut - Herbal Coffee</t>
+          <t>Java - Herbal Coffee</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>10oz bag</t>
+          <t>11oz bag</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>19.99</v>
+        <v>17.99</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>21.99</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>85030</t>
+          <t>80130</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>795239850303</t>
+          <t>795239801305</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lion's Mane Rhodiola Rose Mushroom - Herbal Coffee</t>
+          <t>Maca Chocolate - Herbal Coffee</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>10oz bag</t>
+          <t>11oz bag</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>19.99</v>
+        <v>17.99</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>21.99</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>85050</t>
+          <t>80080</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>795239850501</t>
+          <t>795239800803</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Tail Astragalus Toasted Maple - Herbal Coffee</t>
+          <t>Mocha - Herbal Coffee</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>10oz bag</t>
+          <t>11oz bag</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>19.99</v>
+        <v>17.99</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>21.99</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>85070</t>
+          <t>80010</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>795239850709</t>
+          <t>795239800100</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Adapt &amp; Protect - Herbal Coffee</t>
+          <t>Vanilla Nut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>10oz bag</t>
+          <t>11oz bag</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>21.99</v>
+        <v>17.99</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>23.99</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>86010</t>
+          <t>82110</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>795239860104</t>
+          <t>795239821105</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dark Chocolate - Herbal Coffee</t>
+          <t>French Vanilla - Herbal Coffee</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>10oz bag</t>
+          <t>11oz bag</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>21.99</v>
+        <v>18.49</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>23.99</v>
+        <v>20.49</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1172,7 +1196,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>500g All-purpose Grind:</t>
+          <t>10oz All-purpose Grind:</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -1194,632 +1218,632 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>80116</t>
+          <t>83370</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>795239801169</t>
+          <t>795239833702</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>French Roast - Herbal Coffee</t>
+          <t>Blueberry Vanilla - Herbal Coffee</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>10oz bag</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>27.99</v>
+        <v>18.99</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>30.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>80066</t>
+          <t>83340</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>795239800667</t>
+          <t>795239833405</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hazelnut - Herbal Coffee</t>
+          <t>Dandelion Coconut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>10oz bag</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>27.99</v>
+        <v>18.99</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>30.49</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>80086</t>
+          <t>83110</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>795239831104</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mocha - Herbal Coffee</t>
+          <t>Dandelion Dark Roast - Herbal Coffee</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>10oz bag</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>27.99</v>
+        <v>18.99</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>30.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>80016</t>
+          <t>83080</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>795239800162</t>
+          <t>795239830800</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Vanilla Nut - Herbal Coffee</t>
+          <t>Dandelion Mocha - Herbal Coffee</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>10oz bag</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>27.99</v>
+        <v>18.99</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>30.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>83226</t>
+          <t>83310</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>795239833108</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dandelion Caramel Nut - Herbal Coffee</t>
+          <t>Dandelion Mocha Mint - Herbal Coffee</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>10oz bag</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>34.99</v>
+        <v>18.99</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>38.49</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>83116</t>
+          <t>83320</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>795239833207</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dandelion Dark Roast - Herbal Coffee</t>
+          <t>Dandelion Red Chai - Herbal Coffee</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>10oz bag</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>34.99</v>
+        <v>18.99</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>38.49</v>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Item #</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>UPC:</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>5lb Bulk Bags:</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Packaging Size:</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>Unit Price:</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>MSRP:</t>
-        </is>
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>83330</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>795239833306</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Dandelion Turmeric - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>10oz bag</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>83010</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>795239830107</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Dandelion Vanilla Nut - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>10oz bag</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>20.99</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>60030</t>
+          <t>83360</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>795239600304</t>
+          <t>795239833603</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Almond Amaretto - Herbal Coffee</t>
+          <t>Holiday Eggnog - Herbal Coffee</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>10oz bag</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>18.99</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>62070</t>
+          <t>85010</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>795239850105</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Candy Cane Chicory - Herbal Coffee</t>
+          <t>Reishi Eleuthero French Roast Mushroom - Herbal Coffee</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>10oz bag</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>18.99</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>60020</t>
+          <t>85060</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>795239600205</t>
+          <t>795239850600</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chocolate Mint - Herbal Coffee</t>
+          <t>Tremella Tulsi Cardamom Mushroom - Herbal Coffee</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>10oz bag</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>18.99</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>62120</t>
+          <t>85020</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>795239621200</t>
+          <t>795239850204</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chocolate Raspberry Chicory - Herbal Coffee</t>
+          <t>Chaga Ashwagandha Butterscotch Cream - Herbal Coffee</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>10oz bag</t>
         </is>
       </c>
       <c r="E44" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>19.99</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>60110</t>
+          <t>83220</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>795239601103</t>
+          <t>795239832200</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>French Roast - Herbal Coffee</t>
+          <t>Dandelion Caramel Nut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>10oz bag</t>
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>19.99</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>62050</t>
+          <t>85030</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>795239620500</t>
+          <t>795239850303</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Gingerbread Chicory - Herbal Coffee</t>
+          <t>Lion's Mane Rhodiola Rose Mushroom - Herbal Coffee</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>10oz bag</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>19.99</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>60060</t>
+          <t>85050</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>795239600601</t>
+          <t>795239850501</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hazelnut - Herbal Coffee</t>
+          <t>Turkey Tail Astragalus Toasted Maple - Herbal Coffee</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>10oz bag</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>19.99</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>60070</t>
+          <t>85070</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>795239600700</t>
+          <t>795239850709</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Java - Herbal Coffee</t>
+          <t>Adapt &amp; Protect - Herbal Coffee</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>10oz bag</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>21.99</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>60130</t>
+          <t>86010</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>795239601301</t>
+          <t>795239860104</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Maca Chocolate - Herbal Coffee</t>
+          <t>Dark Chocolate - Herbal Coffee</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>10oz bag</t>
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>21.99</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>98.98999999999999</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>62060</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>795239620609</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Maple Pecan - Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>5lb bag</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="n">
-        <v>89.98999999999999</v>
-      </c>
-      <c r="F50" s="6" t="n">
-        <v>98.98999999999999</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>60080</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>795239600809</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Mocha - Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>5lb bag</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="n">
-        <v>89.98999999999999</v>
-      </c>
-      <c r="F51" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Item #</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>UPC:</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>500g All-purpose Grind:</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Packaging Size:</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Unit Price:</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>MSRP:</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>62010</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>795239620104</t>
+          <t>795239801169</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pumpkin Spice - Herbal Coffee</t>
+          <t>French Roast - Herbal Coffee</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>27.99</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>62040</t>
+          <t>80066</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>795239620401</t>
+          <t>795239800667</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Snickerdoodle Chicory - Herbal Coffee</t>
+          <t>Hazelnut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>27.99</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>30.49</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>60010</t>
+          <t>80086</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>795239600106</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Vanilla Nut - Herbal Coffee</t>
+          <t>Mocha - Herbal Coffee</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E54" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>27.99</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>65020</t>
+          <t>80016</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>795239650200</t>
+          <t>795239800162</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chaga Ashwagandha Butterscotch Cream - Herbal Coffee</t>
+          <t>Vanilla Nut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>114.99</v>
+        <v>27.99</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>126.49</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>63220</t>
+          <t>83226</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>795239632206</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1829,114 +1853,90 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E56" s="6" t="n">
-        <v>114.99</v>
+        <v>34.99</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>126.49</v>
+        <v>38.49</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>63340</t>
+          <t>83116</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>795239633401</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dandelion Coconut - Herbal Coffee</t>
+          <t>Dandelion Dark Roast - Herbal Coffee</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E57" s="6" t="n">
-        <v>114.99</v>
+        <v>34.99</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>126.49</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>63110</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>795239631100</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Dandelion Dark Roast - Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>5lb bag</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="n">
-        <v>114.99</v>
-      </c>
-      <c r="F58" s="6" t="n">
-        <v>126.49</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>63080</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>795239630806</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Dandelion Mocha - Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>5lb bag</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="n">
-        <v>114.99</v>
-      </c>
-      <c r="F59" s="6" t="n">
-        <v>126.49</v>
+        <v>38.49</v>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Item #</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>UPC:</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>5lb Bulk Bags:</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Packaging Size:</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Unit Price:</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>MSRP:</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>63310</t>
+          <t>60030</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>795239633104</t>
+          <t>795239600304</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dandelion Mocha Mint - Herbal Coffee</t>
+          <t>Almond Amaretto - Herbal Coffee</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -1945,26 +1945,26 @@
         </is>
       </c>
       <c r="E60" s="6" t="n">
-        <v>114.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>126.49</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>63010</t>
+          <t>62070</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>795239630103</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dandelion Vanilla Nut - Herbal Coffee</t>
+          <t>Candy Cane Chicory - Herbal Coffee</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -1973,26 +1973,26 @@
         </is>
       </c>
       <c r="E61" s="6" t="n">
-        <v>114.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>126.49</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>65010</t>
+          <t>60020</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>795239650101</t>
+          <t>795239600205</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Reishi Eleuthero French Roast Mushroom - Herbal Coffee</t>
+          <t>Chocolate Mint - Herbal Coffee</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -2001,26 +2001,26 @@
         </is>
       </c>
       <c r="E62" s="6" t="n">
-        <v>114.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>126.49</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>65050</t>
+          <t>62120</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>795239650507</t>
+          <t>795239621200</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Turkey Tail Astragalus Toasted Maple - Herbal Coffee</t>
+          <t>Chocolate Raspberry Chicory - Herbal Coffee</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -2029,26 +2029,26 @@
         </is>
       </c>
       <c r="E63" s="6" t="n">
-        <v>114.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>126.49</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>66010</t>
+          <t>60110</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>795239660100</t>
+          <t>795239601103</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dark Chocolate - Herbal Coffee</t>
+          <t>French Roast - Herbal Coffee</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -2057,590 +2057,590 @@
         </is>
       </c>
       <c r="E64" s="6" t="n">
-        <v>139.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>153.99</v>
-      </c>
-    </row>
-    <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>Item #</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>UPC:</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>Trial Size Packets:</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>Packaging Size:</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>Unit Price:</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>MSRP:</t>
-        </is>
+        <v>98.98999999999999</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>62050</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>795239620500</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Gingerbread Chicory - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>5lb bag</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v>89.98999999999999</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>98.98999999999999</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>60060</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>795239600601</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Hazelnut - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>5lb bag</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>89.98999999999999</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>52030</t>
+          <t>60070</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>795239520305</t>
+          <t>795239600700</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Southern Pecan - Herbal Coffee</t>
+          <t>Java - Herbal Coffee</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E67" s="6" t="n">
-        <v>1.43</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>1.99</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>50030</t>
+          <t>60130</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>795239500307</t>
+          <t>795239601301</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Almond Amaretto - Herbal Coffee</t>
+          <t>Maca Chocolate - Herbal Coffee</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E68" s="6" t="n">
-        <v>3.5</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>3.99</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>50020</t>
+          <t>62060</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>795239500208</t>
+          <t>795239620609</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chocolate Mint - Herbal Coffee</t>
+          <t>Maple Pecan - Herbal Coffee</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E69" s="6" t="n">
-        <v>3.5</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>3.99</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>50110</t>
+          <t>60080</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>795239501106</t>
+          <t>795239600809</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>French Roast - Herbal Coffee</t>
+          <t>Mocha - Herbal Coffee</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E70" s="6" t="n">
-        <v>3.5</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>3.99</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>52050</t>
+          <t>62010</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>795239520503</t>
+          <t>795239620104</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Gingerbread Chicory - Herbal Coffee</t>
+          <t>Pumpkin Spice - Herbal Coffee</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E71" s="6" t="n">
-        <v>3.5</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>3.99</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>50060</t>
+          <t>62040</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>795239500604</t>
+          <t>795239620401</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hazelnut - Herbal Coffee</t>
+          <t>Snickerdoodle Chicory - Herbal Coffee</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E72" s="6" t="n">
-        <v>3.5</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>3.99</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>50070</t>
+          <t>60010</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>795239500703</t>
+          <t>795239600106</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Java - Herbal Coffee</t>
+          <t>Vanilla Nut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E73" s="6" t="n">
-        <v>3.5</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>3.99</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>50130</t>
+          <t>65020</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>795239501304</t>
+          <t>795239650200</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Maca Chocolate - Herbal Coffee</t>
+          <t>Chaga Ashwagandha Butterscotch Cream - Herbal Coffee</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E74" s="6" t="n">
-        <v>3.5</v>
+        <v>114.99</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>3.99</v>
+        <v>126.49</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>52060</t>
+          <t>63220</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>795239520602</t>
+          <t>795239632206</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Maple Pecan - Herbal Coffee</t>
+          <t>Dandelion Caramel Nut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E75" s="6" t="n">
-        <v>3.5</v>
+        <v>114.99</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>3.99</v>
+        <v>126.49</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>50080</t>
+          <t>63340</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>795239500802</t>
+          <t>795239633401</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Mocha - Herbal Coffee</t>
+          <t>Dandelion Coconut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E76" s="6" t="n">
-        <v>3.5</v>
+        <v>114.99</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>3.99</v>
+        <v>126.49</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>52010</t>
+          <t>63110</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>795239520107</t>
+          <t>795239631100</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Pumpkin Spice - Herbal Coffee</t>
+          <t>Dandelion Dark Roast - Herbal Coffee</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E77" s="6" t="n">
-        <v>3.5</v>
+        <v>114.99</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>3.99</v>
+        <v>126.49</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>52040</t>
+          <t>63080</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>795239520404</t>
+          <t>795239630806</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Snickerdoodle Chicory - Herbal Coffee</t>
+          <t>Dandelion Mocha - Herbal Coffee</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E78" s="6" t="n">
-        <v>3.5</v>
+        <v>114.99</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>3.99</v>
+        <v>126.49</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>50010</t>
+          <t>63310</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>795239500109</t>
+          <t>795239633104</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Vanilla Nut - Herbal Coffee</t>
+          <t>Dandelion Mocha Mint - Herbal Coffee</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E79" s="6" t="n">
-        <v>3.5</v>
+        <v>114.99</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>3.99</v>
+        <v>126.49</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>53220</t>
+          <t>63010</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>795239532209</t>
+          <t>795239630103</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dandelion Caramel Nut - Herbal Coffee</t>
+          <t>Dandelion Vanilla Nut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E80" s="6" t="n">
-        <v>3.99</v>
+        <v>114.99</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>4.49</v>
+        <v>126.49</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>53340</t>
+          <t>65010</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>795239533404</t>
+          <t>795239650101</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dandelion Coconut - Herbal Coffee</t>
+          <t>Reishi Eleuthero French Roast Mushroom - Herbal Coffee</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E81" s="6" t="n">
-        <v>3.99</v>
+        <v>114.99</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>4.49</v>
+        <v>126.49</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>53110</t>
+          <t>65050</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>795239531103</t>
+          <t>795239650507</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dandelion Dark Roast - Herbal Coffee</t>
+          <t>Turkey Tail Astragalus Toasted Maple - Herbal Coffee</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E82" s="6" t="n">
-        <v>3.99</v>
+        <v>114.99</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>4.49</v>
+        <v>126.49</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>53080</t>
+          <t>66010</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>795239530809</t>
+          <t>795239660100</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dandelion Mocha - Herbal Coffee</t>
+          <t>Dark Chocolate - Herbal Coffee</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E83" s="6" t="n">
-        <v>3.99</v>
+        <v>139.99</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>4.49</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>53310</t>
-        </is>
-      </c>
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>795239533107</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Dandelion Mocha Mint - Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="inlineStr">
-        <is>
-          <t>1.05oz packet</t>
-        </is>
-      </c>
-      <c r="E84" s="6" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="F84" s="6" t="n">
-        <v>4.49</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>53010</t>
-        </is>
-      </c>
-      <c r="B85" s="5" t="inlineStr">
-        <is>
-          <t>795239530106</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Dandelion Vanilla Nut - Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D85" s="5" t="inlineStr">
-        <is>
-          <t>1.05oz packet</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="F85" s="6" t="n">
-        <v>4.49</v>
+        <v>153.99</v>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>Item #</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>UPC:</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>Trial Size Packets:</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Packaging Size:</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>Unit Price:</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>MSRP:</t>
+        </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>53360</t>
+          <t>52030</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>795239533503</t>
+          <t>795239520305</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Holiday Eggnog - Herbal Coffee</t>
+          <t>Southern Pecan - Herbal Coffee</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -2649,26 +2649,26 @@
         </is>
       </c>
       <c r="E86" s="6" t="n">
-        <v>3.99</v>
+        <v>1.43</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>4.49</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>55020</t>
+          <t>50030</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>795239550203</t>
+          <t>795239500307</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chaga Ashwagandha Butterscotch Cream - Herbal Coffee</t>
+          <t>Almond Amaretto - Herbal Coffee</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -2677,26 +2677,26 @@
         </is>
       </c>
       <c r="E87" s="6" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>4.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>56010</t>
+          <t>50020</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>795239560103</t>
+          <t>795239500208</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dark Chocolate - Herbal Coffee</t>
+          <t>Chocolate Mint - Herbal Coffee</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -2705,26 +2705,26 @@
         </is>
       </c>
       <c r="E88" s="6" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>4.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>55030</t>
+          <t>50110</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>795239550302</t>
+          <t>795239501106</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Lion's Mane Rhodiola Rose Mushroom - Herbal Coffee</t>
+          <t>French Roast - Herbal Coffee</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -2733,26 +2733,26 @@
         </is>
       </c>
       <c r="E89" s="6" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>4.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>55010</t>
+          <t>52050</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>795239550104</t>
+          <t>795239520503</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Reishi Eleuthero French Roast Mushroom - Herbal Coffee</t>
+          <t>Gingerbread Chicory - Herbal Coffee</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -2761,26 +2761,26 @@
         </is>
       </c>
       <c r="E90" s="6" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>4.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>55050</t>
+          <t>50060</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>795239550500</t>
+          <t>795239500604</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Turkey Tail Astragalus Toasted Maple - Herbal Coffee</t>
+          <t>Hazelnut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -2789,491 +2789,1023 @@
         </is>
       </c>
       <c r="E91" s="6" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>4.49</v>
-      </c>
-    </row>
-    <row r="93" ht="22" customHeight="1">
-      <c r="A93" s="3" t="inlineStr">
-        <is>
-          <t>Item #</t>
-        </is>
-      </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>UPC:</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>Instant Herbal Coffee:</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>Packaging Size:</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="inlineStr">
-        <is>
-          <t>Unit Price:</t>
-        </is>
-      </c>
-      <c r="F93" s="3" t="inlineStr">
-        <is>
-          <t>MSRP:</t>
-        </is>
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>50070</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>795239500703</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Java - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>1.05oz packet</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F92" s="6" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>50130</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>795239501304</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Maca Chocolate - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>1.05oz packet</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F93" s="6" t="n">
+        <v>3.99</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>30008</t>
+          <t>52060</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>795239300082</t>
+          <t>795239520602</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>French Roast - Instant Herbal Coffee</t>
+          <t>Maple Pecan - Herbal Coffee</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>3.53oz bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E94" s="6" t="n">
-        <v>16.99</v>
+        <v>3.5</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>18.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>30010</t>
+          <t>50080</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>795239300105</t>
+          <t>795239500802</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hazelnut - Instant Herbal Coffee</t>
+          <t>Mocha - Herbal Coffee</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>3.53oz bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E95" s="6" t="n">
-        <v>16.99</v>
+        <v>3.5</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>18.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>30011</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>795239300112</t>
+          <t>795239520107</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Mocha - Instant Herbal Coffee</t>
+          <t>Pumpkin Spice - Herbal Coffee</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>3.53oz bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E96" s="6" t="n">
-        <v>16.99</v>
+        <v>3.5</v>
       </c>
       <c r="F96" s="6" t="n">
-        <v>18.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>30009</t>
+          <t>52040</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>795239300099</t>
+          <t>795239520404</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Vanilla Nut - Instant Herbal Coffee</t>
+          <t>Snickerdoodle Chicory - Herbal Coffee</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>3.53oz bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E97" s="6" t="n">
-        <v>16.99</v>
+        <v>3.5</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>18.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>30007</t>
+          <t>50010</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>795239300075</t>
+          <t>795239500109</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Adapt &amp; Protect - Instant Herbal Coffee</t>
+          <t>Vanilla Nut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>3.95oz bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E98" s="6" t="n">
-        <v>22.99</v>
+        <v>3.5</v>
       </c>
       <c r="F98" s="6" t="n">
-        <v>25.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>30005</t>
+          <t>53220</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>795239300051</t>
+          <t>795239532209</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dandelion - Instant Herbal Coffee</t>
+          <t>Dandelion Caramel Nut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>3.53oz bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E99" s="6" t="n">
-        <v>29.99</v>
+        <v>3.99</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>32.99</v>
-      </c>
-    </row>
-    <row r="101" ht="22" customHeight="1">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>Item #</t>
-        </is>
-      </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>UPC:</t>
-        </is>
-      </c>
-      <c r="C101" s="4" t="inlineStr">
-        <is>
-          <t>Instant Herbal Lattes:</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>Packaging Size:</t>
-        </is>
-      </c>
-      <c r="E101" s="3" t="inlineStr">
-        <is>
-          <t>Unit Price:</t>
-        </is>
-      </c>
-      <c r="F101" s="3" t="inlineStr">
-        <is>
-          <t>MSRP:</t>
-        </is>
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>53340</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>795239533404</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Dandelion Coconut - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>1.05oz packet</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="F100" s="6" t="n">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>53110</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>795239531103</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Dandelion Dark Roast - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>1.05oz packet</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="F101" s="6" t="n">
+        <v>4.49</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>31008</t>
+          <t>53080</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>795239310081</t>
+          <t>795239530809</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>French Roast - Instant Herbal Latte</t>
+          <t>Dandelion Mocha - Herbal Coffee</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>7.9oz bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E102" s="6" t="n">
-        <v>21.99</v>
+        <v>3.99</v>
       </c>
       <c r="F102" s="6" t="n">
-        <v>23.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>31010</t>
+          <t>53310</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>795239310104</t>
+          <t>795239533107</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Hazelnut - Instant Herbal Latte</t>
+          <t>Dandelion Mocha Mint - Herbal Coffee</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>7.9oz bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E103" s="6" t="n">
-        <v>21.99</v>
+        <v>3.99</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>23.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>31011</t>
+          <t>53010</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>795239310111</t>
+          <t>795239530106</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Mocha - Instant Herbal Latte</t>
+          <t>Dandelion Vanilla Nut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>7.9oz bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E104" s="6" t="n">
-        <v>21.99</v>
+        <v>3.99</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>23.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>31009</t>
+          <t>53360</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>795239310098</t>
+          <t>795239533503</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Vanilla Nut - Instant Herbal Latte</t>
+          <t>Holiday Eggnog - Herbal Coffee</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>7.9oz bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E105" s="6" t="n">
-        <v>21.99</v>
+        <v>3.99</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>23.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>30013</t>
+          <t>55020</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>795239300136</t>
+          <t>795239550203</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Cacao + 5 - Instant Herbal Coffee</t>
+          <t>Chaga Ashwagandha Butterscotch Cream - Herbal Coffee</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>4.76oz bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E106" s="6" t="n">
-        <v>22.99</v>
+        <v>4</v>
       </c>
       <c r="F106" s="6" t="n">
-        <v>25.49</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>31007</t>
+          <t>56010</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>795239310074</t>
+          <t>795239560103</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Adapt &amp; Protect - Instant Herbal Latte</t>
+          <t>Dark Chocolate - Herbal Coffee</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>7.9oz bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E107" s="6" t="n">
-        <v>24.99</v>
+        <v>4</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>27.49</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>31005</t>
+          <t>55030</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>795239310050</t>
+          <t>795239550302</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Dandelion - Instant Herbal Latte</t>
+          <t>Lion's Mane Rhodiola Rose Mushroom - Herbal Coffee</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>7.9oz bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E108" s="6" t="n">
-        <v>24.99</v>
+        <v>4</v>
       </c>
       <c r="F108" s="6" t="n">
-        <v>27.49</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
+          <t>55010</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>795239550104</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Reishi Eleuthero French Roast Mushroom - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>1.05oz packet</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F109" s="6" t="n">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>55050</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>795239550500</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Turkey Tail Astragalus Toasted Maple - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>1.05oz packet</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F110" s="6" t="n">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="112" ht="22" customHeight="1">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>Item #</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>UPC:</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>Instant Herbal Coffee:</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>Packaging Size:</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>Unit Price:</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>MSRP:</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>30008</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>795239300082</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>French Roast - Instant Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>3.53oz bag</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="F113" s="6" t="n">
+        <v>18.49</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>30010</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>795239300105</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Hazelnut - Instant Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>3.53oz bag</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="F114" s="6" t="n">
+        <v>18.49</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>30011</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>795239300112</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Mocha - Instant Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>3.53oz bag</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="F115" s="6" t="n">
+        <v>18.49</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>30009</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>795239300099</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Vanilla Nut - Instant Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>3.53oz bag</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="F116" s="6" t="n">
+        <v>18.49</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>30007</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>795239300075</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Adapt &amp; Protect - Instant Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>3.95oz bag</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="F117" s="6" t="n">
+        <v>25.49</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>30005</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>795239300051</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Dandelion - Instant Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>3.53oz bag</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="F118" s="6" t="n">
+        <v>32.99</v>
+      </c>
+    </row>
+    <row r="120" ht="22" customHeight="1">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>Item #</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>UPC:</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>Instant Herbal Lattes:</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>Packaging Size:</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>Unit Price:</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>MSRP:</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>31008</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>795239310081</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>French Roast - Instant Herbal Latte</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>7.9oz bag</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="F121" s="6" t="n">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>31010</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>795239310104</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Hazelnut - Instant Herbal Latte</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>7.9oz bag</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="F122" s="6" t="n">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>31011</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>795239310111</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Mocha - Instant Herbal Latte</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>7.9oz bag</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="F123" s="6" t="n">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>31009</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>795239310098</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Vanilla Nut - Instant Herbal Latte</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>7.9oz bag</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="F124" s="6" t="n">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>30013</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>795239300136</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Cacao + 5 - Instant Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>4.76oz bag</t>
+        </is>
+      </c>
+      <c r="E125" s="6" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="F125" s="6" t="n">
+        <v>25.49</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>31007</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>795239310074</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Adapt &amp; Protect - Instant Herbal Latte</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>7.9oz bag</t>
+        </is>
+      </c>
+      <c r="E126" s="6" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="F126" s="6" t="n">
+        <v>27.49</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>31005</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>795239310050</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Dandelion - Instant Herbal Latte</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>7.9oz bag</t>
+        </is>
+      </c>
+      <c r="E127" s="6" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="F127" s="6" t="n">
+        <v>27.49</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
           <t>31014</t>
         </is>
       </c>
-      <c r="B109" s="5" t="inlineStr">
+      <c r="B128" s="5" t="inlineStr">
         <is>
           <t>795239310142</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>Matcha Latte - Instant Herbal Latte</t>
         </is>
       </c>
-      <c r="D109" s="5" t="inlineStr">
+      <c r="D128" s="5" t="inlineStr">
         <is>
           <t>8.9oz bag</t>
         </is>
       </c>
-      <c r="E109" s="6" t="n">
+      <c r="E128" s="6" t="n">
         <v>29.99</v>
       </c>
-      <c r="F109" s="6" t="n">
+      <c r="F128" s="6" t="n">
         <v>35.49</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="7" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="7" t="inlineStr">
         <is>
           <t>Copies of All Certifications Available Upon Request</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="7" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="7" t="inlineStr">
         <is>
           <t>All prices are FOB, Oxnard, California USA with no minimum.</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="7" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="7" t="inlineStr">
         <is>
           <t>Order lead time - 5 business days</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="8" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="8" t="inlineStr">
         <is>
           <t>Teeccino Caffé, Inc.  |  P: (800) 498-3434  |  F: (805) 966-0522  |  sales@teeccino.com  |  teeccino.com</t>
         </is>
@@ -3281,12 +3813,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A112:F112"/>
-    <mergeCell ref="A116:F116"/>
+    <mergeCell ref="A132:F132"/>
+    <mergeCell ref="A133:F133"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A114:F114"/>
+    <mergeCell ref="A135:F135"/>
+    <mergeCell ref="A131:F131"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToWidth="1"/>
@@ -3300,7 +3832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A8:F63"/>
+  <dimension ref="A8:F92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.4" customWidth="1" min="1" max="1"/>
@@ -3367,17 +3899,17 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>40030</t>
+          <t>40110</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>795239400300</t>
+          <t>795239401109</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Almond Amaretto - Herbal Tea</t>
+          <t>French Roast - Herbal Tea</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -3386,26 +3918,26 @@
         </is>
       </c>
       <c r="E11" s="6" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="F11" s="6" t="n">
         <v>9.99</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>10.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>40060</t>
+          <t>40030</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>795239400607</t>
+          <t>795239400300</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hazelnut - Herbal Tea</t>
+          <t>Almond Amaretto - Herbal Tea</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -3423,17 +3955,17 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>42080</t>
+          <t>43340</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>795239420803</t>
+          <t>795239433407</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Irish Cream - Herbal Tea</t>
+          <t>Dandelion Coconut - Herbal Tea</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -3451,17 +3983,17 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>40130</t>
+          <t>43310</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>795239401307</t>
+          <t>795239433100</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Maca Chocolate - Herbal Tea</t>
+          <t>Dandelion Mocha Mint - Herbal Tea</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -3479,22 +4011,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>42040</t>
+          <t>43320</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>795239420407</t>
+          <t>795239433209</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Snickerdoodle Chicory - Herbal Tea</t>
+          <t>Dandelion Red Chai - Herbal Tea</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>10ct box</t>
+          <t>10ct</t>
         </is>
       </c>
       <c r="E15" s="6" t="n">
@@ -3507,45 +4039,45 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>40010</t>
+          <t>43330</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>795239400102</t>
+          <t>795239433308</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vanilla Nut - Herbal Tea</t>
+          <t>Dandelion Turmeric - Herbal Tea</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>10ct box</t>
+          <t>10ct</t>
         </is>
       </c>
       <c r="E16" s="6" t="n">
         <v>9.99</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>11.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>45020</t>
+          <t>40060</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>795239450206</t>
+          <t>795239400607</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chaga Ashwagandha Butterscotch Cream Mushroom - Herbal Tea</t>
+          <t>Hazelnut - Herbal Tea</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -3554,26 +4086,26 @@
         </is>
       </c>
       <c r="E17" s="6" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F17" s="6" t="n">
         <v>10.99</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>11.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>43370</t>
+          <t>42080</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>795239433704</t>
+          <t>795239420803</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dandelion Blueberry Vanilla - Herbal Tea</t>
+          <t>Irish Cream - Herbal Tea</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -3582,28 +4114,26 @@
         </is>
       </c>
       <c r="E18" s="6" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F18" s="6" t="n">
         <v>10.99</v>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>43220</t>
+          <t>40130</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>795239432202</t>
+          <t>795239401307</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dandelion Caramel Nut - Herbal Tea</t>
+          <t>Maca Chocolate - Herbal Tea</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -3612,26 +4142,26 @@
         </is>
       </c>
       <c r="E19" s="6" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F19" s="6" t="n">
         <v>10.99</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>11.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>43110</t>
+          <t>42040</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>795239431106</t>
+          <t>795239420407</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dandelion Dark Roast - Herbal Tea</t>
+          <t>Snickerdoodle Chicory - Herbal Tea</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -3640,26 +4170,26 @@
         </is>
       </c>
       <c r="E20" s="6" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F20" s="6" t="n">
         <v>10.99</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>11.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>45030</t>
+          <t>40010</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>795239450305</t>
+          <t>795239400102</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lion's Mane Rhodiola Rose - Herbal Tea</t>
+          <t>Vanilla Nut - Herbal Tea</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -3668,7 +4198,7 @@
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>10.99</v>
+        <v>9.99</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>11.99</v>
@@ -3677,17 +4207,17 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>45010</t>
+          <t>45020</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>795239450107</t>
+          <t>795239450206</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Reishi Eleuthero French Roast Mushroom - Herbal Tea</t>
+          <t>Chaga Ashwagandha Butterscotch Cream Mushroom - Herbal Tea</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -3705,17 +4235,17 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>45050</t>
+          <t>43370</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>795239450503</t>
+          <t>795239433704</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey Tail Astragalus Toasted Maple Mushroom - Herbal Tea</t>
+          <t>Dandelion Blueberry Vanilla - Herbal Tea</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -3726,24 +4256,26 @@
       <c r="E23" s="6" t="n">
         <v>10.99</v>
       </c>
-      <c r="F23" s="6" t="n">
-        <v>11.99</v>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>45070</t>
+          <t>43220</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>795239450701</t>
+          <t>795239432202</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Adapt &amp; Protect - Herbal Tea</t>
+          <t>Dandelion Caramel Nut - Herbal Tea</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -3752,28 +4284,26 @@
         </is>
       </c>
       <c r="E24" s="6" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="F24" s="6" t="n">
         <v>11.99</v>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>46010</t>
+          <t>43110</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>795239460106</t>
+          <t>795239431106</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dark Chocolate Prebiotic SuperBoost - Herbal Tea</t>
+          <t>Dandelion Dark Roast - Herbal Tea</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -3782,398 +4312,400 @@
         </is>
       </c>
       <c r="E25" s="6" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="F25" s="6" t="n">
         <v>11.99</v>
       </c>
-      <c r="F25" s="6" t="n">
-        <v>12.99</v>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Item #</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>UPC:</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>12ct Tea Bag Boxes:</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Packaging Size:</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>Unit Price:</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>MSRP:</t>
-        </is>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>45030</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>795239450305</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Lion's Mane Rhodiola Rose - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>10ct box</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>46020</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>795239460205</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Macadamia Nut Prebiotic SuperBoost - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>10ct box</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>11.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>40001</t>
+          <t>45010</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>795239400010</t>
+          <t>795239450107</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Classic - Herbal Tea</t>
+          <t>Reishi Eleuthero French Roast Mushroom - Herbal Tea</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>12ct box</t>
+          <t>10ct box</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="F28" s="6" t="n">
         <v>11.99</v>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>12.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>12251</t>
+          <t>45050</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>795239122516</t>
+          <t>795239450503</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Holiday Tea - Herbal Tea</t>
+          <t>Turkey Tail Astragalus Toasted Maple Mushroom - Herbal Tea</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>12ct box</t>
+          <t>10ct box</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="F29" s="6" t="n">
         <v>11.99</v>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>13.49</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>43001</t>
+          <t>45070</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>795239430017</t>
+          <t>795239450701</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dandelion - Herbal Tea</t>
+          <t>Adapt &amp; Protect - Herbal Tea</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>12ct box</t>
+          <t>10ct box</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>12.99</v>
-      </c>
-      <c r="F30" s="6" t="n">
-        <v>13.99</v>
+        <v>11.99</v>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>45001</t>
+          <t>46010</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>795239450015</t>
+          <t>795239460106</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mushroom Adaptogen - Herbal Tea</t>
+          <t>Dark Chocolate Prebiotic SuperBoost - Herbal Tea</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
+          <t>10ct box</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Item #</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>UPC:</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>12ct Tea Bag Boxes:</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Packaging Size:</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Unit Price:</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>MSRP:</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>40001</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>795239400010</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Classic - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
           <t>12ct box</t>
         </is>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="E34" s="6" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="F34" s="6" t="n">
         <v>12.99</v>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>13.99</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>46001</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>795239460014</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Prebiotic Superboost - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>12ct</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="n">
-        <v>12.99</v>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>14.49</v>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Item #</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>UPC:</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>25ct Tea Bag Boxes:</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Packaging Size:</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Unit Price:</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>MSRP:</t>
-        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>42071</t>
+          <t>12251</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>795239420711</t>
+          <t>795239122516</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Candy Cane Chicory - Herbal Tea</t>
+          <t>Holiday Tea - Herbal Tea</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>25ct</t>
+          <t>12ct box</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>17.99</v>
+        <v>11.99</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>19.49</v>
+        <v>13.49</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>42121</t>
+          <t>43001</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>795239421213</t>
+          <t>795239430017</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chocolate Raspberry Chicory - Herbal Tea</t>
+          <t>Dandelion - Herbal Tea</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>25ct box</t>
+          <t>12ct box</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>17.99</v>
+        <v>12.99</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>19.49</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>40051</t>
+          <t>45001</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>795239420117</t>
+          <t>795239450015</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>English Toffee - Herbal Tea</t>
+          <t>Mushroom Adaptogen - Herbal Tea</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>25ct box</t>
+          <t>12ct box</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>17.99</v>
+        <v>12.99</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>19.49</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>40111</t>
+          <t>46001</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>795239401116</t>
+          <t>795239460014</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>French Roast - Herbal Tea</t>
+          <t>Prebiotic Superboost - Herbal Tea</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>25ct box</t>
+          <t>12ct</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>17.99</v>
+        <v>12.99</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>19.49</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>42051</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>795239420513</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Gingerbread Chicory - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>25ct box</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="F39" s="6" t="n">
-        <v>19.49</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>40081</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>795239400812</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Mocha - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>25ct box</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="F40" s="6" t="n">
-        <v>19.49</v>
+        <v>14.49</v>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Item #</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>UPC:</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>25ct Tea Bag Boxes:</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Packaging Size:</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Unit Price:</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>MSRP:</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>40011</t>
+          <t>40031</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>795239400119</t>
+          <t>795239400317</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Vanilla Nut - Herbal Tea</t>
+          <t>Almond Amaretto - Herbal Tea</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -4182,26 +4714,26 @@
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>17.99</v>
+        <v>16.99</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>19.49</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>43221</t>
+          <t>40041</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>795239432219</t>
+          <t>795239400416</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dandelion Caramel Nut - Herbal Tea</t>
+          <t>Blood Orange - Herbal Tea</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -4210,26 +4742,26 @@
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>19.99</v>
+        <v>16.99</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>21.99</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>43341</t>
+          <t>40021</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>795239433414</t>
+          <t>795239400218</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dandelion Coconut - Herbal Tea</t>
+          <t>Chocolate Peppermint - Herbal Tea</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -4238,26 +4770,26 @@
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>19.99</v>
+        <v>16.99</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>21.99</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>43011</t>
+          <t>40061</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>795239430116</t>
+          <t>795239400614</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dandelion Vanilla Nut - Herbal Tea</t>
+          <t>Hazelnut - Herbal Tea</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -4266,26 +4798,26 @@
         </is>
       </c>
       <c r="E44" s="6" t="n">
-        <v>19.99</v>
+        <v>16.99</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>21.99</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>43361</t>
+          <t>42081</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>795239433612</t>
+          <t>795239420810</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Holiday Eggnog - Herbal Tea</t>
+          <t>Irish Cream - Herbal Tea</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -4294,26 +4826,26 @@
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>19.99</v>
+        <v>16.99</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>21.99</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>45031</t>
+          <t>40071</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>795239450312</t>
+          <t>795239400713</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lion's Mane Rhodiola Rose - Herbal Tea</t>
+          <t>Java - Herbal Tea</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -4322,26 +4854,26 @@
         </is>
       </c>
       <c r="E46" s="6" t="n">
-        <v>19.99</v>
+        <v>16.99</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>21.99</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>45051</t>
+          <t>40132</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>795239450510</t>
+          <t>795239401321</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey Tail Astragalus Toasted Maple Mushroom - Herbal Tea</t>
+          <t>Maca Chocolate - Herbal Tea</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -4350,263 +4882,1075 @@
         </is>
       </c>
       <c r="E47" s="6" t="n">
-        <v>19.99</v>
+        <v>16.99</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>21.99</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>45071</t>
+          <t>42061</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>795239450718</t>
+          <t>795239420612</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Adapt &amp; Protect - Herbal Tea</t>
+          <t>Maple Pecan - Herbal Tea</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>25ct</t>
+          <t>25ct box</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
-        <v>21.99</v>
+        <v>16.99</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>Item #</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>UPC:</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>50ct Tagless Tea Bags:</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>Packaging Size:</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>Unit Price:</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>MSRP:</t>
-        </is>
+        <v>18.49</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>40131</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>795239401314</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Mexican Chocolate Chicory - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>25ct box</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>18.49</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>42011</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>795239420117</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Pumpkin Spice - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>25ct box</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>18.49</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>40116</t>
+          <t>42041</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>795239420414</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>French Roast - Herbal Tea</t>
+          <t>Snickerdoodle Chicory - Herbal Tea</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>50ct</t>
+          <t>25ct box</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>23.99</v>
+        <v>16.99</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>25.99</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>40066</t>
+          <t>42071</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>795239400669</t>
+          <t>795239420711</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hazelnut - Herbal Tea</t>
+          <t>Candy Cane Chicory - Herbal Tea</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>50ct</t>
+          <t>25ct</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>23.99</v>
+        <v>17.99</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>25.99</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>40086</t>
+          <t>42121</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>795239421213</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Mocha - Herbal Tea</t>
+          <t>Chocolate Raspberry Chicory - Herbal Tea</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>50ct</t>
+          <t>25ct box</t>
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>23.99</v>
+        <v>17.99</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>25.99</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>40016</t>
+          <t>40051</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>795239420117</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Vanilla Nut - Herbal Tea</t>
+          <t>English Toffee - Herbal Tea</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>50ct</t>
+          <t>25ct box</t>
         </is>
       </c>
       <c r="E54" s="6" t="n">
-        <v>23.99</v>
+        <v>17.99</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>25.99</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>43226</t>
+          <t>40111</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>795239401116</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dandelion Caramel Nut - Herbal Tea</t>
+          <t>French Roast - Herbal Tea</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>50ct</t>
+          <t>25ct box</t>
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>32.99</v>
+        <v>17.99</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>36.49</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
+          <t>42051</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>795239420513</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Gingerbread Chicory - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>25ct box</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>19.49</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>40081</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>795239400812</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Mocha - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>25ct box</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>19.49</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>40011</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>795239400119</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Vanilla Nut - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>25ct box</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>19.49</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>42111</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>795239421114</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>French Vanilla - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>25ct box</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>18.49</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>20.49</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>45021</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>795239450213</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Chaga Ashwagandha Butterscotch Cream Mushroom - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>25ct box</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>43371</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>795239433711</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dandelion Blueberry Vanilla - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>25ct box</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>43111</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>795239431113</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Dandelion Dark Roast - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>25ct box</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>43081</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>795239430819</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Dandelion Mocha - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>25ct box</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>43311</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>795239433117</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Dandelion Mocha Mint - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>25ct box</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>43351</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>795239433513</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Dandelion Passionfruit Peach - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>25ct box</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>43321</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>795239433216</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Dandelion Red Chai - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>25ct box</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>43331</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>795239433315</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Dandelion Turmeric - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>25ct box</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>45011</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>795239450114</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Reishi Eleuthero French Roast Mushroom - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>25ct box</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>45061</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>795239450619</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Tremella Tulsi Cardamom Mushroom - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>25ct box</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>43221</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>795239432219</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Dandelion Caramel Nut - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>25ct box</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>43341</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>795239433414</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Dandelion Coconut - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>25ct box</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>43011</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>795239430116</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Dandelion Vanilla Nut - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>25ct box</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>46011</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>795239460113</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Dark Chocolate Prebiotic SuperBoost - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>25ct box</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>43361</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>795239433612</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Holiday Eggnog - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>25ct</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="F74" s="6" t="n">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>45031</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>795239450312</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Lion's Mane Rhodiola Rose - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>25ct box</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>45051</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>795239450510</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Turkey Tail Astragalus Toasted Maple Mushroom - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>25ct box</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="F76" s="6" t="n">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>45071</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>795239450718</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Adapt &amp; Protect - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>25ct</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="F77" s="6" t="n">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>Item #</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>UPC:</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>50ct Tagless Tea Bags:</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Packaging Size:</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>Unit Price:</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>MSRP:</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>40116</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>French Roast - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>50ct</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="F80" s="6" t="n">
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>40066</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>795239400669</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Hazelnut - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>50ct</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="F81" s="6" t="n">
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>40086</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Mocha - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>50ct</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="F82" s="6" t="n">
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>40016</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Vanilla Nut - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>50ct</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="F83" s="6" t="n">
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>43226</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Dandelion Caramel Nut - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>50ct</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="F84" s="6" t="n">
+        <v>36.49</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
           <t>43116</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B85" s="5" t="inlineStr">
         <is>
           <t>795239431168</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Dandelion Dark Roast - Herbal Tea</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D85" s="5" t="inlineStr">
         <is>
           <t>50ct</t>
         </is>
       </c>
-      <c r="E56" s="6" t="n">
+      <c r="E85" s="6" t="n">
         <v>32.99</v>
       </c>
-      <c r="F56" s="6" t="n">
+      <c r="F85" s="6" t="n">
         <v>36.49</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="7" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
         <is>
           <t>Copies of All Certifications Available Upon Request</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="7" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
         <is>
           <t>All prices are FOB, Oxnard, California USA with no minimum.</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="7" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
         <is>
           <t>Order lead time - 5 business days</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="8" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="8" t="inlineStr">
         <is>
           <t>Teeccino Caffé, Inc.  |  P: (800) 498-3434  |  F: (805) 966-0522  |  sales@teeccino.com  |  teeccino.com</t>
         </is>
@@ -4614,12 +5958,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A63:F63"/>
-    <mergeCell ref="A60:F60"/>
+    <mergeCell ref="A90:F90"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A61:F61"/>
-    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="A89:F89"/>
+    <mergeCell ref="A88:F88"/>
+    <mergeCell ref="A92:F92"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToWidth="1"/>

--- a/teeccino-retail-price-list-new-prices.xlsx
+++ b/teeccino-retail-price-list-new-prices.xlsx
@@ -3899,17 +3899,17 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>40110</t>
+          <t>40030</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>795239401109</t>
+          <t>795239400300</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>French Roast - Herbal Tea</t>
+          <t>Almond Amaretto - Herbal Tea</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -3927,17 +3927,17 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>40030</t>
+          <t>40110</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>795239400300</t>
+          <t>795239401109</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Almond Amaretto - Herbal Tea</t>
+          <t>French Roast - Herbal Tea</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -3946,26 +3946,26 @@
         </is>
       </c>
       <c r="E12" s="6" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="F12" s="6" t="n">
         <v>9.99</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>10.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>43340</t>
+          <t>40060</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>795239433407</t>
+          <t>795239400607</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dandelion Coconut - Herbal Tea</t>
+          <t>Hazelnut - Herbal Tea</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -3974,26 +3974,26 @@
         </is>
       </c>
       <c r="E13" s="6" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="F13" s="6" t="n">
         <v>9.99</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>10.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>43310</t>
+          <t>42080</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>795239433100</t>
+          <t>795239420803</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dandelion Mocha Mint - Herbal Tea</t>
+          <t>Irish Cream - Herbal Tea</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -4002,82 +4002,82 @@
         </is>
       </c>
       <c r="E14" s="6" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="F14" s="6" t="n">
         <v>9.99</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>10.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>43320</t>
+          <t>40130</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>795239433209</t>
+          <t>795239401307</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dandelion Red Chai - Herbal Tea</t>
+          <t>Maca Chocolate - Herbal Tea</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>10ct</t>
+          <t>10ct box</t>
         </is>
       </c>
       <c r="E15" s="6" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="F15" s="6" t="n">
         <v>9.99</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>10.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>43330</t>
+          <t>42040</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>795239433308</t>
+          <t>795239420407</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dandelion Turmeric - Herbal Tea</t>
+          <t>Snickerdoodle Chicory - Herbal Tea</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>10ct</t>
+          <t>10ct box</t>
         </is>
       </c>
       <c r="E16" s="6" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="F16" s="6" t="n">
         <v>9.99</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>10.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>40060</t>
+          <t>40010</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>795239400607</t>
+          <t>795239400102</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hazelnut - Herbal Tea</t>
+          <t>Vanilla Nut - Herbal Tea</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>9.99</v>
+        <v>8.99</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10.99</v>
@@ -4095,17 +4095,17 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>42080</t>
+          <t>45020</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>795239420803</t>
+          <t>795239450206</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irish Cream - Herbal Tea</t>
+          <t>Chaga Ashwagandha Butterscotch Cream Mushroom - Herbal Tea</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -4123,17 +4123,17 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>40130</t>
+          <t>43370</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>795239401307</t>
+          <t>795239433704</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Maca Chocolate - Herbal Tea</t>
+          <t>Dandelion Blueberry Vanilla - Herbal Tea</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -4144,24 +4144,26 @@
       <c r="E19" s="6" t="n">
         <v>9.99</v>
       </c>
-      <c r="F19" s="6" t="n">
-        <v>10.99</v>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>42040</t>
+          <t>43220</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>795239420407</t>
+          <t>795239432202</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Snickerdoodle Chicory - Herbal Tea</t>
+          <t>Dandelion Caramel Nut - Herbal Tea</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -4179,17 +4181,17 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>40010</t>
+          <t>43340</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>795239400102</t>
+          <t>795239433407</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Vanilla Nut - Herbal Tea</t>
+          <t>Dandelion Coconut - Herbal Tea</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -4201,23 +4203,23 @@
         <v>9.99</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>11.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>45020</t>
+          <t>43110</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>795239450206</t>
+          <t>795239431106</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chaga Ashwagandha Butterscotch Cream Mushroom - Herbal Tea</t>
+          <t>Dandelion Dark Roast - Herbal Tea</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -4226,26 +4228,26 @@
         </is>
       </c>
       <c r="E22" s="6" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F22" s="6" t="n">
         <v>10.99</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>11.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>43370</t>
+          <t>43310</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>795239433704</t>
+          <t>795239433100</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dandelion Blueberry Vanilla - Herbal Tea</t>
+          <t>Dandelion Mocha Mint - Herbal Tea</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -4254,68 +4256,66 @@
         </is>
       </c>
       <c r="E23" s="6" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F23" s="6" t="n">
         <v>10.99</v>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>43220</t>
+          <t>43320</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>795239432202</t>
+          <t>795239433209</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dandelion Caramel Nut - Herbal Tea</t>
+          <t>Dandelion Red Chai - Herbal Tea</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>10ct box</t>
+          <t>10ct</t>
         </is>
       </c>
       <c r="E24" s="6" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F24" s="6" t="n">
         <v>10.99</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>11.99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>43110</t>
+          <t>43330</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>795239431106</t>
+          <t>795239433308</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dandelion Dark Roast - Herbal Tea</t>
+          <t>Dandelion Turmeric - Herbal Tea</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>10ct box</t>
+          <t>10ct</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F25" s="6" t="n">
         <v>10.99</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>11.99</v>
       </c>
     </row>
     <row r="26">
@@ -4340,26 +4340,26 @@
         </is>
       </c>
       <c r="E26" s="6" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F26" s="6" t="n">
         <v>10.99</v>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>11.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>46020</t>
+          <t>45010</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>795239460205</t>
+          <t>795239450107</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Macadamia Nut Prebiotic SuperBoost - Herbal Tea</t>
+          <t>Reishi Eleuthero French Roast Mushroom - Herbal Tea</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -4368,26 +4368,26 @@
         </is>
       </c>
       <c r="E27" s="6" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F27" s="6" t="n">
         <v>10.99</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>11.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>45010</t>
+          <t>45050</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>795239450107</t>
+          <t>795239450503</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Reishi Eleuthero French Roast Mushroom - Herbal Tea</t>
+          <t>Turkey Tail Astragalus Toasted Maple Mushroom - Herbal Tea</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -4396,26 +4396,26 @@
         </is>
       </c>
       <c r="E28" s="6" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F28" s="6" t="n">
         <v>10.99</v>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>11.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>45050</t>
+          <t>45070</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>795239450503</t>
+          <t>795239450701</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey Tail Astragalus Toasted Maple Mushroom - Herbal Tea</t>
+          <t>Adapt &amp; Protect - Herbal Tea</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -4424,26 +4424,28 @@
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>11.99</v>
+        <v>10.49</v>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>45070</t>
+          <t>46010</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>795239450701</t>
+          <t>795239460106</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Adapt &amp; Protect - Herbal Tea</t>
+          <t>Dark Chocolate Prebiotic SuperBoost - Herbal Tea</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -4452,28 +4454,26 @@
         </is>
       </c>
       <c r="E30" s="6" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="F30" s="6" t="n">
         <v>11.99</v>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>46010</t>
+          <t>46020</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>795239460106</t>
+          <t>795239460205</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dark Chocolate Prebiotic SuperBoost - Herbal Tea</t>
+          <t>Macadamia Nut Prebiotic SuperBoost - Herbal Tea</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -4482,10 +4482,10 @@
         </is>
       </c>
       <c r="E31" s="6" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="F31" s="6" t="n">
         <v>11.99</v>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>12.99</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/teeccino-retail-price-list-new-prices.xlsx
+++ b/teeccino-retail-price-list-new-prices.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,6 +42,10 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="008A8178"/>
     </font>
     <font>
       <i val="1"/>
@@ -80,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -101,7 +105,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -559,15 +564,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A8:F135"/>
+  <dimension ref="A8:F157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.4" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="53.5" customWidth="1" min="3" max="3"/>
-    <col width="20.5" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="19.6" customWidth="1" min="6" max="6"/>
+    <col width="15.6" customWidth="1" min="2" max="2"/>
+    <col width="76" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12.4" customWidth="1" min="5" max="5"/>
+    <col width="15.6" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1"/>
@@ -654,17 +659,17 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>82050</t>
+          <t>82020</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>795239820504</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Gingerbread Chicory - Herbal Coffee</t>
+          <t>795239820207</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Caramel Nut - Herbal Coffee (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -682,17 +687,17 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>82060</t>
+          <t>82050</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>795239820603</t>
+          <t>795239820504</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Maple Pecan - Herbal Coffee</t>
+          <t>Gingerbread Chicory - Herbal Coffee</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -710,17 +715,17 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>82130</t>
+          <t>82060</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>795239821303</t>
+          <t>795239820603</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mexican Chocolate Chicory - Herbal Coffee</t>
+          <t>Maple Pecan - Herbal Coffee</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -738,17 +743,17 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>82010</t>
+          <t>80120</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>795239820108</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Pumpkin Spice - Herbal Coffee</t>
+          <t>795239801206</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Maya Chai - Herbal Coffee (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -766,17 +771,17 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>80089</t>
+          <t>82130</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>795239800896</t>
+          <t>795239821303</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Raspberry Mocha - Herbal Coffee</t>
+          <t>Mexican Chocolate Chicory - Herbal Coffee</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -788,23 +793,23 @@
         <v>16.99</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>18.99</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>82040</t>
+          <t>80140</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>795239820405</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Snickerdoodle Chicory - Herbal Coffee</t>
+          <t>795239801404</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Original - Herbal Coffee (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -822,17 +827,17 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>80030</t>
+          <t>82010</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>795239800308</t>
+          <t>795239820108</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Almond Amaretto - Herbal Coffee</t>
+          <t>Pumpkin Spice - Herbal Coffee</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -841,26 +846,26 @@
         </is>
       </c>
       <c r="E18" s="6" t="n">
-        <v>17.99</v>
+        <v>16.99</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>19.49</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>82070</t>
+          <t>80089</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>795239820702</t>
+          <t>795239800896</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Candy Cane Chicory - Herbal Coffee</t>
+          <t>Raspberry Mocha - Herbal Coffee</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -869,26 +874,26 @@
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>17.99</v>
+        <v>16.99</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>19.49</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>80020</t>
+          <t>82040</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>795239800209</t>
+          <t>795239820405</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chocolate Mint - Herbal Coffee</t>
+          <t>Snickerdoodle Chicory - Herbal Coffee</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -897,26 +902,26 @@
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>17.99</v>
+        <v>16.99</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>19.49</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>82120</t>
+          <t>80030</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>795239821204</t>
+          <t>795239800308</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chocolate Raspberry - Herbal Coffee</t>
+          <t>Almond Amaretto - Herbal Coffee</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -934,17 +939,17 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>80050</t>
+          <t>82070</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>795239800506</t>
+          <t>795239820702</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>English Toffee - Herbal Coffee</t>
+          <t>Candy Cane Chicory - Herbal Coffee</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -962,17 +967,17 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>80110</t>
+          <t>80020</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>795239801107</t>
+          <t>795239800209</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>French Roast - Herbal Coffee</t>
+          <t>Chocolate Mint - Herbal Coffee</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -990,17 +995,17 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>80060</t>
+          <t>82120</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>795239800605</t>
+          <t>795239821204</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hazelnut - Herbal Coffee</t>
+          <t>Chocolate Raspberry - Herbal Coffee</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1018,17 +1023,17 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>82080</t>
+          <t>80050</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>795239800506</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irish Cream - Herbal Coffee</t>
+          <t>English Toffee - Herbal Coffee</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1046,17 +1051,17 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>80070</t>
+          <t>80110</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>795239800704</t>
+          <t>795239801107</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Java - Herbal Coffee</t>
+          <t>French Roast - Herbal Coffee</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1074,17 +1079,17 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>80130</t>
+          <t>80060</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>795239801305</t>
+          <t>795239800605</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Maca Chocolate - Herbal Coffee</t>
+          <t>Hazelnut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1102,17 +1107,17 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>80080</t>
+          <t>82080</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>795239800803</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mocha - Herbal Coffee</t>
+          <t>Irish Cream - Herbal Coffee</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -1130,17 +1135,17 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>80010</t>
+          <t>80070</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>795239800100</t>
+          <t>795239800704</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Vanilla Nut - Herbal Coffee</t>
+          <t>Java - Herbal Coffee</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -1158,17 +1163,17 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>82110</t>
+          <t>80130</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>795239821105</t>
+          <t>795239801305</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>French Vanilla - Herbal Coffee</t>
+          <t>Maca Chocolate - Herbal Coffee</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -1177,142 +1182,142 @@
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>18.49</v>
+        <v>17.99</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>20.49</v>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Item #</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>UPC:</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>10oz All-purpose Grind:</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Packaging Size:</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Unit Price:</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>MSRP:</t>
-        </is>
+        <v>19.49</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>80080</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>795239800803</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Mocha - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>11oz bag</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>19.49</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>80010</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>795239800100</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Vanilla Nut - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>11oz bag</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>19.49</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>83370</t>
+          <t>82110</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>795239833702</t>
+          <t>795239821105</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Blueberry Vanilla - Herbal Coffee</t>
+          <t>French Vanilla - Herbal Coffee</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>10oz bag</t>
+          <t>11oz bag</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>18.99</v>
+        <v>18.49</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>20.99</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>83340</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>795239833405</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Dandelion Coconut - Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>10oz bag</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="n">
-        <v>18.99</v>
-      </c>
-      <c r="F34" s="6" t="n">
-        <v>20.99</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>83110</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>795239831104</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Dandelion Dark Roast - Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>10oz bag</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="n">
-        <v>18.99</v>
-      </c>
-      <c r="F35" s="6" t="n">
-        <v>20.99</v>
+        <v>20.49</v>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Item #</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>UPC:</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>10oz All-purpose Grind:</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Packaging Size:</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Unit Price:</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>MSRP:</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>83080</t>
+          <t>83370</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>795239830800</t>
+          <t>795239833702</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dandelion Mocha - Herbal Coffee</t>
+          <t>Blueberry Vanilla - Herbal Coffee</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -1330,17 +1335,17 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>83310</t>
+          <t>85040</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>795239833108</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Dandelion Mocha Mint - Herbal Coffee</t>
+          <t>795239850402</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Cordyceps Schisandra Cinnamon Berry Mushroom - Herbal Coffee (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -1358,17 +1363,17 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>83340</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>795239833207</t>
+          <t>795239833405</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dandelion Red Chai - Herbal Coffee</t>
+          <t>Dandelion Coconut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -1386,17 +1391,17 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>83330</t>
+          <t>83110</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>795239833306</t>
+          <t>795239831104</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dandelion Turmeric - Herbal Coffee</t>
+          <t>Dandelion Dark Roast - Herbal Coffee</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -1414,17 +1419,17 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>83010</t>
+          <t>83080</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>795239830107</t>
+          <t>795239830800</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dandelion Vanilla Nut - Herbal Coffee</t>
+          <t>Dandelion Mocha - Herbal Coffee</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -1442,17 +1447,17 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>83360</t>
+          <t>83310</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>795239833603</t>
+          <t>795239833108</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Holiday Eggnog - Herbal Coffee</t>
+          <t>Dandelion Mocha Mint - Herbal Coffee</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -1470,17 +1475,17 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>85010</t>
+          <t>83350</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>795239850105</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Reishi Eleuthero French Roast Mushroom - Herbal Coffee</t>
+          <t>795239833504</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Dandelion Passionfruit Peach - Herbal Coffee (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -1498,17 +1503,17 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>85060</t>
+          <t>83320</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>795239850600</t>
+          <t>795239833207</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tremella Tulsi Cardamom Mushroom - Herbal Coffee</t>
+          <t>Dandelion Red Chai - Herbal Coffee</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -1526,17 +1531,17 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>85020</t>
+          <t>83330</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>795239850204</t>
+          <t>795239833306</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chaga Ashwagandha Butterscotch Cream - Herbal Coffee</t>
+          <t>Dandelion Turmeric - Herbal Coffee</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -1545,26 +1550,26 @@
         </is>
       </c>
       <c r="E44" s="6" t="n">
-        <v>19.99</v>
+        <v>18.99</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>21.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>83220</t>
+          <t>83010</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>795239832200</t>
+          <t>795239830107</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dandelion Caramel Nut - Herbal Coffee</t>
+          <t>Dandelion Vanilla Nut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -1573,26 +1578,26 @@
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>19.99</v>
+        <v>18.99</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>21.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>85030</t>
+          <t>83360</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>795239850303</t>
+          <t>795239833603</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lion's Mane Rhodiola Rose Mushroom - Herbal Coffee</t>
+          <t>Holiday Eggnog - Herbal Coffee</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -1601,26 +1606,26 @@
         </is>
       </c>
       <c r="E46" s="6" t="n">
-        <v>19.99</v>
+        <v>18.99</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>21.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>85050</t>
+          <t>85010</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>795239850501</t>
+          <t>795239850105</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey Tail Astragalus Toasted Maple - Herbal Coffee</t>
+          <t>Reishi Eleuthero French Roast Mushroom - Herbal Coffee</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -1629,26 +1634,26 @@
         </is>
       </c>
       <c r="E47" s="6" t="n">
-        <v>19.99</v>
+        <v>18.99</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>21.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>85070</t>
+          <t>85060</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>795239850709</t>
+          <t>795239850600</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Adapt &amp; Protect - Herbal Coffee</t>
+          <t>Tremella Tulsi Cardamom Mushroom - Herbal Coffee</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -1657,26 +1662,26 @@
         </is>
       </c>
       <c r="E48" s="6" t="n">
-        <v>21.99</v>
+        <v>18.99</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>23.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>86010</t>
+          <t>85020</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>795239860104</t>
+          <t>795239850204</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dark Chocolate - Herbal Coffee</t>
+          <t>Chaga Ashwagandha Butterscotch Cream - Herbal Coffee</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -1685,276 +1690,300 @@
         </is>
       </c>
       <c r="E49" s="6" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="F49" s="6" t="n">
         <v>21.99</v>
       </c>
-      <c r="F49" s="6" t="n">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>Item #</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>UPC:</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>500g All-purpose Grind:</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>Packaging Size:</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>Unit Price:</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>MSRP:</t>
-        </is>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>83220</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>795239832200</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Dandelion Caramel Nut - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>10oz bag</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>85030</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>795239850303</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Lion's Mane Rhodiola Rose Mushroom - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>10oz bag</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>21.99</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>80116</t>
+          <t>86020</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>795239801169</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>French Roast - Herbal Coffee</t>
+          <t>795239860203</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>Macadamia Nut Prebiotic SuperBoost - Herbal Coffee (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>10oz bag</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>27.99</v>
+        <v>19.99</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>30.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>80066</t>
+          <t>86030</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>795239800667</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Hazelnut - Herbal Coffee</t>
+          <t>795239860302</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>Mango Lemon Balm Prebiotic SuperBoost - Herbal Coffee (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>10oz bag</t>
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>27.99</v>
+        <v>19.99</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>30.49</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>80086</t>
+          <t>85050</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>795239850501</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Mocha - Herbal Coffee</t>
+          <t>Turkey Tail Astragalus Toasted Maple - Herbal Coffee</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>10oz bag</t>
         </is>
       </c>
       <c r="E54" s="6" t="n">
-        <v>27.99</v>
+        <v>19.99</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>30.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>80016</t>
+          <t>85070</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>795239800162</t>
+          <t>795239850709</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Vanilla Nut - Herbal Coffee</t>
+          <t>Adapt &amp; Protect - Herbal Coffee</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>10oz bag</t>
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>27.99</v>
+        <v>21.99</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>30.99</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>83226</t>
+          <t>86010</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>795239860104</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dandelion Caramel Nut - Herbal Coffee</t>
+          <t>Dark Chocolate - Herbal Coffee</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
+          <t>10oz bag</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Item #</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>UPC:</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>500g All-purpose Grind:</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Packaging Size:</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Unit Price:</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>MSRP:</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>80116</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>795239801169</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>French Roast - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
           <t>500g</t>
         </is>
       </c>
-      <c r="E56" s="6" t="n">
-        <v>34.99</v>
-      </c>
-      <c r="F56" s="6" t="n">
-        <v>38.49</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>83116</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Dandelion Dark Roast - Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>500g</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="n">
-        <v>34.99</v>
-      </c>
-      <c r="F57" s="6" t="n">
-        <v>38.49</v>
-      </c>
-    </row>
-    <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>Item #</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>UPC:</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>5lb Bulk Bags:</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>Packaging Size:</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>Unit Price:</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>MSRP:</t>
-        </is>
+      <c r="E59" s="6" t="n">
+        <v>27.99</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>30.99</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>60030</t>
+          <t>80066</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>795239600304</t>
+          <t>795239800667</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Almond Amaretto - Herbal Coffee</t>
+          <t>Hazelnut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E60" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>27.99</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>30.49</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>62070</t>
+          <t>80086</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -1964,175 +1993,151 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Candy Cane Chicory - Herbal Coffee</t>
+          <t>Mocha - Herbal Coffee</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E61" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>27.99</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>60020</t>
+          <t>80016</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>795239600205</t>
+          <t>795239800162</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chocolate Mint - Herbal Coffee</t>
+          <t>Vanilla Nut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E62" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>27.99</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>62120</t>
+          <t>83226</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>795239621200</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chocolate Raspberry Chicory - Herbal Coffee</t>
+          <t>Dandelion Caramel Nut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E63" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>34.99</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>38.49</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>60110</t>
+          <t>83116</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>795239601103</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>French Roast - Herbal Coffee</t>
+          <t>Dandelion Dark Roast - Herbal Coffee</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>5lb bag</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E64" s="6" t="n">
-        <v>89.98999999999999</v>
+        <v>34.99</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>98.98999999999999</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>62050</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>795239620500</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Gingerbread Chicory - Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>5lb bag</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="n">
-        <v>89.98999999999999</v>
-      </c>
-      <c r="F65" s="6" t="n">
-        <v>98.98999999999999</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>60060</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>795239600601</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Hazelnut - Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>5lb bag</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="n">
-        <v>89.98999999999999</v>
-      </c>
-      <c r="F66" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>38.49</v>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Item #</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>UPC:</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>5lb Bulk Bags:</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Packaging Size:</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Unit Price:</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>MSRP:</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>60070</t>
+          <t>60030</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>795239600700</t>
+          <t>795239600304</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Java - Herbal Coffee</t>
+          <t>Almond Amaretto - Herbal Coffee</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -2150,17 +2155,17 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>60130</t>
+          <t>60040</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>795239601301</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Maca Chocolate - Herbal Coffee</t>
+          <t>795239600403</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>Blood Orange - Herbal Coffee (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -2178,17 +2183,17 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>62060</t>
+          <t>62070</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>795239620609</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Maple Pecan - Herbal Coffee</t>
+          <t>Candy Cane Chicory - Herbal Coffee</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -2206,17 +2211,17 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>60080</t>
+          <t>62020</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>795239600809</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Mocha - Herbal Coffee</t>
+          <t>795239620203</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>Caramel Nut - Herbal Coffee (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -2234,17 +2239,17 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>62010</t>
+          <t>60020</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>795239620104</t>
+          <t>795239600205</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pumpkin Spice - Herbal Coffee</t>
+          <t>Chocolate Mint - Herbal Coffee</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -2262,17 +2267,17 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>62040</t>
+          <t>62120</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>795239620401</t>
+          <t>795239621200</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Snickerdoodle Chicory - Herbal Coffee</t>
+          <t>Chocolate Raspberry Chicory - Herbal Coffee</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -2290,17 +2295,17 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>60010</t>
+          <t>60110</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>795239600106</t>
+          <t>795239601103</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Vanilla Nut - Herbal Coffee</t>
+          <t>French Roast - Herbal Coffee</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -2318,17 +2323,17 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>65020</t>
+          <t>62050</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>795239650200</t>
+          <t>795239620500</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chaga Ashwagandha Butterscotch Cream - Herbal Coffee</t>
+          <t>Gingerbread Chicory - Herbal Coffee</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -2337,26 +2342,26 @@
         </is>
       </c>
       <c r="E74" s="6" t="n">
-        <v>114.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>126.49</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>63220</t>
+          <t>60060</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>795239632206</t>
+          <t>795239600601</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dandelion Caramel Nut - Herbal Coffee</t>
+          <t>Hazelnut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -2365,26 +2370,26 @@
         </is>
       </c>
       <c r="E75" s="6" t="n">
-        <v>114.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>126.49</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>63340</t>
+          <t>60070</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>795239633401</t>
+          <t>795239600700</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dandelion Coconut - Herbal Coffee</t>
+          <t>Java - Herbal Coffee</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -2393,26 +2398,26 @@
         </is>
       </c>
       <c r="E76" s="6" t="n">
-        <v>114.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>126.49</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>63110</t>
+          <t>60130</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>795239631100</t>
+          <t>795239601301</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dandelion Dark Roast - Herbal Coffee</t>
+          <t>Maca Chocolate - Herbal Coffee</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -2421,26 +2426,26 @@
         </is>
       </c>
       <c r="E77" s="6" t="n">
-        <v>114.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>126.49</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>63080</t>
+          <t>62060</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>795239630806</t>
+          <t>795239620609</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dandelion Mocha - Herbal Coffee</t>
+          <t>Maple Pecan - Herbal Coffee</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -2449,26 +2454,26 @@
         </is>
       </c>
       <c r="E78" s="6" t="n">
-        <v>114.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>126.49</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>63310</t>
+          <t>60120</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>795239633104</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Dandelion Mocha Mint - Herbal Coffee</t>
+          <t>795239601202</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>Maya Chai - Herbal Coffee (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -2477,26 +2482,26 @@
         </is>
       </c>
       <c r="E79" s="6" t="n">
-        <v>114.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>126.49</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>63010</t>
+          <t>60080</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>795239630103</t>
+          <t>795239600809</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dandelion Vanilla Nut - Herbal Coffee</t>
+          <t>Mocha - Herbal Coffee</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -2505,26 +2510,26 @@
         </is>
       </c>
       <c r="E80" s="6" t="n">
-        <v>114.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>126.49</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>65010</t>
+          <t>62010</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>795239650101</t>
+          <t>795239620104</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Reishi Eleuthero French Roast Mushroom - Herbal Coffee</t>
+          <t>Pumpkin Spice - Herbal Coffee</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -2533,26 +2538,26 @@
         </is>
       </c>
       <c r="E81" s="6" t="n">
-        <v>114.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>126.49</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>65050</t>
+          <t>62040</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>795239650507</t>
+          <t>795239620401</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Turkey Tail Astragalus Toasted Maple - Herbal Coffee</t>
+          <t>Snickerdoodle Chicory - Herbal Coffee</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -2561,26 +2566,26 @@
         </is>
       </c>
       <c r="E82" s="6" t="n">
-        <v>114.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>126.49</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>66010</t>
+          <t>60010</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>795239660100</t>
+          <t>795239600106</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dark Chocolate - Herbal Coffee</t>
+          <t>Vanilla Nut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -2589,338 +2594,338 @@
         </is>
       </c>
       <c r="E83" s="6" t="n">
-        <v>139.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>153.99</v>
-      </c>
-    </row>
-    <row r="85" ht="22" customHeight="1">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>Item #</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>UPC:</t>
-        </is>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>Trial Size Packets:</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>Packaging Size:</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>Unit Price:</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t>MSRP:</t>
-        </is>
+        <v>98.98999999999999</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>65020</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>795239650200</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Chaga Ashwagandha Butterscotch Cream - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>5lb bag</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="n">
+        <v>114.99</v>
+      </c>
+      <c r="F84" s="6" t="n">
+        <v>126.49</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>63220</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>795239632206</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Dandelion Caramel Nut - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>5lb bag</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="n">
+        <v>114.99</v>
+      </c>
+      <c r="F85" s="6" t="n">
+        <v>126.49</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>52030</t>
+          <t>63340</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>795239520305</t>
+          <t>795239633401</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Southern Pecan - Herbal Coffee</t>
+          <t>Dandelion Coconut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E86" s="6" t="n">
-        <v>1.43</v>
+        <v>114.99</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>1.99</v>
+        <v>126.49</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>50030</t>
+          <t>63110</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>795239500307</t>
+          <t>795239631100</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Almond Amaretto - Herbal Coffee</t>
+          <t>Dandelion Dark Roast - Herbal Coffee</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E87" s="6" t="n">
-        <v>3.5</v>
+        <v>114.99</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>3.99</v>
+        <v>126.49</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>50020</t>
+          <t>63080</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>795239500208</t>
+          <t>795239630806</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chocolate Mint - Herbal Coffee</t>
+          <t>Dandelion Mocha - Herbal Coffee</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E88" s="6" t="n">
-        <v>3.5</v>
+        <v>114.99</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>3.99</v>
+        <v>126.49</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>50110</t>
+          <t>63310</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>795239501106</t>
+          <t>795239633104</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>French Roast - Herbal Coffee</t>
+          <t>Dandelion Mocha Mint - Herbal Coffee</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E89" s="6" t="n">
-        <v>3.5</v>
+        <v>114.99</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>3.99</v>
+        <v>126.49</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>52050</t>
+          <t>63010</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>795239520503</t>
+          <t>795239630103</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Gingerbread Chicory - Herbal Coffee</t>
+          <t>Dandelion Vanilla Nut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E90" s="6" t="n">
-        <v>3.5</v>
+        <v>114.99</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>3.99</v>
+        <v>126.49</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>50060</t>
+          <t>65010</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>795239500604</t>
+          <t>795239650101</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hazelnut - Herbal Coffee</t>
+          <t>Reishi Eleuthero French Roast Mushroom - Herbal Coffee</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E91" s="6" t="n">
-        <v>3.5</v>
+        <v>114.99</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>3.99</v>
+        <v>126.49</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>50070</t>
+          <t>65050</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>795239500703</t>
+          <t>795239650507</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Java - Herbal Coffee</t>
+          <t>Turkey Tail Astragalus Toasted Maple - Herbal Coffee</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E92" s="6" t="n">
-        <v>3.5</v>
+        <v>114.99</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>3.99</v>
+        <v>126.49</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>50130</t>
+          <t>66010</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>795239501304</t>
+          <t>795239660100</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Maca Chocolate - Herbal Coffee</t>
+          <t>Dark Chocolate - Herbal Coffee</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>1.05oz packet</t>
+          <t>5lb bag</t>
         </is>
       </c>
       <c r="E93" s="6" t="n">
-        <v>3.5</v>
+        <v>139.99</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>52060</t>
-        </is>
-      </c>
-      <c r="B94" s="5" t="inlineStr">
-        <is>
-          <t>795239520602</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Maple Pecan - Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
-        <is>
-          <t>1.05oz packet</t>
-        </is>
-      </c>
-      <c r="E94" s="6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F94" s="6" t="n">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>50080</t>
-        </is>
-      </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>795239500802</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Mocha - Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t>1.05oz packet</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F95" s="6" t="n">
-        <v>3.99</v>
+        <v>153.99</v>
+      </c>
+    </row>
+    <row r="95" ht="22" customHeight="1">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>Item #</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>UPC:</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>Trial Size Packets:</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>Packaging Size:</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>Unit Price:</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>MSRP:</t>
+        </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>52010</t>
+          <t>52030</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>795239520107</t>
+          <t>795239520305</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Pumpkin Spice - Herbal Coffee</t>
+          <t>Southern Pecan - Herbal Coffee</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
@@ -2929,26 +2934,26 @@
         </is>
       </c>
       <c r="E96" s="6" t="n">
-        <v>3.5</v>
+        <v>1.43</v>
       </c>
       <c r="F96" s="6" t="n">
-        <v>3.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>52040</t>
+          <t>50030</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>795239520404</t>
+          <t>795239500307</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Snickerdoodle Chicory - Herbal Coffee</t>
+          <t>Almond Amaretto - Herbal Coffee</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
@@ -2966,17 +2971,17 @@
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>50010</t>
+          <t>50040</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>795239500109</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Vanilla Nut - Herbal Coffee</t>
+          <t>795239500406</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>Blood Orange - Herbal Coffee (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -2994,17 +2999,17 @@
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>53220</t>
+          <t>52020</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>795239532209</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Dandelion Caramel Nut - Herbal Coffee</t>
+          <t>795239520206</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>Caramel Nut - Herbal Coffee (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
@@ -3013,26 +3018,26 @@
         </is>
       </c>
       <c r="E99" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F99" s="6" t="n">
         <v>3.99</v>
-      </c>
-      <c r="F99" s="6" t="n">
-        <v>4.49</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>53340</t>
+          <t>50020</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>795239533404</t>
+          <t>795239500208</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Dandelion Coconut - Herbal Coffee</t>
+          <t>Chocolate Mint - Herbal Coffee</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
@@ -3041,26 +3046,26 @@
         </is>
       </c>
       <c r="E100" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F100" s="6" t="n">
         <v>3.99</v>
-      </c>
-      <c r="F100" s="6" t="n">
-        <v>4.49</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>53110</t>
+          <t>52120</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>795239531103</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Dandelion Dark Roast - Herbal Coffee</t>
+          <t>795239521203</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>Chocolate Raspberry Chicory - Sampler (APG) (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
@@ -3069,26 +3074,26 @@
         </is>
       </c>
       <c r="E101" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F101" s="6" t="n">
         <v>3.99</v>
-      </c>
-      <c r="F101" s="6" t="n">
-        <v>4.49</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>53080</t>
+          <t>50110</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>795239530809</t>
+          <t>795239501106</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Dandelion Mocha - Herbal Coffee</t>
+          <t>French Roast - Herbal Coffee</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
@@ -3097,26 +3102,26 @@
         </is>
       </c>
       <c r="E102" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F102" s="6" t="n">
         <v>3.99</v>
-      </c>
-      <c r="F102" s="6" t="n">
-        <v>4.49</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>53310</t>
+          <t>52110</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>795239533107</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Dandelion Mocha Mint - Herbal Coffee</t>
+          <t>795239521104</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>French Vanilla Chicory - Sampler (APG) (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
@@ -3125,26 +3130,26 @@
         </is>
       </c>
       <c r="E103" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F103" s="6" t="n">
         <v>3.99</v>
-      </c>
-      <c r="F103" s="6" t="n">
-        <v>4.49</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>53010</t>
+          <t>52050</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>795239530106</t>
+          <t>795239520503</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Dandelion Vanilla Nut - Herbal Coffee</t>
+          <t>Gingerbread Chicory - Herbal Coffee</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
@@ -3153,26 +3158,26 @@
         </is>
       </c>
       <c r="E104" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F104" s="6" t="n">
         <v>3.99</v>
-      </c>
-      <c r="F104" s="6" t="n">
-        <v>4.49</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>53360</t>
+          <t>50060</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>795239533503</t>
+          <t>795239500604</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Holiday Eggnog - Herbal Coffee</t>
+          <t>Hazelnut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
@@ -3181,26 +3186,26 @@
         </is>
       </c>
       <c r="E105" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F105" s="6" t="n">
         <v>3.99</v>
-      </c>
-      <c r="F105" s="6" t="n">
-        <v>4.49</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>55020</t>
+          <t>50070</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>795239550203</t>
+          <t>795239500703</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chaga Ashwagandha Butterscotch Cream - Herbal Coffee</t>
+          <t>Java - Herbal Coffee</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
@@ -3209,26 +3214,26 @@
         </is>
       </c>
       <c r="E106" s="6" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="F106" s="6" t="n">
-        <v>4.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>56010</t>
+          <t>50130</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>795239560103</t>
+          <t>795239501304</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Dark Chocolate - Herbal Coffee</t>
+          <t>Maca Chocolate - Herbal Coffee</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
@@ -3237,26 +3242,26 @@
         </is>
       </c>
       <c r="E107" s="6" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>4.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>55030</t>
+          <t>52060</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>795239550302</t>
+          <t>795239520602</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Lion's Mane Rhodiola Rose Mushroom - Herbal Coffee</t>
+          <t>Maple Pecan - Herbal Coffee</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
@@ -3265,26 +3270,26 @@
         </is>
       </c>
       <c r="E108" s="6" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="F108" s="6" t="n">
-        <v>4.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>55010</t>
+          <t>50120</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>795239550104</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Reishi Eleuthero French Roast Mushroom - Herbal Coffee</t>
+          <t>795239501205</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>Maya Chai Chicory - Sampler (APG) (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
@@ -3293,26 +3298,26 @@
         </is>
       </c>
       <c r="E109" s="6" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>4.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>55050</t>
+          <t>50080</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>795239550500</t>
+          <t>795239500802</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Turkey Tail Astragalus Toasted Maple - Herbal Coffee</t>
+          <t>Mocha - Herbal Coffee</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
@@ -3321,491 +3326,1107 @@
         </is>
       </c>
       <c r="E110" s="6" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="F110" s="6" t="n">
-        <v>4.49</v>
-      </c>
-    </row>
-    <row r="112" ht="22" customHeight="1">
-      <c r="A112" s="3" t="inlineStr">
-        <is>
-          <t>Item #</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>UPC:</t>
-        </is>
-      </c>
-      <c r="C112" s="4" t="inlineStr">
-        <is>
-          <t>Instant Herbal Coffee:</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>Packaging Size:</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>Unit Price:</t>
-        </is>
-      </c>
-      <c r="F112" s="3" t="inlineStr">
-        <is>
-          <t>MSRP:</t>
-        </is>
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>50140</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>795239501403</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>Original - Herbal Coffee (DISCONTINUED)</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>1.05oz packet</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F111" s="6" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>52010</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>795239520107</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Pumpkin Spice - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>1.05oz packet</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F112" s="6" t="n">
+        <v>3.99</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>30008</t>
+          <t>52040</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>795239300082</t>
+          <t>795239520404</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>French Roast - Instant Herbal Coffee</t>
+          <t>Snickerdoodle Chicory - Herbal Coffee</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>3.53oz bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E113" s="6" t="n">
-        <v>16.99</v>
+        <v>3.5</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>18.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>30010</t>
+          <t>50010</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>795239300105</t>
+          <t>795239500109</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Hazelnut - Instant Herbal Coffee</t>
+          <t>Vanilla Nut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>3.53oz bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E114" s="6" t="n">
-        <v>16.99</v>
+        <v>3.5</v>
       </c>
       <c r="F114" s="6" t="n">
-        <v>18.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>30011</t>
+          <t>53220</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>795239300112</t>
+          <t>795239532209</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Mocha - Instant Herbal Coffee</t>
+          <t>Dandelion Caramel Nut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>3.53oz bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E115" s="6" t="n">
-        <v>16.99</v>
+        <v>3.99</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>18.49</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>30009</t>
+          <t>53340</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>795239300099</t>
+          <t>795239533404</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Vanilla Nut - Instant Herbal Coffee</t>
+          <t>Dandelion Coconut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>3.53oz bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E116" s="6" t="n">
-        <v>16.99</v>
+        <v>3.99</v>
       </c>
       <c r="F116" s="6" t="n">
-        <v>18.49</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>30007</t>
+          <t>53110</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>795239300075</t>
+          <t>795239531103</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Adapt &amp; Protect - Instant Herbal Coffee</t>
+          <t>Dandelion Dark Roast - Herbal Coffee</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>3.95oz bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E117" s="6" t="n">
-        <v>22.99</v>
+        <v>3.99</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>25.49</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>30005</t>
+          <t>53080</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>795239300051</t>
+          <t>795239530809</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Dandelion - Instant Herbal Coffee</t>
+          <t>Dandelion Mocha - Herbal Coffee</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>3.53oz bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E118" s="6" t="n">
-        <v>29.99</v>
+        <v>3.99</v>
       </c>
       <c r="F118" s="6" t="n">
-        <v>32.99</v>
-      </c>
-    </row>
-    <row r="120" ht="22" customHeight="1">
-      <c r="A120" s="3" t="inlineStr">
-        <is>
-          <t>Item #</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>UPC:</t>
-        </is>
-      </c>
-      <c r="C120" s="4" t="inlineStr">
-        <is>
-          <t>Instant Herbal Lattes:</t>
-        </is>
-      </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>Packaging Size:</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>Unit Price:</t>
-        </is>
-      </c>
-      <c r="F120" s="3" t="inlineStr">
-        <is>
-          <t>MSRP:</t>
-        </is>
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>53310</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>795239533107</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Dandelion Mocha Mint - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>1.05oz packet</t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="F119" s="6" t="n">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>53350</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>795239533503</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
+        <is>
+          <t>Dandelion Passionfruit Peach - Sampler (APG) (DISCONTINUED)</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>1.05oz packet</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="F120" s="6" t="n">
+        <v>4.49</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>31008</t>
+          <t>53320</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>795239310081</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>French Roast - Instant Herbal Latte</t>
+          <t>795239533206</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="inlineStr">
+        <is>
+          <t>Dandelion Red Chai - Sampler (APG) (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>7.9oz bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E121" s="6" t="n">
-        <v>21.99</v>
+        <v>3.99</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>23.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>31010</t>
+          <t>53010</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>795239310104</t>
+          <t>795239530106</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Hazelnut - Instant Herbal Latte</t>
+          <t>Dandelion Vanilla Nut - Herbal Coffee</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>7.9oz bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E122" s="6" t="n">
-        <v>21.99</v>
+        <v>3.99</v>
       </c>
       <c r="F122" s="6" t="n">
-        <v>23.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>31011</t>
+          <t>53360</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>795239310111</t>
+          <t>795239533503</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Mocha - Instant Herbal Latte</t>
+          <t>Holiday Eggnog - Herbal Coffee</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>7.9oz bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E123" s="6" t="n">
-        <v>21.99</v>
+        <v>3.99</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>23.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>31009</t>
+          <t>55020</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>795239310098</t>
+          <t>795239550203</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Vanilla Nut - Instant Herbal Latte</t>
+          <t>Chaga Ashwagandha Butterscotch Cream - Herbal Coffee</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>7.9oz bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E124" s="6" t="n">
-        <v>21.99</v>
+        <v>4</v>
       </c>
       <c r="F124" s="6" t="n">
-        <v>23.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>30013</t>
+          <t>55040</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>795239300136</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Cacao + 5 - Instant Herbal Coffee</t>
+          <t>795239550401</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>Cordyceps Schisandra Cinnamon Berry Mushroom - Herbal Coffee (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>4.76oz bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E125" s="6" t="n">
-        <v>22.99</v>
+        <v>4</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>25.49</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>31007</t>
+          <t>56010</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>795239310074</t>
+          <t>795239560103</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Adapt &amp; Protect - Instant Herbal Latte</t>
+          <t>Dark Chocolate - Herbal Coffee</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>7.9oz bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E126" s="6" t="n">
-        <v>24.99</v>
+        <v>4</v>
       </c>
       <c r="F126" s="6" t="n">
-        <v>27.49</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>31005</t>
+          <t>55030</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>795239310050</t>
+          <t>795239550302</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Dandelion - Instant Herbal Latte</t>
+          <t>Lion's Mane Rhodiola Rose Mushroom - Herbal Coffee</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>7.9oz bag</t>
+          <t>1.05oz packet</t>
         </is>
       </c>
       <c r="E127" s="6" t="n">
-        <v>24.99</v>
+        <v>4</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>27.49</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
+          <t>56020</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>795239560202</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="inlineStr">
+        <is>
+          <t>Macadamia Nut Prebiotic SuperBoost - Herbal Coffee (DISCONTINUED)</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>1.05oz packet</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F128" s="6" t="n">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>56030</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>795239560301</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="inlineStr">
+        <is>
+          <t>Mango Lemon Balm Prebiotic SuperBoost - Herbal Coffee (DISCONTINUED)</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>1.05oz packet</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F129" s="6" t="n">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>55010</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>795239550104</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Reishi Eleuthero French Roast Mushroom - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>1.05oz packet</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F130" s="6" t="n">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>55060</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>795239550609</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t>Tremella Tulsi Cardamom Mushroom - Herbal Coffee (DISCONTINUED)</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>1.05oz packet</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F131" s="6" t="n">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>55050</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>795239550500</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Turkey Tail Astragalus Toasted Maple - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>1.05oz packet</t>
+        </is>
+      </c>
+      <c r="E132" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F132" s="6" t="n">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="134" ht="22" customHeight="1">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>Item #</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>UPC:</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>Instant Herbal Coffee:</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>Packaging Size:</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>Unit Price:</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>MSRP:</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>30008</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>795239300082</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>French Roast - Instant Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>3.53oz bag</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="F135" s="6" t="n">
+        <v>18.49</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>30010</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>795239300105</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Hazelnut - Instant Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>3.53oz bag</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="F136" s="6" t="n">
+        <v>18.49</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>30011</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>795239300112</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Mocha - Instant Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>3.53oz bag</t>
+        </is>
+      </c>
+      <c r="E137" s="6" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="F137" s="6" t="n">
+        <v>18.49</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>30009</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>795239300099</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Vanilla Nut - Instant Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>3.53oz bag</t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="F138" s="6" t="n">
+        <v>18.49</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>30007</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>795239300075</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Adapt &amp; Protect - Instant Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>3.95oz bag</t>
+        </is>
+      </c>
+      <c r="E139" s="6" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="F139" s="6" t="n">
+        <v>25.49</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>30005</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>795239300051</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Dandelion - Instant Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>3.53oz bag</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="F140" s="6" t="n">
+        <v>32.99</v>
+      </c>
+    </row>
+    <row r="142" ht="22" customHeight="1">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>Item #</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>UPC:</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>Instant Herbal Lattes:</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>Packaging Size:</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>Unit Price:</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>MSRP:</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>31008</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>795239310081</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>French Roast - Instant Herbal Latte</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>7.9oz bag</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="F143" s="6" t="n">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>31010</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>795239310104</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Hazelnut - Instant Herbal Latte</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>7.9oz bag</t>
+        </is>
+      </c>
+      <c r="E144" s="6" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="F144" s="6" t="n">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>31011</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>795239310111</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Mocha - Instant Herbal Latte</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>7.9oz bag</t>
+        </is>
+      </c>
+      <c r="E145" s="6" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="F145" s="6" t="n">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>31009</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>795239310098</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Vanilla Nut - Instant Herbal Latte</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>7.9oz bag</t>
+        </is>
+      </c>
+      <c r="E146" s="6" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="F146" s="6" t="n">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>30013</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>795239300136</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Cacao + 5 - Instant Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>4.76oz bag</t>
+        </is>
+      </c>
+      <c r="E147" s="6" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="F147" s="6" t="n">
+        <v>25.49</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>31007</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>795239310074</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Adapt &amp; Protect - Instant Herbal Latte</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="inlineStr">
+        <is>
+          <t>7.9oz bag</t>
+        </is>
+      </c>
+      <c r="E148" s="6" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="F148" s="6" t="n">
+        <v>27.49</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>31005</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>795239310050</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Dandelion - Instant Herbal Latte</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>7.9oz bag</t>
+        </is>
+      </c>
+      <c r="E149" s="6" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="F149" s="6" t="n">
+        <v>27.49</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr">
+        <is>
           <t>31014</t>
         </is>
       </c>
-      <c r="B128" s="5" t="inlineStr">
+      <c r="B150" s="5" t="inlineStr">
         <is>
           <t>795239310142</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C150" t="inlineStr">
         <is>
           <t>Matcha Latte - Instant Herbal Latte</t>
         </is>
       </c>
-      <c r="D128" s="5" t="inlineStr">
+      <c r="D150" s="5" t="inlineStr">
         <is>
           <t>8.9oz bag</t>
         </is>
       </c>
-      <c r="E128" s="6" t="n">
+      <c r="E150" s="6" t="n">
         <v>29.99</v>
       </c>
-      <c r="F128" s="6" t="n">
+      <c r="F150" s="6" t="n">
         <v>35.49</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="7" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="8" t="inlineStr">
         <is>
           <t>Copies of All Certifications Available Upon Request</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="7" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="8" t="inlineStr">
         <is>
           <t>All prices are FOB, Oxnard, California USA with no minimum.</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="7" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="8" t="inlineStr">
         <is>
           <t>Order lead time - 5 business days</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="8" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="9" t="inlineStr">
         <is>
           <t>Teeccino Caffé, Inc.  |  P: (800) 498-3434  |  F: (805) 966-0522  |  sales@teeccino.com  |  teeccino.com</t>
         </is>
@@ -3813,12 +4434,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A132:F132"/>
-    <mergeCell ref="A133:F133"/>
+    <mergeCell ref="A155:F155"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A135:F135"/>
-    <mergeCell ref="A131:F131"/>
+    <mergeCell ref="A157:F157"/>
+    <mergeCell ref="A153:F153"/>
+    <mergeCell ref="A154:F154"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToWidth="1"/>
@@ -3832,15 +4453,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A8:F92"/>
+  <dimension ref="A8:F100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.4" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="53.5" customWidth="1" min="3" max="3"/>
-    <col width="20.5" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="19.6" customWidth="1" min="6" max="6"/>
+    <col width="15.6" customWidth="1" min="2" max="2"/>
+    <col width="76" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12.4" customWidth="1" min="5" max="5"/>
+    <col width="15.6" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1"/>
@@ -4377,17 +4998,17 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>45050</t>
+          <t>45060</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>795239450503</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Turkey Tail Astragalus Toasted Maple Mushroom - Herbal Tea</t>
+          <t>795239450602</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Tremella Tulsi Cardamom Mushroom - Herbal Tea (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -4405,17 +5026,17 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>45070</t>
+          <t>45050</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>795239450701</t>
+          <t>795239450503</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Adapt &amp; Protect - Herbal Tea</t>
+          <t>Turkey Tail Astragalus Toasted Maple Mushroom - Herbal Tea</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -4424,28 +5045,26 @@
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>10.49</v>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>9.99</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>10.99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>46010</t>
+          <t>45070</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>795239460106</t>
+          <t>795239450701</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dark Chocolate Prebiotic SuperBoost - Herbal Tea</t>
+          <t>Adapt &amp; Protect - Herbal Tea</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -4454,26 +5073,28 @@
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="F30" s="6" t="n">
-        <v>11.99</v>
+        <v>10.49</v>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>46020</t>
+          <t>46010</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>795239460205</t>
+          <t>795239460106</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Macadamia Nut Prebiotic SuperBoost - Herbal Tea</t>
+          <t>Dark Chocolate Prebiotic SuperBoost - Herbal Tea</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -4488,108 +5109,108 @@
         <v>11.99</v>
       </c>
     </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>46020</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>795239460205</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Macadamia Nut Prebiotic SuperBoost - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>10ct box</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>46030</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>795239460304</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Mango Lemon Balm Prebiotic SuperBoost - Herbal Tea (DISCONTINUED)</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>10ct box</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>Item #</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>UPC:</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>12ct Tea Bag Boxes:</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Packaging Size:</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>Unit Price:</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>MSRP:</t>
         </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>40001</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>795239400010</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Classic - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>12ct box</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="F34" s="6" t="n">
-        <v>12.99</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>12251</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>795239122516</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Holiday Tea - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>12ct box</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="F35" s="6" t="n">
-        <v>13.49</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>43001</t>
+          <t>40001</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>795239430017</t>
+          <t>795239400010</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dandelion - Herbal Tea</t>
+          <t>Classic - Herbal Tea</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -4598,26 +5219,26 @@
         </is>
       </c>
       <c r="E36" s="6" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="F36" s="6" t="n">
         <v>12.99</v>
-      </c>
-      <c r="F36" s="6" t="n">
-        <v>13.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>45001</t>
+          <t>12251</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>795239450015</t>
+          <t>795239122516</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mushroom Adaptogen - Herbal Tea</t>
+          <t>Holiday Tea - Herbal Tea</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -4626,142 +5247,142 @@
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>12.99</v>
+        <v>11.99</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>13.99</v>
+        <v>13.49</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>46001</t>
+          <t>43001</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>795239460014</t>
+          <t>795239430017</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Prebiotic Superboost - Herbal Tea</t>
+          <t>Dandelion - Herbal Tea</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>12ct</t>
+          <t>12ct box</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
         <v>12.99</v>
       </c>
       <c r="F38" s="6" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>45001</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>795239450015</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Mushroom Adaptogen - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>12ct box</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>46001</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>795239460014</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Prebiotic Superboost - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>12ct</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="F40" s="6" t="n">
         <v>14.49</v>
       </c>
     </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>Item #</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>UPC:</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>25ct Tea Bag Boxes:</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Packaging Size:</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>Unit Price:</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>MSRP:</t>
         </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>40031</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>795239400317</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Almond Amaretto - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>25ct box</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="n">
-        <v>16.99</v>
-      </c>
-      <c r="F41" s="6" t="n">
-        <v>18.49</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>40041</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>795239400416</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Blood Orange - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>25ct box</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="n">
-        <v>16.99</v>
-      </c>
-      <c r="F42" s="6" t="n">
-        <v>18.49</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>40021</t>
+          <t>40031</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>795239400218</t>
+          <t>795239400317</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chocolate Peppermint - Herbal Tea</t>
+          <t>Almond Amaretto - Herbal Tea</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -4779,17 +5400,17 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>40061</t>
+          <t>40041</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>795239400614</t>
+          <t>795239400416</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hazelnut - Herbal Tea</t>
+          <t>Blood Orange - Herbal Tea</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -4807,22 +5428,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>42081</t>
+          <t>42021</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>795239420810</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Irish Cream - Herbal Tea</t>
+          <t>795239420216</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Caramel Nut - Herbal Tea (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>25ct</t>
+          <t>25ct box</t>
         </is>
       </c>
       <c r="E45" s="6" t="n">
@@ -4835,17 +5456,17 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>40071</t>
+          <t>40021</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>795239400713</t>
+          <t>795239400218</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Java - Herbal Tea</t>
+          <t>Chocolate Peppermint - Herbal Tea</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -4863,17 +5484,17 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>40132</t>
+          <t>40061</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>795239401321</t>
+          <t>795239400614</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Maca Chocolate - Herbal Tea</t>
+          <t>Hazelnut - Herbal Tea</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -4891,22 +5512,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>42061</t>
+          <t>42081</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>795239420612</t>
+          <t>795239420810</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Maple Pecan - Herbal Tea</t>
+          <t>Irish Cream - Herbal Tea</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>25ct box</t>
+          <t>25ct</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
@@ -4919,17 +5540,17 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>40131</t>
+          <t>40071</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>795239401314</t>
+          <t>795239400713</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Mexican Chocolate Chicory - Herbal Tea</t>
+          <t>Java - Herbal Tea</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -4947,17 +5568,17 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>42011</t>
+          <t>40132</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>795239420117</t>
+          <t>795239401321</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pumpkin Spice - Herbal Tea</t>
+          <t>Maca Chocolate - Herbal Tea</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -4975,17 +5596,17 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>42041</t>
+          <t>42061</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>795239420414</t>
+          <t>795239420612</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Snickerdoodle Chicory - Herbal Tea</t>
+          <t>Maple Pecan - Herbal Tea</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -5003,45 +5624,45 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>42071</t>
+          <t>40121</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>795239420711</t>
+          <t>795239401215</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Candy Cane Chicory - Herbal Tea</t>
+          <t>Maya Chai - Herbal Tea</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>25ct</t>
+          <t>25ct box</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>17.99</v>
+        <v>16.99</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>19.49</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>42121</t>
+          <t>40131</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>795239421213</t>
+          <t>795239401314</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chocolate Raspberry Chicory - Herbal Tea</t>
+          <t>Mexican Chocolate Chicory - Herbal Tea</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -5050,54 +5671,54 @@
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>17.99</v>
+        <v>16.99</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>19.49</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>40051</t>
+          <t>40141</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>795239420117</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>English Toffee - Herbal Tea</t>
+          <t>795239401413</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>Original - Herbal Tea (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>25ct box</t>
+          <t>25ct</t>
         </is>
       </c>
       <c r="E54" s="6" t="n">
-        <v>17.99</v>
+        <v>16.99</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>19.49</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>40111</t>
+          <t>42011</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>795239401116</t>
+          <t>795239420117</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>French Roast - Herbal Tea</t>
+          <t>Pumpkin Spice - Herbal Tea</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -5106,26 +5727,26 @@
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>17.99</v>
+        <v>16.99</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>19.49</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>42051</t>
+          <t>42041</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>795239420513</t>
+          <t>795239420414</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Gingerbread Chicory - Herbal Tea</t>
+          <t>Snickerdoodle Chicory - Herbal Tea</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -5134,31 +5755,31 @@
         </is>
       </c>
       <c r="E56" s="6" t="n">
-        <v>17.99</v>
+        <v>16.99</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>19.49</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>40081</t>
+          <t>42071</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>795239400812</t>
+          <t>795239420711</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Mocha - Herbal Tea</t>
+          <t>Candy Cane Chicory - Herbal Tea</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>25ct box</t>
+          <t>25ct</t>
         </is>
       </c>
       <c r="E57" s="6" t="n">
@@ -5171,17 +5792,17 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>40011</t>
+          <t>42121</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>795239400119</t>
+          <t>795239421213</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Vanilla Nut - Herbal Tea</t>
+          <t>Chocolate Raspberry Chicory - Herbal Tea</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -5199,17 +5820,17 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>42111</t>
+          <t>40051</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>795239421114</t>
+          <t>795239420117</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>French Vanilla - Herbal Tea</t>
+          <t>English Toffee - Herbal Tea</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -5218,26 +5839,26 @@
         </is>
       </c>
       <c r="E59" s="6" t="n">
-        <v>18.49</v>
+        <v>17.99</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>20.49</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>45021</t>
+          <t>40111</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>795239450213</t>
+          <t>795239401116</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chaga Ashwagandha Butterscotch Cream Mushroom - Herbal Tea</t>
+          <t>French Roast - Herbal Tea</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -5246,26 +5867,26 @@
         </is>
       </c>
       <c r="E60" s="6" t="n">
-        <v>18.99</v>
+        <v>17.99</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>20.99</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>43371</t>
+          <t>42051</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>795239433711</t>
+          <t>795239420513</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dandelion Blueberry Vanilla - Herbal Tea</t>
+          <t>Gingerbread Chicory - Herbal Tea</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -5274,26 +5895,26 @@
         </is>
       </c>
       <c r="E61" s="6" t="n">
-        <v>18.99</v>
+        <v>17.99</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>20.99</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>40081</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>795239431113</t>
+          <t>795239400812</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dandelion Dark Roast - Herbal Tea</t>
+          <t>Mocha - Herbal Tea</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -5302,26 +5923,26 @@
         </is>
       </c>
       <c r="E62" s="6" t="n">
-        <v>18.99</v>
+        <v>17.99</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>20.99</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>43081</t>
+          <t>40011</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>795239430819</t>
+          <t>795239400119</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dandelion Mocha - Herbal Tea</t>
+          <t>Vanilla Nut - Herbal Tea</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -5330,26 +5951,26 @@
         </is>
       </c>
       <c r="E63" s="6" t="n">
-        <v>18.99</v>
+        <v>17.99</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>20.99</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>43311</t>
+          <t>42111</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>795239433117</t>
+          <t>795239421114</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dandelion Mocha Mint - Herbal Tea</t>
+          <t>French Vanilla - Herbal Tea</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -5358,26 +5979,26 @@
         </is>
       </c>
       <c r="E64" s="6" t="n">
-        <v>18.99</v>
+        <v>18.49</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>20.99</v>
+        <v>20.49</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>43351</t>
+          <t>45021</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>795239433513</t>
+          <t>795239450213</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dandelion Passionfruit Peach - Herbal Tea</t>
+          <t>Chaga Ashwagandha Butterscotch Cream Mushroom - Herbal Tea</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -5395,17 +6016,17 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>43321</t>
+          <t>45041</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>795239433216</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Dandelion Red Chai - Herbal Tea</t>
+          <t>795239450411</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>Cordyceps Schisandra Cinnamon Berry Mushroom - Herbal Tea (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -5423,17 +6044,17 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>43331</t>
+          <t>43371</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>795239433315</t>
+          <t>795239433711</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dandelion Turmeric - Herbal Tea</t>
+          <t>Dandelion Blueberry Vanilla - Herbal Tea</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -5451,17 +6072,17 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>45011</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>795239450114</t>
+          <t>795239431113</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Reishi Eleuthero French Roast Mushroom - Herbal Tea</t>
+          <t>Dandelion Dark Roast - Herbal Tea</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -5479,17 +6100,17 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>45061</t>
+          <t>43081</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>795239450619</t>
+          <t>795239430819</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tremella Tulsi Cardamom Mushroom - Herbal Tea</t>
+          <t>Dandelion Mocha - Herbal Tea</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -5507,17 +6128,17 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>43221</t>
+          <t>43311</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>795239432219</t>
+          <t>795239433117</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dandelion Caramel Nut - Herbal Tea</t>
+          <t>Dandelion Mocha Mint - Herbal Tea</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -5526,26 +6147,26 @@
         </is>
       </c>
       <c r="E70" s="6" t="n">
-        <v>19.99</v>
+        <v>18.99</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>21.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>43341</t>
+          <t>43351</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>795239433414</t>
+          <t>795239433513</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dandelion Coconut - Herbal Tea</t>
+          <t>Dandelion Passionfruit Peach - Herbal Tea</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -5554,26 +6175,26 @@
         </is>
       </c>
       <c r="E71" s="6" t="n">
-        <v>19.99</v>
+        <v>18.99</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>21.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>43011</t>
+          <t>43321</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>795239430116</t>
+          <t>795239433216</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dandelion Vanilla Nut - Herbal Tea</t>
+          <t>Dandelion Red Chai - Herbal Tea</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -5582,26 +6203,26 @@
         </is>
       </c>
       <c r="E72" s="6" t="n">
-        <v>19.99</v>
+        <v>18.99</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>21.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>43331</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>795239460113</t>
+          <t>795239433315</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dark Chocolate Prebiotic SuperBoost - Herbal Tea</t>
+          <t>Dandelion Turmeric - Herbal Tea</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -5610,54 +6231,54 @@
         </is>
       </c>
       <c r="E73" s="6" t="n">
-        <v>19.99</v>
+        <v>18.99</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>21.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>43361</t>
+          <t>45011</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>795239433612</t>
+          <t>795239450114</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Holiday Eggnog - Herbal Tea</t>
+          <t>Reishi Eleuthero French Roast Mushroom - Herbal Tea</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>25ct</t>
+          <t>25ct box</t>
         </is>
       </c>
       <c r="E74" s="6" t="n">
-        <v>19.99</v>
+        <v>18.99</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>21.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>45031</t>
+          <t>45061</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>795239450312</t>
+          <t>795239450619</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Lion's Mane Rhodiola Rose - Herbal Tea</t>
+          <t>Tremella Tulsi Cardamom Mushroom - Herbal Tea</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -5666,26 +6287,26 @@
         </is>
       </c>
       <c r="E75" s="6" t="n">
-        <v>19.99</v>
+        <v>18.99</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>21.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>45051</t>
+          <t>43221</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>795239450510</t>
+          <t>795239432219</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Turkey Tail Astragalus Toasted Maple Mushroom - Herbal Tea</t>
+          <t>Dandelion Caramel Nut - Herbal Tea</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -5703,254 +6324,478 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>45071</t>
+          <t>43341</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>795239450718</t>
+          <t>795239433414</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Adapt &amp; Protect - Herbal Tea</t>
+          <t>Dandelion Coconut - Herbal Tea</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>25ct</t>
+          <t>25ct box</t>
         </is>
       </c>
       <c r="E77" s="6" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="F77" s="6" t="n">
         <v>21.99</v>
       </c>
-      <c r="F77" s="6" t="n">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>Item #</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>UPC:</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>50ct Tagless Tea Bags:</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>Packaging Size:</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="inlineStr">
-        <is>
-          <t>Unit Price:</t>
-        </is>
-      </c>
-      <c r="F79" s="3" t="inlineStr">
-        <is>
-          <t>MSRP:</t>
-        </is>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>43011</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>795239430116</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Dandelion Vanilla Nut - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>25ct box</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>46011</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>795239460113</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Dark Chocolate Prebiotic SuperBoost - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>25ct box</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>21.99</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>40116</t>
+          <t>43361</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>795239433612</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>French Roast - Herbal Tea</t>
+          <t>Holiday Eggnog - Herbal Tea</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>50ct</t>
+          <t>25ct</t>
         </is>
       </c>
       <c r="E80" s="6" t="n">
-        <v>23.99</v>
+        <v>19.99</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>25.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>40066</t>
+          <t>45031</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>795239400669</t>
+          <t>795239450312</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hazelnut - Herbal Tea</t>
+          <t>Lion's Mane Rhodiola Rose - Herbal Tea</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>50ct</t>
+          <t>25ct box</t>
         </is>
       </c>
       <c r="E81" s="6" t="n">
-        <v>23.99</v>
+        <v>19.99</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>25.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>40086</t>
+          <t>46021</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Mocha - Herbal Tea</t>
+          <t>795239460212</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>Macadamia Nut Prebiotic SuperBoost - Herbal Tea (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>50ct</t>
+          <t>25ct box</t>
         </is>
       </c>
       <c r="E82" s="6" t="n">
-        <v>23.99</v>
+        <v>19.99</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>25.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>40016</t>
+          <t>46031</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Vanilla Nut - Herbal Tea</t>
+          <t>795239460311</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>Mango Lemon Balm Prebiotic SuperBoost - Herbal Tea (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>50ct</t>
+          <t>25ct box</t>
         </is>
       </c>
       <c r="E83" s="6" t="n">
-        <v>23.99</v>
+        <v>19.99</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>25.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>43226</t>
+          <t>45051</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>795239450510</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dandelion Caramel Nut - Herbal Tea</t>
+          <t>Turkey Tail Astragalus Toasted Maple Mushroom - Herbal Tea</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>50ct</t>
+          <t>25ct box</t>
         </is>
       </c>
       <c r="E84" s="6" t="n">
-        <v>32.99</v>
+        <v>19.99</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>36.49</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
+          <t>45071</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>795239450718</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Adapt &amp; Protect - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>25ct</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="F85" s="6" t="n">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>Item #</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>UPC:</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>50ct Tagless Tea Bags:</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>Packaging Size:</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>Unit Price:</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>MSRP:</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>40116</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>French Roast - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>50ct</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="F88" s="6" t="n">
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>40066</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>795239400669</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Hazelnut - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>50ct</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="F89" s="6" t="n">
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>40086</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Mocha - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>50ct</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="F90" s="6" t="n">
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>40016</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Vanilla Nut - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>50ct</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="F91" s="6" t="n">
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>43226</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Dandelion Caramel Nut - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>50ct</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="F92" s="6" t="n">
+        <v>36.49</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
           <t>43116</t>
         </is>
       </c>
-      <c r="B85" s="5" t="inlineStr">
+      <c r="B93" s="5" t="inlineStr">
         <is>
           <t>795239431168</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Dandelion Dark Roast - Herbal Tea</t>
         </is>
       </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>50ct</t>
         </is>
       </c>
-      <c r="E85" s="6" t="n">
+      <c r="E93" s="6" t="n">
         <v>32.99</v>
       </c>
-      <c r="F85" s="6" t="n">
+      <c r="F93" s="6" t="n">
         <v>36.49</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="7" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
         <is>
           <t>Copies of All Certifications Available Upon Request</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="7" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
         <is>
           <t>All prices are FOB, Oxnard, California USA with no minimum.</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="7" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
         <is>
           <t>Order lead time - 5 business days</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="8" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="9" t="inlineStr">
         <is>
           <t>Teeccino Caffé, Inc.  |  P: (800) 498-3434  |  F: (805) 966-0522  |  sales@teeccino.com  |  teeccino.com</t>
         </is>
@@ -5958,12 +6803,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A90:F90"/>
+    <mergeCell ref="A98:F98"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A89:F89"/>
-    <mergeCell ref="A88:F88"/>
-    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="A97:F97"/>
+    <mergeCell ref="A100:F100"/>
+    <mergeCell ref="A96:F96"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToWidth="1"/>
@@ -5981,11 +6826,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.4" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="53.5" customWidth="1" min="3" max="3"/>
-    <col width="20.5" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="19.6" customWidth="1" min="6" max="6"/>
+    <col width="15.6" customWidth="1" min="2" max="2"/>
+    <col width="76" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12.4" customWidth="1" min="5" max="5"/>
+    <col width="15.6" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1"/>
@@ -8540,28 +9385,28 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="7" t="inlineStr">
+      <c r="A115" s="8" t="inlineStr">
         <is>
           <t>Copies of All Certifications Available Upon Request</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="7" t="inlineStr">
+      <c r="A116" s="8" t="inlineStr">
         <is>
           <t>All prices are FOB, Oxnard, California USA with no minimum.</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="7" t="inlineStr">
+      <c r="A117" s="8" t="inlineStr">
         <is>
           <t>Order lead time - 5 business days</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="8" t="inlineStr">
+      <c r="A119" s="9" t="inlineStr">
         <is>
           <t>Teeccino Caffé, Inc.  |  P: (800) 498-3434  |  F: (805) 966-0522  |  sales@teeccino.com  |  teeccino.com</t>
         </is>

--- a/teeccino-retail-price-list-new-prices.xlsx
+++ b/teeccino-retail-price-list-new-prices.xlsx
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A8:F157"/>
+  <dimension ref="A8:F158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.4" customWidth="1" min="1" max="1"/>
@@ -3948,80 +3948,80 @@
         <v>4.49</v>
       </c>
     </row>
-    <row r="134" ht="22" customHeight="1">
-      <c r="A134" s="3" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>50094</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Six - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>1.05oz packet</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="F133" s="6" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="135" ht="22" customHeight="1">
+      <c r="A135" s="3" t="inlineStr">
         <is>
           <t>Item #</t>
         </is>
       </c>
-      <c r="B134" s="3" t="inlineStr">
+      <c r="B135" s="3" t="inlineStr">
         <is>
           <t>UPC:</t>
         </is>
       </c>
-      <c r="C134" s="4" t="inlineStr">
+      <c r="C135" s="4" t="inlineStr">
         <is>
           <t>Instant Herbal Coffee:</t>
         </is>
       </c>
-      <c r="D134" s="3" t="inlineStr">
+      <c r="D135" s="3" t="inlineStr">
         <is>
           <t>Packaging Size:</t>
         </is>
       </c>
-      <c r="E134" s="3" t="inlineStr">
+      <c r="E135" s="3" t="inlineStr">
         <is>
           <t>Unit Price:</t>
         </is>
       </c>
-      <c r="F134" s="3" t="inlineStr">
+      <c r="F135" s="3" t="inlineStr">
         <is>
           <t>MSRP:</t>
         </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="5" t="inlineStr">
-        <is>
-          <t>30008</t>
-        </is>
-      </c>
-      <c r="B135" s="5" t="inlineStr">
-        <is>
-          <t>795239300082</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>French Roast - Instant Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D135" s="5" t="inlineStr">
-        <is>
-          <t>3.53oz bag</t>
-        </is>
-      </c>
-      <c r="E135" s="6" t="n">
-        <v>16.99</v>
-      </c>
-      <c r="F135" s="6" t="n">
-        <v>18.49</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>30010</t>
+          <t>30008</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>795239300105</t>
+          <t>795239300082</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Hazelnut - Instant Herbal Coffee</t>
+          <t>French Roast - Instant Herbal Coffee</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
@@ -4039,17 +4039,17 @@
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>30011</t>
+          <t>30010</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>795239300112</t>
+          <t>795239300105</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Mocha - Instant Herbal Coffee</t>
+          <t>Hazelnut - Instant Herbal Coffee</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
@@ -4067,17 +4067,17 @@
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>30009</t>
+          <t>30011</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>795239300099</t>
+          <t>795239300112</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Vanilla Nut - Instant Herbal Coffee</t>
+          <t>Mocha - Instant Herbal Coffee</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
@@ -4095,133 +4095,133 @@
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>30007</t>
+          <t>30009</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>795239300075</t>
+          <t>795239300099</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Adapt &amp; Protect - Instant Herbal Coffee</t>
+          <t>Vanilla Nut - Instant Herbal Coffee</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>3.95oz bag</t>
+          <t>3.53oz bag</t>
         </is>
       </c>
       <c r="E139" s="6" t="n">
-        <v>22.99</v>
+        <v>16.99</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>25.49</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
+          <t>30007</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>795239300075</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Adapt &amp; Protect - Instant Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>3.95oz bag</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="F140" s="6" t="n">
+        <v>25.49</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
           <t>30005</t>
         </is>
       </c>
-      <c r="B140" s="5" t="inlineStr">
+      <c r="B141" s="5" t="inlineStr">
         <is>
           <t>795239300051</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
+      <c r="C141" t="inlineStr">
         <is>
           <t>Dandelion - Instant Herbal Coffee</t>
         </is>
       </c>
-      <c r="D140" s="5" t="inlineStr">
+      <c r="D141" s="5" t="inlineStr">
         <is>
           <t>3.53oz bag</t>
         </is>
       </c>
-      <c r="E140" s="6" t="n">
+      <c r="E141" s="6" t="n">
         <v>29.99</v>
       </c>
-      <c r="F140" s="6" t="n">
+      <c r="F141" s="6" t="n">
         <v>32.99</v>
       </c>
     </row>
-    <row r="142" ht="22" customHeight="1">
-      <c r="A142" s="3" t="inlineStr">
+    <row r="143" ht="22" customHeight="1">
+      <c r="A143" s="3" t="inlineStr">
         <is>
           <t>Item #</t>
         </is>
       </c>
-      <c r="B142" s="3" t="inlineStr">
+      <c r="B143" s="3" t="inlineStr">
         <is>
           <t>UPC:</t>
         </is>
       </c>
-      <c r="C142" s="4" t="inlineStr">
+      <c r="C143" s="4" t="inlineStr">
         <is>
           <t>Instant Herbal Lattes:</t>
         </is>
       </c>
-      <c r="D142" s="3" t="inlineStr">
+      <c r="D143" s="3" t="inlineStr">
         <is>
           <t>Packaging Size:</t>
         </is>
       </c>
-      <c r="E142" s="3" t="inlineStr">
+      <c r="E143" s="3" t="inlineStr">
         <is>
           <t>Unit Price:</t>
         </is>
       </c>
-      <c r="F142" s="3" t="inlineStr">
+      <c r="F143" s="3" t="inlineStr">
         <is>
           <t>MSRP:</t>
         </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="5" t="inlineStr">
-        <is>
-          <t>31008</t>
-        </is>
-      </c>
-      <c r="B143" s="5" t="inlineStr">
-        <is>
-          <t>795239310081</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>French Roast - Instant Herbal Latte</t>
-        </is>
-      </c>
-      <c r="D143" s="5" t="inlineStr">
-        <is>
-          <t>7.9oz bag</t>
-        </is>
-      </c>
-      <c r="E143" s="6" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F143" s="6" t="n">
-        <v>23.99</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>31010</t>
+          <t>31008</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>795239310104</t>
+          <t>795239310081</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Hazelnut - Instant Herbal Latte</t>
+          <t>French Roast - Instant Herbal Latte</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
@@ -4239,17 +4239,17 @@
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>31011</t>
+          <t>31010</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>795239310111</t>
+          <t>795239310104</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Mocha - Instant Herbal Latte</t>
+          <t>Hazelnut - Instant Herbal Latte</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
@@ -4267,17 +4267,17 @@
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>31009</t>
+          <t>31011</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>795239310098</t>
+          <t>795239310111</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Vanilla Nut - Instant Herbal Latte</t>
+          <t>Mocha - Instant Herbal Latte</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
@@ -4295,73 +4295,73 @@
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>30013</t>
+          <t>31009</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>795239300136</t>
+          <t>795239310098</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Cacao + 5 - Instant Herbal Coffee</t>
+          <t>Vanilla Nut - Instant Herbal Latte</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>4.76oz bag</t>
+          <t>7.9oz bag</t>
         </is>
       </c>
       <c r="E147" s="6" t="n">
-        <v>22.99</v>
+        <v>21.99</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>25.49</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>31007</t>
+          <t>30013</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>795239310074</t>
+          <t>795239300136</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Adapt &amp; Protect - Instant Herbal Latte</t>
+          <t>Cacao + 5 - Instant Herbal Coffee</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>7.9oz bag</t>
+          <t>4.76oz bag</t>
         </is>
       </c>
       <c r="E148" s="6" t="n">
-        <v>24.99</v>
+        <v>22.99</v>
       </c>
       <c r="F148" s="6" t="n">
-        <v>27.49</v>
+        <v>25.49</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>31005</t>
+          <t>31007</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>795239310050</t>
+          <t>795239310074</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Dandelion - Instant Herbal Latte</t>
+          <t>Adapt &amp; Protect - Instant Herbal Latte</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
@@ -4379,54 +4379,82 @@
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
+          <t>31005</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>795239310050</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Dandelion - Instant Herbal Latte</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>7.9oz bag</t>
+        </is>
+      </c>
+      <c r="E150" s="6" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="F150" s="6" t="n">
+        <v>27.49</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="inlineStr">
+        <is>
           <t>31014</t>
         </is>
       </c>
-      <c r="B150" s="5" t="inlineStr">
+      <c r="B151" s="5" t="inlineStr">
         <is>
           <t>795239310142</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
+      <c r="C151" t="inlineStr">
         <is>
           <t>Matcha Latte - Instant Herbal Latte</t>
         </is>
       </c>
-      <c r="D150" s="5" t="inlineStr">
+      <c r="D151" s="5" t="inlineStr">
         <is>
           <t>8.9oz bag</t>
         </is>
       </c>
-      <c r="E150" s="6" t="n">
+      <c r="E151" s="6" t="n">
         <v>29.99</v>
       </c>
-      <c r="F150" s="6" t="n">
+      <c r="F151" s="6" t="n">
         <v>35.49</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="8" t="inlineStr">
-        <is>
-          <t>Copies of All Certifications Available Upon Request</t>
-        </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="8" t="inlineStr">
         <is>
-          <t>All prices are FOB, Oxnard, California USA with no minimum.</t>
+          <t>Copies of All Certifications Available Upon Request</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
         <is>
+          <t>All prices are FOB, Oxnard, California USA with no minimum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="8" t="inlineStr">
+        <is>
           <t>Order lead time - 5 business days</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="9" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="9" t="inlineStr">
         <is>
           <t>Teeccino Caffé, Inc.  |  P: (800) 498-3434  |  F: (805) 966-0522  |  sales@teeccino.com  |  teeccino.com</t>
         </is>
@@ -4437,9 +4465,9 @@
     <mergeCell ref="A155:F155"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A157:F157"/>
-    <mergeCell ref="A153:F153"/>
+    <mergeCell ref="A158:F158"/>
     <mergeCell ref="A154:F154"/>
+    <mergeCell ref="A156:F156"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToWidth="1"/>
@@ -4453,7 +4481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A8:F100"/>
+  <dimension ref="A8:F102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.4" customWidth="1" min="1" max="1"/>
@@ -5372,17 +5400,17 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>40031</t>
+          <t>42031</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>795239400317</t>
+          <t>795239420315</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Almond Amaretto - Herbal Tea</t>
+          <t>Southern Pecan - Herbal Tea</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -5391,26 +5419,26 @@
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>16.99</v>
+        <v>15.99</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>18.49</v>
+        <v>16.49</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>40041</t>
+          <t>40031</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>795239400416</t>
+          <t>795239400317</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Blood Orange - Herbal Tea</t>
+          <t>Almond Amaretto - Herbal Tea</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -5428,17 +5456,17 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>42021</t>
+          <t>40041</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>795239420216</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>Caramel Nut - Herbal Tea (DISCONTINUED)</t>
+          <t>795239400416</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Blood Orange - Herbal Tea</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -5456,17 +5484,17 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>40021</t>
+          <t>42021</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>795239400218</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Chocolate Peppermint - Herbal Tea</t>
+          <t>795239420216</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Caramel Nut - Herbal Tea (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -5484,17 +5512,17 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>40061</t>
+          <t>40021</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>795239400614</t>
+          <t>795239400218</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hazelnut - Herbal Tea</t>
+          <t>Chocolate Peppermint - Herbal Tea</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -5512,22 +5540,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>42081</t>
+          <t>40061</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>795239420810</t>
+          <t>795239400614</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Irish Cream - Herbal Tea</t>
+          <t>Hazelnut - Herbal Tea</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>25ct</t>
+          <t>25ct box</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
@@ -5540,22 +5568,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>40071</t>
+          <t>42081</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>795239400713</t>
+          <t>795239420810</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Java - Herbal Tea</t>
+          <t>Irish Cream - Herbal Tea</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>25ct box</t>
+          <t>25ct</t>
         </is>
       </c>
       <c r="E49" s="6" t="n">
@@ -5568,17 +5596,17 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>40132</t>
+          <t>40071</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>795239401321</t>
+          <t>795239400713</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Maca Chocolate - Herbal Tea</t>
+          <t>Java - Herbal Tea</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -5596,17 +5624,17 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>42061</t>
+          <t>40132</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>795239420612</t>
+          <t>795239401321</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Maple Pecan - Herbal Tea</t>
+          <t>Maca Chocolate - Herbal Tea</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -5624,17 +5652,17 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>40121</t>
+          <t>42061</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>795239401215</t>
+          <t>795239420612</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Maya Chai - Herbal Tea</t>
+          <t>Maple Pecan - Herbal Tea</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -5652,17 +5680,17 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>40131</t>
+          <t>40121</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>795239401314</t>
+          <t>795239401215</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Mexican Chocolate Chicory - Herbal Tea</t>
+          <t>Maya Chai - Herbal Tea</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -5680,22 +5708,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>40141</t>
+          <t>40131</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>795239401413</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>Original - Herbal Tea (DISCONTINUED)</t>
+          <t>795239401314</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Mexican Chocolate Chicory - Herbal Tea</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>25ct</t>
+          <t>25ct box</t>
         </is>
       </c>
       <c r="E54" s="6" t="n">
@@ -5708,22 +5736,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>42011</t>
+          <t>40141</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>795239420117</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Pumpkin Spice - Herbal Tea</t>
+          <t>795239401413</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>Original - Herbal Tea (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>25ct box</t>
+          <t>25ct</t>
         </is>
       </c>
       <c r="E55" s="6" t="n">
@@ -5736,17 +5764,17 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>42041</t>
+          <t>42011</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>795239420414</t>
+          <t>795239420117</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Snickerdoodle Chicory - Herbal Tea</t>
+          <t>Pumpkin Spice - Herbal Tea</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -5764,50 +5792,50 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>42071</t>
+          <t>42041</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>795239420711</t>
+          <t>795239420414</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Candy Cane Chicory - Herbal Tea</t>
+          <t>Snickerdoodle Chicory - Herbal Tea</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>25ct</t>
+          <t>25ct box</t>
         </is>
       </c>
       <c r="E57" s="6" t="n">
-        <v>17.99</v>
+        <v>16.99</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>19.49</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>42121</t>
+          <t>42071</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>795239421213</t>
+          <t>795239420711</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chocolate Raspberry Chicory - Herbal Tea</t>
+          <t>Candy Cane Chicory - Herbal Tea</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>25ct box</t>
+          <t>25ct</t>
         </is>
       </c>
       <c r="E58" s="6" t="n">
@@ -5820,17 +5848,17 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>40051</t>
+          <t>42121</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>795239420117</t>
+          <t>795239421213</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>English Toffee - Herbal Tea</t>
+          <t>Chocolate Raspberry Chicory - Herbal Tea</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -5848,17 +5876,17 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>40111</t>
+          <t>40051</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>795239401116</t>
+          <t>795239420117</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>French Roast - Herbal Tea</t>
+          <t>English Toffee - Herbal Tea</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -5876,17 +5904,17 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>42051</t>
+          <t>40111</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>795239420513</t>
+          <t>795239401116</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Gingerbread Chicory - Herbal Tea</t>
+          <t>French Roast - Herbal Tea</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -5904,17 +5932,17 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>40081</t>
+          <t>42051</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>795239400812</t>
+          <t>795239420513</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Mocha - Herbal Tea</t>
+          <t>Gingerbread Chicory - Herbal Tea</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -5932,17 +5960,17 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>40011</t>
+          <t>40081</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>795239400119</t>
+          <t>795239400812</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Vanilla Nut - Herbal Tea</t>
+          <t>Mocha - Herbal Tea</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -5960,17 +5988,17 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>42111</t>
+          <t>40089</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>795239421114</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>French Vanilla - Herbal Tea</t>
+          <t>Raspberry Mocha - Herbal Tea</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -5979,26 +6007,26 @@
         </is>
       </c>
       <c r="E64" s="6" t="n">
-        <v>18.49</v>
+        <v>17.99</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>20.49</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>45021</t>
+          <t>40011</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>795239450213</t>
+          <t>795239400119</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chaga Ashwagandha Butterscotch Cream Mushroom - Herbal Tea</t>
+          <t>Vanilla Nut - Herbal Tea</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -6007,26 +6035,26 @@
         </is>
       </c>
       <c r="E65" s="6" t="n">
-        <v>18.99</v>
+        <v>17.99</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>20.99</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>45041</t>
+          <t>42111</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>795239450411</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="inlineStr">
-        <is>
-          <t>Cordyceps Schisandra Cinnamon Berry Mushroom - Herbal Tea (DISCONTINUED)</t>
+          <t>795239421114</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>French Vanilla - Herbal Tea</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -6035,26 +6063,26 @@
         </is>
       </c>
       <c r="E66" s="6" t="n">
-        <v>18.99</v>
+        <v>18.49</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>20.99</v>
+        <v>20.49</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>43371</t>
+          <t>45021</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>795239433711</t>
+          <t>795239450213</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dandelion Blueberry Vanilla - Herbal Tea</t>
+          <t>Chaga Ashwagandha Butterscotch Cream Mushroom - Herbal Tea</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -6072,17 +6100,17 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>45041</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>795239431113</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Dandelion Dark Roast - Herbal Tea</t>
+          <t>795239450411</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>Cordyceps Schisandra Cinnamon Berry Mushroom - Herbal Tea (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -6100,17 +6128,17 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>43081</t>
+          <t>43371</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>795239430819</t>
+          <t>795239433711</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dandelion Mocha - Herbal Tea</t>
+          <t>Dandelion Blueberry Vanilla - Herbal Tea</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -6128,17 +6156,17 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>43311</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>795239433117</t>
+          <t>795239431113</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dandelion Mocha Mint - Herbal Tea</t>
+          <t>Dandelion Dark Roast - Herbal Tea</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -6156,17 +6184,17 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>43351</t>
+          <t>43081</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>795239433513</t>
+          <t>795239430819</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dandelion Passionfruit Peach - Herbal Tea</t>
+          <t>Dandelion Mocha - Herbal Tea</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -6184,17 +6212,17 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>43321</t>
+          <t>43311</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>795239433216</t>
+          <t>795239433117</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dandelion Red Chai - Herbal Tea</t>
+          <t>Dandelion Mocha Mint - Herbal Tea</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -6212,17 +6240,17 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>43331</t>
+          <t>43351</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>795239433315</t>
+          <t>795239433513</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dandelion Turmeric - Herbal Tea</t>
+          <t>Dandelion Passionfruit Peach - Herbal Tea</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -6240,17 +6268,17 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>45011</t>
+          <t>43321</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>795239450114</t>
+          <t>795239433216</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Reishi Eleuthero French Roast Mushroom - Herbal Tea</t>
+          <t>Dandelion Red Chai - Herbal Tea</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -6268,17 +6296,17 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>45061</t>
+          <t>43331</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>795239450619</t>
+          <t>795239433315</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tremella Tulsi Cardamom Mushroom - Herbal Tea</t>
+          <t>Dandelion Turmeric - Herbal Tea</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -6296,17 +6324,17 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>43221</t>
+          <t>45011</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>795239432219</t>
+          <t>795239450114</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dandelion Caramel Nut - Herbal Tea</t>
+          <t>Reishi Eleuthero French Roast Mushroom - Herbal Tea</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -6315,26 +6343,26 @@
         </is>
       </c>
       <c r="E76" s="6" t="n">
-        <v>19.99</v>
+        <v>18.99</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>21.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>43341</t>
+          <t>45061</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>795239433414</t>
+          <t>795239450619</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dandelion Coconut - Herbal Tea</t>
+          <t>Tremella Tulsi Cardamom Mushroom - Herbal Tea</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -6343,26 +6371,26 @@
         </is>
       </c>
       <c r="E77" s="6" t="n">
-        <v>19.99</v>
+        <v>18.99</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>21.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>43011</t>
+          <t>43221</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>795239430116</t>
+          <t>795239432219</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dandelion Vanilla Nut - Herbal Tea</t>
+          <t>Dandelion Caramel Nut - Herbal Tea</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -6380,17 +6408,17 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>43341</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>795239460113</t>
+          <t>795239433414</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dark Chocolate Prebiotic SuperBoost - Herbal Tea</t>
+          <t>Dandelion Coconut - Herbal Tea</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -6408,22 +6436,22 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>43361</t>
+          <t>43011</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>795239433612</t>
+          <t>795239430116</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Holiday Eggnog - Herbal Tea</t>
+          <t>Dandelion Vanilla Nut - Herbal Tea</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>25ct</t>
+          <t>25ct box</t>
         </is>
       </c>
       <c r="E80" s="6" t="n">
@@ -6436,17 +6464,17 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>45031</t>
+          <t>46011</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>795239450312</t>
+          <t>795239460113</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Lion's Mane Rhodiola Rose - Herbal Tea</t>
+          <t>Dark Chocolate Prebiotic SuperBoost - Herbal Tea</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -6464,22 +6492,22 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>46021</t>
+          <t>43361</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>795239460212</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>Macadamia Nut Prebiotic SuperBoost - Herbal Tea (DISCONTINUED)</t>
+          <t>795239433612</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Holiday Eggnog - Herbal Tea</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>25ct box</t>
+          <t>25ct</t>
         </is>
       </c>
       <c r="E82" s="6" t="n">
@@ -6492,17 +6520,17 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>46031</t>
+          <t>45031</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>795239460311</t>
-        </is>
-      </c>
-      <c r="C83" s="7" t="inlineStr">
-        <is>
-          <t>Mango Lemon Balm Prebiotic SuperBoost - Herbal Tea (DISCONTINUED)</t>
+          <t>795239450312</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Lion's Mane Rhodiola Rose - Herbal Tea</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -6520,17 +6548,17 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>45051</t>
+          <t>46021</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>795239450510</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Turkey Tail Astragalus Toasted Maple Mushroom - Herbal Tea</t>
+          <t>795239460212</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>Macadamia Nut Prebiotic SuperBoost - Herbal Tea (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -6548,123 +6576,123 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
+          <t>46031</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>795239460311</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>Mango Lemon Balm Prebiotic SuperBoost - Herbal Tea (DISCONTINUED)</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>25ct box</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="F85" s="6" t="n">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>45051</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>795239450510</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Turkey Tail Astragalus Toasted Maple Mushroom - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>25ct box</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="F86" s="6" t="n">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
           <t>45071</t>
         </is>
       </c>
-      <c r="B85" s="5" t="inlineStr">
+      <c r="B87" s="5" t="inlineStr">
         <is>
           <t>795239450718</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>Adapt &amp; Protect - Herbal Tea</t>
         </is>
       </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D87" s="5" t="inlineStr">
         <is>
           <t>25ct</t>
         </is>
       </c>
-      <c r="E85" s="6" t="n">
+      <c r="E87" s="6" t="n">
         <v>21.99</v>
       </c>
-      <c r="F85" s="6" t="n">
+      <c r="F87" s="6" t="n">
         <v>23.99</v>
       </c>
     </row>
-    <row r="87" ht="22" customHeight="1">
-      <c r="A87" s="3" t="inlineStr">
+    <row r="89" ht="22" customHeight="1">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>Item #</t>
         </is>
       </c>
-      <c r="B87" s="3" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>UPC:</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>50ct Tagless Tea Bags:</t>
         </is>
       </c>
-      <c r="D87" s="3" t="inlineStr">
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>Packaging Size:</t>
         </is>
       </c>
-      <c r="E87" s="3" t="inlineStr">
+      <c r="E89" s="3" t="inlineStr">
         <is>
           <t>Unit Price:</t>
         </is>
       </c>
-      <c r="F87" s="3" t="inlineStr">
+      <c r="F89" s="3" t="inlineStr">
         <is>
           <t>MSRP:</t>
         </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>40116</t>
-        </is>
-      </c>
-      <c r="B88" s="5" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>French Roast - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="inlineStr">
-        <is>
-          <t>50ct</t>
-        </is>
-      </c>
-      <c r="E88" s="6" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="F88" s="6" t="n">
-        <v>25.99</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>40066</t>
-        </is>
-      </c>
-      <c r="B89" s="5" t="inlineStr">
-        <is>
-          <t>795239400669</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Hazelnut - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
-        <is>
-          <t>50ct</t>
-        </is>
-      </c>
-      <c r="E89" s="6" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="F89" s="6" t="n">
-        <v>25.99</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>40086</t>
+          <t>40116</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
@@ -6674,7 +6702,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Mocha - Herbal Tea</t>
+          <t>French Roast - Herbal Tea</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -6692,17 +6720,17 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>40016</t>
+          <t>40066</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>795239400669</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Vanilla Nut - Herbal Tea</t>
+          <t>Hazelnut - Herbal Tea</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -6720,7 +6748,7 @@
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>43226</t>
+          <t>40086</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -6730,7 +6758,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dandelion Caramel Nut - Herbal Tea</t>
+          <t>Mocha - Herbal Tea</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -6739,63 +6767,119 @@
         </is>
       </c>
       <c r="E92" s="6" t="n">
-        <v>32.99</v>
+        <v>23.99</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>36.49</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
+          <t>40016</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Vanilla Nut - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>50ct</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="F93" s="6" t="n">
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>43226</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Dandelion Caramel Nut - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>50ct</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="F94" s="6" t="n">
+        <v>36.49</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
           <t>43116</t>
         </is>
       </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="B95" s="5" t="inlineStr">
         <is>
           <t>795239431168</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>Dandelion Dark Roast - Herbal Tea</t>
         </is>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D95" s="5" t="inlineStr">
         <is>
           <t>50ct</t>
         </is>
       </c>
-      <c r="E93" s="6" t="n">
+      <c r="E95" s="6" t="n">
         <v>32.99</v>
       </c>
-      <c r="F93" s="6" t="n">
+      <c r="F95" s="6" t="n">
         <v>36.49</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="8" t="inlineStr">
-        <is>
-          <t>Copies of All Certifications Available Upon Request</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="8" t="inlineStr">
-        <is>
-          <t>All prices are FOB, Oxnard, California USA with no minimum.</t>
-        </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
+          <t>Copies of All Certifications Available Upon Request</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>All prices are FOB, Oxnard, California USA with no minimum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
+        <is>
           <t>Order lead time - 5 business days</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="9" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr">
         <is>
           <t>Teeccino Caffé, Inc.  |  P: (800) 498-3434  |  F: (805) 966-0522  |  sales@teeccino.com  |  teeccino.com</t>
         </is>
@@ -6803,12 +6887,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A99:F99"/>
     <mergeCell ref="A98:F98"/>
+    <mergeCell ref="A102:F102"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A97:F97"/>
     <mergeCell ref="A100:F100"/>
-    <mergeCell ref="A96:F96"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToWidth="1"/>
@@ -6822,7 +6906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A8:F119"/>
+  <dimension ref="A8:F118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.4" customWidth="1" min="1" max="1"/>
@@ -7613,7 +7697,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>50094</t>
+          <t>40097</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -7623,21 +7707,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Six - Herbal Coffee</t>
+          <t>Best Selling - Herbal Tea</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr"/>
       <c r="E41" s="6" t="n">
-        <v>17.99</v>
+        <v>20.99</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>19.99</v>
+        <v>22.99</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>40097</t>
+          <t>50092</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -7647,7 +7731,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Best Selling - Herbal Tea</t>
+          <t>Chocolate Sampler Pack - Sampler</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr"/>
@@ -7661,7 +7745,7 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>50092</t>
+          <t>50095</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -7671,21 +7755,23 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chocolate Sampler Pack - Sampler</t>
+          <t>Holiday Flavors - Herbal Coffee</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr"/>
       <c r="E43" s="6" t="n">
         <v>20.99</v>
       </c>
-      <c r="F43" s="6" t="n">
-        <v>22.99</v>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>50095</t>
+          <t>59001</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -7695,7 +7781,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Holiday Flavors - Herbal Coffee</t>
+          <t>Teeccino Most Coffee Like Blends Sampler - Sampler</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr"/>
@@ -7711,7 +7797,7 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>59001</t>
+          <t>53091</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -7721,33 +7807,35 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Teeccino Most Coffee Like Blends Sampler - Sampler</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr"/>
+          <t>Dandelion - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>6ct</t>
+        </is>
+      </c>
       <c r="E45" s="6" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>23.99</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>24.99</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>53091</t>
+          <t>55092</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>795239550920</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dandelion - Herbal Coffee</t>
+          <t>Mushroom Coffee - Herbal Coffee</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -7759,41 +7847,39 @@
         <v>23.99</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>24.99</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>55092</t>
+          <t>53098</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>795239550920</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Mushroom Coffee - Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>6ct</t>
-        </is>
-      </c>
+          <t>Dandelion - Herbal Coffee</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr"/>
       <c r="E47" s="6" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="F47" s="6" t="n">
-        <v>25.99</v>
+        <v>30.99</v>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>53098</t>
+          <t>50093</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -7803,23 +7889,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dandelion - Herbal Coffee</t>
+          <t>Teeccino Wellness - Herbal Coffee</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr"/>
       <c r="E48" s="6" t="n">
-        <v>30.99</v>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>31.99</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>34.99</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>50093</t>
+          <t>50097</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -7829,219 +7913,221 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Teeccino Wellness - Herbal Coffee</t>
+          <t>Classic - Herbal Coffee</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr"/>
       <c r="E49" s="6" t="n">
-        <v>31.99</v>
+        <v>33.99</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>34.99</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>50097</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Classic - Herbal Coffee</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr"/>
-      <c r="E50" s="6" t="n">
-        <v>33.99</v>
-      </c>
-      <c r="F50" s="6" t="n">
         <v>36.99</v>
       </c>
     </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>Item #</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>UPC:</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>TeeChia Super Seed Cereal:</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>Packaging Size:</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>Unit Price:</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>MSRP:</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>74422</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>853510004217</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>TeeChia Cran Apple - Super Seed Cereal</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>300g</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>74422</t>
+          <t>74420</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>853510004217</t>
+          <t>853510004200</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TeeChia Cran Apple - Super Seed Cereal</t>
+          <t>TeeChia Blueberry - Super Seed Cereal</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>300g</t>
+          <t>10.6oz</t>
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>13.99</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>15.49</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>74420</t>
+          <t>74439</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>853510004200</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TeeChia Blueberry - Super Seed Cereal</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>10.6oz</t>
-        </is>
-      </c>
+          <t>TeeChia Variety - Cereal</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr"/>
       <c r="E54" s="6" t="n">
-        <v>13.99</v>
+        <v>18.99</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>15.49</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>74439</t>
+          <t>74440</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
+          <t>853510744403</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>TeeChia Blueberry Date - Super Seed Cereal</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>5lb</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>74.98999999999999</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>82.48999999999999</v>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Item #</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>UPC:</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Variety Packs &amp; Baskets:</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Packaging Size:</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Unit Price:</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>MSRP:</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>GIFT CARD</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>TeeChia Variety - Cereal</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr"/>
-      <c r="E55" s="6" t="n">
-        <v>18.99</v>
-      </c>
-      <c r="F55" s="6" t="n">
-        <v>19.99</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>74440</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>853510744403</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>TeeChia Blueberry Date - Super Seed Cereal</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>5lb</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="n">
-        <v>74.98999999999999</v>
-      </c>
-      <c r="F56" s="6" t="n">
-        <v>82.48999999999999</v>
-      </c>
-    </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>Item #</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>UPC:</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>Variety Packs &amp; Baskets:</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>Packaging Size:</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>Unit Price:</t>
-        </is>
-      </c>
-      <c r="F58" s="3" t="inlineStr">
-        <is>
-          <t>MSRP:</t>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>GIFT CARD</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr"/>
+      <c r="E58" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>GIFT CARD</t>
+          <t>GIFTCARD</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -8051,7 +8137,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GIFT CARD</t>
+          <t>eGift Card</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr"/>
@@ -8082,7 +8168,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr"/>
       <c r="E60" s="6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
@@ -8093,7 +8179,7 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>GIFTCARD</t>
+          <t>12250</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -8103,61 +8189,59 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>eGift Card</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr"/>
+          <t>Advent Calendar - Herbal Tea - Advent calendar</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>24ct</t>
+        </is>
+      </c>
       <c r="E61" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>29.99</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>32.99</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>12250</t>
+          <t>43998</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>795239439980</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Advent Calendar - Herbal Tea - Advent calendar</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>24ct</t>
-        </is>
-      </c>
+          <t>Dandelion Tea - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr"/>
       <c r="E62" s="6" t="n">
-        <v>29.99</v>
+        <v>34.99</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>32.99</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>43998</t>
+          <t>40999</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>795239439980</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dandelion Tea - Herbal Tea</t>
+          <t>Teeccino Classic - Herbal Tea</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr"/>
@@ -8165,13 +8249,13 @@
         <v>34.99</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>36.99</v>
+        <v>38.49</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>40999</t>
+          <t>90077</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -8181,21 +8265,21 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Teeccino Classic - Herbal Tea</t>
+          <t>Teeccino &amp; TeeChia Breakfast Gift - Cereal - Gift box</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr"/>
       <c r="E64" s="6" t="n">
-        <v>34.99</v>
+        <v>36.99</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>38.49</v>
+        <v>38.99</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>90077</t>
+          <t>49020</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -8205,21 +8289,25 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Teeccino &amp; TeeChia Breakfast Gift - Cereal - Gift box</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr"/>
+          <t>Sampler Gift - Herbal Tea</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>48ct</t>
+        </is>
+      </c>
       <c r="E65" s="6" t="n">
-        <v>36.99</v>
+        <v>37.99</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>38.99</v>
+        <v>41.99</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>49020</t>
+          <t>MDBOXTB</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -8229,25 +8317,23 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sampler Gift - Herbal Tea</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>48ct</t>
-        </is>
-      </c>
+          <t>Father's Day Gift (coffee and Tea Editions) - Herbal Tea - Gift box</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr"/>
       <c r="E66" s="6" t="n">
-        <v>37.99</v>
-      </c>
-      <c r="F66" s="6" t="n">
-        <v>41.99</v>
+        <v>42.99</v>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>MDBOXTB</t>
+          <t>HFBOXAPGOLD</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -8257,7 +8343,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Father's Day Gift (coffee and Tea Editions) - Herbal Tea - Gift box</t>
+          <t>Holiday Favorites Gift OLD DO NOT USE - Herbal Tea</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr"/>
@@ -8273,7 +8359,7 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>HFBOXAPGOLD</t>
+          <t>HFBOXTBOOLD</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -8299,7 +8385,7 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>HFBOXTBOOLD</t>
+          <t>NCBOXAPG</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -8309,23 +8395,21 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Holiday Favorites Gift OLD DO NOT USE - Herbal Tea</t>
+          <t>Teeccino - Herbal Coffee - Gift box (APG)</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr"/>
       <c r="E69" s="6" t="n">
         <v>42.99</v>
       </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="F69" s="6" t="n">
+        <v>54.99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>NCBOXAPG</t>
+          <t>NCBOXTB</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -8335,21 +8419,23 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Teeccino - Herbal Coffee - Gift box (APG)</t>
+          <t>Teeccino - Herbal Tea - Gift box</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr"/>
       <c r="E70" s="6" t="n">
         <v>42.99</v>
       </c>
-      <c r="F70" s="6" t="n">
-        <v>54.99</v>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>NCBOXTB</t>
+          <t>FDBOXAPG</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -8359,23 +8445,21 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Teeccino - Herbal Tea - Gift box</t>
+          <t>Bold Brew (coffee and Tea Editions) - Bundle - Gift box</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr"/>
       <c r="E71" s="6" t="n">
-        <v>42.99</v>
-      </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>43.99</v>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>56.99</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>FDBOXAPG</t>
+          <t>FALLBOXAPG</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -8385,95 +8469,95 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bold Brew (coffee and Tea Editions) - Bundle - Gift box</t>
+          <t>Fall Favorites Box - Herbal Coffee - Gift box</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr"/>
       <c r="E72" s="6" t="n">
         <v>43.99</v>
       </c>
-      <c r="F72" s="6" t="n">
-        <v>56.99</v>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>FALLBOXAPG</t>
+          <t>89006</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>795239890064</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fall Favorites Box - Herbal Coffee - Gift box</t>
+          <t>Teeccino Pour Over Starter Kit - Bundle</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr"/>
       <c r="E73" s="6" t="n">
         <v>43.99</v>
       </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="F73" s="6" t="n">
+        <v>45.99</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>89006</t>
+          <t>89004</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>795239890064</t>
+          <t>795239890040</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Teeccino Pour Over Starter Kit - Bundle</t>
+          <t>Teeccino Vanilla Nut French Roast Mocha - Variety pack</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr"/>
       <c r="E74" s="6" t="n">
-        <v>43.99</v>
+        <v>44.99</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>45.99</v>
+        <v>46.99</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>89004</t>
+          <t>FDBOXTB</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>795239890040</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Teeccino Vanilla Nut French Roast Mocha - Variety pack</t>
+          <t>Bold Brew (coffee and Tea Editions) - Herbal Tea - Gift box</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr"/>
       <c r="E75" s="6" t="n">
-        <v>44.99</v>
+        <v>47.99</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>46.99</v>
+        <v>56.49</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>FDBOXTB</t>
+          <t>FALLBOXTB</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -8483,57 +8567,57 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bold Brew (coffee and Tea Editions) - Herbal Tea - Gift box</t>
+          <t>Fall Favorites Box - Herbal Tea - Gift box</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr"/>
       <c r="E76" s="6" t="n">
         <v>47.99</v>
       </c>
-      <c r="F76" s="6" t="n">
-        <v>56.49</v>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>FALLBOXTB</t>
+          <t>90073</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>795239900732</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Fall Favorites Box - Herbal Tea - Gift box</t>
+          <t>Teeccino - Bundle - Brew starter kit</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr"/>
       <c r="E77" s="6" t="n">
         <v>47.99</v>
       </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="F77" s="6" t="n">
+        <v>52.99</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>90073</t>
+          <t>89006</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>795239900732</t>
+          <t>795239890064</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Teeccino - Bundle - Brew starter kit</t>
+          <t>Teeccino Pour Over Starter Kit - Bundle</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr"/>
@@ -8541,37 +8625,39 @@
         <v>47.99</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>52.99</v>
+        <v>60.99</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>89006</t>
+          <t>CLBOXAPG</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>795239890064</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Teeccino Pour Over Starter Kit - Bundle</t>
+          <t>Chocolate Lovers Gift Coffee Edition - Bundle - Gift box</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr"/>
       <c r="E79" s="6" t="n">
-        <v>47.99</v>
-      </c>
-      <c r="F79" s="6" t="n">
-        <v>60.99</v>
+        <v>48.99</v>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>CLBOXAPG</t>
+          <t>CLBOXTB</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -8581,7 +8667,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chocolate Lovers Gift Coffee Edition - Bundle - Gift box</t>
+          <t>Chocolate Lovers Gift Tea Edition - Herbal Tea - Gift box</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr"/>
@@ -8597,7 +8683,7 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>CLBOXTB</t>
+          <t>90002</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
@@ -8607,7 +8693,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chocolate Lovers Gift Tea Edition - Herbal Tea - Gift box</t>
+          <t>Daily Ritual - Bundle - Bundle</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr"/>
@@ -8623,7 +8709,7 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>90002</t>
+          <t>GIFTCARD</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -8633,12 +8719,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Daily Ritual - Bundle - Bundle</t>
+          <t>eGift Card</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr"/>
       <c r="E82" s="6" t="n">
-        <v>48.99</v>
+        <v>50</v>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
@@ -8649,7 +8735,7 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>GIFTCARD</t>
+          <t>FDBOXAPG</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
@@ -8659,23 +8745,21 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>eGift Card</t>
+          <t>Bold Brew (coffee and Tea Editions) - Bundle - Gift box</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr"/>
       <c r="E83" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>53.99</v>
+      </c>
+      <c r="F83" s="6" t="n">
+        <v>62.49</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>FDBOXAPG</t>
+          <t>90003</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
@@ -8685,21 +8769,23 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bold Brew (coffee and Tea Editions) - Bundle - Gift box</t>
+          <t>Daily Ritual - Herbal Tea - Bundle</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr"/>
       <c r="E84" s="6" t="n">
         <v>53.99</v>
       </c>
-      <c r="F84" s="6" t="n">
-        <v>62.49</v>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>90003</t>
+          <t>s</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
@@ -8709,23 +8795,21 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Daily Ritual - Herbal Tea - Bundle</t>
+          <t>Fall Box - Herbal Coffee</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr"/>
       <c r="E85" s="6" t="n">
         <v>53.99</v>
       </c>
-      <c r="F85" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="F85" s="6" t="n">
+        <v>80.98999999999999</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>MDBOXAPG</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
@@ -8735,21 +8819,23 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Fall Box - Herbal Coffee</t>
+          <t>Father's Day Gift (coffee and Tea Editions) - Bundle - Gift box</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr"/>
       <c r="E86" s="6" t="n">
         <v>53.99</v>
       </c>
-      <c r="F86" s="6" t="n">
-        <v>80.98999999999999</v>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>MDBOXAPG</t>
+          <t>MDBOXTB</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
@@ -8759,7 +8845,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Father's Day Gift (coffee and Tea Editions) - Bundle - Gift box</t>
+          <t>Father's Day Gift (coffee and Tea Editions) - Herbal Tea - Gift box</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr"/>
@@ -8775,7 +8861,7 @@
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>MDBOXTB</t>
+          <t>HFBOXAPG</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
@@ -8785,7 +8871,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Father's Day Gift (coffee and Tea Editions) - Herbal Tea - Gift box</t>
+          <t>Holiday Favorites - Bundle - Gift box</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr"/>
@@ -8801,7 +8887,7 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>HFBOXAPG</t>
+          <t>HFBOXTB</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
@@ -8811,7 +8897,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Holiday Favorites - Bundle - Gift box</t>
+          <t>Holiday Favorites Gift Tea Edition - Herbal Tea - Gift box</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr"/>
@@ -8827,7 +8913,7 @@
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>HFBOXTB</t>
+          <t>BU003</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
@@ -8837,23 +8923,21 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Holiday Favorites Gift Tea Edition - Herbal Tea - Gift box</t>
+          <t>✨Teeccino Clarity &amp; Glow Bundle✨ - Bundle</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr"/>
       <c r="E90" s="6" t="n">
         <v>53.99</v>
       </c>
-      <c r="F90" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="F90" s="6" t="n">
+        <v>69.98999999999999</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>BU003</t>
+          <t>90004</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
@@ -8863,7 +8947,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>✨Teeccino Clarity &amp; Glow Bundle✨ - Bundle</t>
+          <t>🌙 Teeccino Lights Out Bundle 🌙 - Bundle - Bundle</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr"/>
@@ -8871,13 +8955,13 @@
         <v>53.99</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>69.98999999999999</v>
+        <v>65.98999999999999</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>90004</t>
+          <t>BU001</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -8887,7 +8971,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>🌙 Teeccino Lights Out Bundle 🌙 - Bundle - Bundle</t>
+          <t>🌞 Teeccino Daily Ritual Bundle 🌞 - Bundle</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr"/>
@@ -8895,13 +8979,13 @@
         <v>53.99</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>65.98999999999999</v>
+        <v>67.98999999999999</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>BU001</t>
+          <t>BU002</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
@@ -8911,7 +8995,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>🌞 Teeccino Daily Ritual Bundle 🌞 - Bundle</t>
+          <t>💧 Teeccino Daily Detox Bundle 💧 - Bundle</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr"/>
@@ -8919,15 +9003,11 @@
         <v>53.99</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>67.98999999999999</v>
+        <v>68.98999999999999</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>BU002</t>
-        </is>
-      </c>
+      <c r="A94" s="5" t="inlineStr"/>
       <c r="B94" s="5" t="inlineStr">
         <is>
           <t>n/a</t>
@@ -8935,19 +9015,23 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>💧 Teeccino Daily Detox Bundle 💧 - Bundle</t>
+          <t>Teeccino Classic Herbal Coffee Starter Kit</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr"/>
       <c r="E94" s="6" t="n">
-        <v>53.99</v>
+        <v>56.99</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>68.98999999999999</v>
+        <v>73.48999999999999</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="inlineStr"/>
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>WELBOX</t>
+        </is>
+      </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
           <t>n/a</t>
@@ -8955,23 +9039,21 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Teeccino Classic Herbal Coffee Starter Kit</t>
+          <t>Wellness - Bundle - Wellness box</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr"/>
       <c r="E95" s="6" t="n">
         <v>56.99</v>
       </c>
-      <c r="F95" s="6" t="n">
-        <v>73.48999999999999</v>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>WELBOX</t>
-        </is>
-      </c>
+      <c r="A96" s="5" t="inlineStr"/>
       <c r="B96" s="5" t="inlineStr">
         <is>
           <t>n/a</t>
@@ -8979,21 +9061,23 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Wellness - Bundle - Wellness box</t>
+          <t>Fall Box - Herbal Coffee</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr"/>
       <c r="E96" s="6" t="n">
-        <v>56.99</v>
-      </c>
-      <c r="F96" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>58.99</v>
+      </c>
+      <c r="F96" s="6" t="n">
+        <v>80.48999999999999</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="inlineStr"/>
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>90001</t>
+        </is>
+      </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
           <t>n/a</t>
@@ -9001,7 +9085,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Fall Box - Herbal Coffee</t>
+          <t>Instant Miraculous Mushroom - Instant Herbal Coffee - Bundle</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr"/>
@@ -9015,17 +9099,17 @@
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>90001</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>795239100040</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Instant Miraculous Mushroom - Instant Herbal Coffee - Bundle</t>
+          <t>Maca Vanilla Maple Pecan French Vanilla Variety - Variety pack</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr"/>
@@ -9033,37 +9117,37 @@
         <v>58.99</v>
       </c>
       <c r="F98" s="6" t="n">
-        <v>80.48999999999999</v>
+        <v>79.48999999999999</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>85002</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>795239100040</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Maca Vanilla Maple Pecan French Vanilla Variety - Variety pack</t>
+          <t>Mushroom Starter Pack - Custom kit</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr"/>
       <c r="E99" s="6" t="n">
-        <v>58.99</v>
+        <v>59</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>79.48999999999999</v>
+        <v>64.98999999999999</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>85002</t>
+          <t>89005</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
@@ -9073,69 +9157,69 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Mushroom Starter Pack - Custom kit</t>
+          <t>Mocha French Roast Hazelup French Press - Bundle - Starter kit</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr"/>
       <c r="E100" s="6" t="n">
-        <v>59</v>
+        <v>59.99</v>
       </c>
       <c r="F100" s="6" t="n">
-        <v>64.98999999999999</v>
+        <v>62.99</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>89005</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>795239100033</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Mocha French Roast Hazelup French Press - Bundle - Starter kit</t>
+          <t>French Roast Hazenul Choco Ras Caramel Nut - Variety pack</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr"/>
       <c r="E101" s="6" t="n">
-        <v>59.99</v>
+        <v>60.99</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>62.99</v>
+        <v>66.98999999999999</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>90013</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>795239100033</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>French Roast Hazenul Choco Ras Caramel Nut - Variety pack</t>
+          <t>Teeccino Instant Collections - Instant Herbal Coffee - Gift box</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr"/>
       <c r="E102" s="6" t="n">
-        <v>60.99</v>
+        <v>63.99</v>
       </c>
       <c r="F102" s="6" t="n">
-        <v>66.98999999999999</v>
+        <v>86.48999999999999</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>90013</t>
+          <t>83001</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
@@ -9145,21 +9229,21 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Teeccino Instant Collections - Instant Herbal Coffee - Gift box</t>
+          <t>Dandelion W/ French Press Starter - Bundle - Starter kit</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr"/>
       <c r="E103" s="6" t="n">
-        <v>63.99</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>86.48999999999999</v>
+        <v>75.98999999999999</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>83001</t>
+          <t>90001</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
@@ -9169,21 +9253,21 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Dandelion W/ French Press Starter - Bundle - Starter kit</t>
+          <t>Instant Miraculous Mushroom - Instant Herbal Coffee - Bundle</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr"/>
       <c r="E104" s="6" t="n">
-        <v>68.98999999999999</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>75.98999999999999</v>
+        <v>101.99</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>90001</t>
+          <t>GIFTCARD</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
@@ -9193,15 +9277,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Instant Miraculous Mushroom - Instant Herbal Coffee - Bundle</t>
+          <t>eGift Card</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr"/>
       <c r="E105" s="6" t="n">
-        <v>74.98999999999999</v>
-      </c>
-      <c r="F105" s="6" t="n">
-        <v>101.99</v>
+        <v>75</v>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -9222,7 +9308,7 @@
       </c>
       <c r="D106" s="5" t="inlineStr"/>
       <c r="E106" s="6" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
@@ -9233,7 +9319,7 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>GIFTCARD</t>
+          <t>90078</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
@@ -9243,23 +9329,21 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>eGift Card</t>
+          <t>Works - Gift basket</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr"/>
       <c r="E107" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="F107" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>128.99</v>
+      </c>
+      <c r="F107" s="6" t="n">
+        <v>141.99</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>90078</t>
+          <t>90045</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -9269,21 +9353,23 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Works - Gift basket</t>
+          <t>Handwoven Teeccino Combo - Herbal Coffee - Bag + product combo (APG)</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr"/>
       <c r="E108" s="6" t="n">
-        <v>128.99</v>
-      </c>
-      <c r="F108" s="6" t="n">
-        <v>141.99</v>
+        <v>139.99</v>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>90045</t>
+          <t>90048</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
@@ -9309,7 +9395,7 @@
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>90048</t>
+          <t>90046</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
@@ -9319,7 +9405,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Handwoven Teeccino Combo - Herbal Coffee - Bag + product combo (APG)</t>
+          <t>Handwoven Teeccino Combo - Herbal Tea - Bag + product combo</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr"/>
@@ -9335,7 +9421,7 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>90046</t>
+          <t>90047</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
@@ -9358,55 +9444,29 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="5" t="inlineStr">
-        <is>
-          <t>90047</t>
-        </is>
-      </c>
-      <c r="B112" s="5" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Handwoven Teeccino Combo - Herbal Tea - Bag + product combo</t>
-        </is>
-      </c>
-      <c r="D112" s="5" t="inlineStr"/>
-      <c r="E112" s="6" t="n">
-        <v>139.99</v>
-      </c>
-      <c r="F112" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
+    <row r="114">
+      <c r="A114" s="8" t="inlineStr">
+        <is>
+          <t>Copies of All Certifications Available Upon Request</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>Copies of All Certifications Available Upon Request</t>
+          <t>All prices are FOB, Oxnard, California USA with no minimum.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t>All prices are FOB, Oxnard, California USA with no minimum.</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="8" t="inlineStr">
-        <is>
           <t>Order lead time - 5 business days</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="9" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="9" t="inlineStr">
         <is>
           <t>Teeccino Caffé, Inc.  |  P: (800) 498-3434  |  F: (805) 966-0522  |  sales@teeccino.com  |  teeccino.com</t>
         </is>
@@ -9416,10 +9476,10 @@
   <mergeCells count="6">
     <mergeCell ref="A115:F115"/>
     <mergeCell ref="A116:F116"/>
-    <mergeCell ref="A117:F117"/>
+    <mergeCell ref="A118:F118"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A119:F119"/>
+    <mergeCell ref="A114:F114"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToWidth="1"/>

--- a/teeccino-retail-price-list-new-prices.xlsx
+++ b/teeccino-retail-price-list-new-prices.xlsx
@@ -101,10 +101,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -639,9 +639,9 @@
           <t>795239800407</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Blood Orange - Herbal Coffee (APG)</t>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Blood Orange - Herbal Coffee (APG) (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -649,10 +649,10 @@
           <t>11oz bag</t>
         </is>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="7" t="n">
         <v>18.49</v>
       </c>
     </row>
@@ -667,7 +667,7 @@
           <t>795239820207</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Caramel Nut - Herbal Coffee (DISCONTINUED)</t>
         </is>
@@ -677,10 +677,10 @@
           <t>11oz bag</t>
         </is>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="7" t="n">
         <v>18.49</v>
       </c>
     </row>
@@ -705,10 +705,10 @@
           <t>11oz bag</t>
         </is>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="7" t="n">
         <v>18.49</v>
       </c>
     </row>
@@ -733,10 +733,10 @@
           <t>11oz bag</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F14" s="7" t="n">
         <v>18.49</v>
       </c>
     </row>
@@ -751,7 +751,7 @@
           <t>795239801206</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Maya Chai - Herbal Coffee (DISCONTINUED)</t>
         </is>
@@ -761,10 +761,10 @@
           <t>11oz bag</t>
         </is>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="7" t="n">
         <v>18.49</v>
       </c>
     </row>
@@ -789,10 +789,10 @@
           <t>11oz bag</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F16" s="7" t="n">
         <v>18.49</v>
       </c>
     </row>
@@ -807,7 +807,7 @@
           <t>795239801404</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Original - Herbal Coffee (DISCONTINUED)</t>
         </is>
@@ -817,10 +817,10 @@
           <t>11oz bag</t>
         </is>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="E17" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="7" t="n">
         <v>18.49</v>
       </c>
     </row>
@@ -845,10 +845,10 @@
           <t>11oz bag</t>
         </is>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F18" s="7" t="n">
         <v>18.49</v>
       </c>
     </row>
@@ -873,10 +873,10 @@
           <t>11oz bag</t>
         </is>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E19" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="F19" s="7" t="n">
         <v>18.99</v>
       </c>
     </row>
@@ -901,10 +901,10 @@
           <t>11oz bag</t>
         </is>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E20" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F20" s="7" t="n">
         <v>18.49</v>
       </c>
     </row>
@@ -929,10 +929,10 @@
           <t>11oz bag</t>
         </is>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E21" s="7" t="n">
         <v>17.99</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F21" s="7" t="n">
         <v>19.49</v>
       </c>
     </row>
@@ -957,10 +957,10 @@
           <t>11oz bag</t>
         </is>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="7" t="n">
         <v>17.99</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F22" s="7" t="n">
         <v>19.49</v>
       </c>
     </row>
@@ -985,10 +985,10 @@
           <t>11oz bag</t>
         </is>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E23" s="7" t="n">
         <v>17.99</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="F23" s="7" t="n">
         <v>19.49</v>
       </c>
     </row>
@@ -1013,10 +1013,10 @@
           <t>11oz bag</t>
         </is>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E24" s="7" t="n">
         <v>17.99</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="F24" s="7" t="n">
         <v>19.49</v>
       </c>
     </row>
@@ -1041,10 +1041,10 @@
           <t>11oz bag</t>
         </is>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="E25" s="7" t="n">
         <v>17.99</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="F25" s="7" t="n">
         <v>19.49</v>
       </c>
     </row>
@@ -1069,10 +1069,10 @@
           <t>11oz bag</t>
         </is>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E26" s="7" t="n">
         <v>17.99</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="F26" s="7" t="n">
         <v>19.49</v>
       </c>
     </row>
@@ -1097,10 +1097,10 @@
           <t>11oz bag</t>
         </is>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="E27" s="7" t="n">
         <v>17.99</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="F27" s="7" t="n">
         <v>19.49</v>
       </c>
     </row>
@@ -1125,10 +1125,10 @@
           <t>11oz bag</t>
         </is>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E28" s="7" t="n">
         <v>17.99</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F28" s="7" t="n">
         <v>19.49</v>
       </c>
     </row>
@@ -1153,10 +1153,10 @@
           <t>11oz bag</t>
         </is>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="E29" s="7" t="n">
         <v>17.99</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="F29" s="7" t="n">
         <v>19.49</v>
       </c>
     </row>
@@ -1181,10 +1181,10 @@
           <t>11oz bag</t>
         </is>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="E30" s="7" t="n">
         <v>17.99</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="F30" s="7" t="n">
         <v>19.49</v>
       </c>
     </row>
@@ -1209,10 +1209,10 @@
           <t>11oz bag</t>
         </is>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="E31" s="7" t="n">
         <v>17.99</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="F31" s="7" t="n">
         <v>19.49</v>
       </c>
     </row>
@@ -1237,10 +1237,10 @@
           <t>11oz bag</t>
         </is>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="E32" s="7" t="n">
         <v>17.99</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="F32" s="7" t="n">
         <v>19.49</v>
       </c>
     </row>
@@ -1265,10 +1265,10 @@
           <t>11oz bag</t>
         </is>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="E33" s="7" t="n">
         <v>18.49</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="F33" s="7" t="n">
         <v>20.49</v>
       </c>
     </row>
@@ -1325,10 +1325,10 @@
           <t>10oz bag</t>
         </is>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="E36" s="7" t="n">
         <v>18.99</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="F36" s="7" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
           <t>795239850402</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>Cordyceps Schisandra Cinnamon Berry Mushroom - Herbal Coffee (DISCONTINUED)</t>
         </is>
@@ -1353,10 +1353,10 @@
           <t>10oz bag</t>
         </is>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="E37" s="7" t="n">
         <v>18.99</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="F37" s="7" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -1381,10 +1381,10 @@
           <t>10oz bag</t>
         </is>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="E38" s="7" t="n">
         <v>18.99</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="F38" s="7" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -1409,10 +1409,10 @@
           <t>10oz bag</t>
         </is>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="E39" s="7" t="n">
         <v>18.99</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="F39" s="7" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -1437,10 +1437,10 @@
           <t>10oz bag</t>
         </is>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="E40" s="7" t="n">
         <v>18.99</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="F40" s="7" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -1465,10 +1465,10 @@
           <t>10oz bag</t>
         </is>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="E41" s="7" t="n">
         <v>18.99</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="F41" s="7" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
           <t>795239833504</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>Dandelion Passionfruit Peach - Herbal Coffee (DISCONTINUED)</t>
         </is>
@@ -1493,10 +1493,10 @@
           <t>10oz bag</t>
         </is>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="E42" s="7" t="n">
         <v>18.99</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="F42" s="7" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -1521,10 +1521,10 @@
           <t>10oz bag</t>
         </is>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="E43" s="7" t="n">
         <v>18.99</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="F43" s="7" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -1549,10 +1549,10 @@
           <t>10oz bag</t>
         </is>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="E44" s="7" t="n">
         <v>18.99</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="F44" s="7" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -1577,10 +1577,10 @@
           <t>10oz bag</t>
         </is>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="E45" s="7" t="n">
         <v>18.99</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="F45" s="7" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -1605,10 +1605,10 @@
           <t>10oz bag</t>
         </is>
       </c>
-      <c r="E46" s="6" t="n">
+      <c r="E46" s="7" t="n">
         <v>18.99</v>
       </c>
-      <c r="F46" s="6" t="n">
+      <c r="F46" s="7" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -1633,10 +1633,10 @@
           <t>10oz bag</t>
         </is>
       </c>
-      <c r="E47" s="6" t="n">
+      <c r="E47" s="7" t="n">
         <v>18.99</v>
       </c>
-      <c r="F47" s="6" t="n">
+      <c r="F47" s="7" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -1661,10 +1661,10 @@
           <t>10oz bag</t>
         </is>
       </c>
-      <c r="E48" s="6" t="n">
+      <c r="E48" s="7" t="n">
         <v>18.99</v>
       </c>
-      <c r="F48" s="6" t="n">
+      <c r="F48" s="7" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -1689,10 +1689,10 @@
           <t>10oz bag</t>
         </is>
       </c>
-      <c r="E49" s="6" t="n">
+      <c r="E49" s="7" t="n">
         <v>19.99</v>
       </c>
-      <c r="F49" s="6" t="n">
+      <c r="F49" s="7" t="n">
         <v>21.99</v>
       </c>
     </row>
@@ -1717,10 +1717,10 @@
           <t>10oz bag</t>
         </is>
       </c>
-      <c r="E50" s="6" t="n">
+      <c r="E50" s="7" t="n">
         <v>19.99</v>
       </c>
-      <c r="F50" s="6" t="n">
+      <c r="F50" s="7" t="n">
         <v>21.99</v>
       </c>
     </row>
@@ -1745,10 +1745,10 @@
           <t>10oz bag</t>
         </is>
       </c>
-      <c r="E51" s="6" t="n">
+      <c r="E51" s="7" t="n">
         <v>19.99</v>
       </c>
-      <c r="F51" s="6" t="n">
+      <c r="F51" s="7" t="n">
         <v>21.99</v>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
           <t>795239860203</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>Macadamia Nut Prebiotic SuperBoost - Herbal Coffee (DISCONTINUED)</t>
         </is>
@@ -1773,10 +1773,10 @@
           <t>10oz bag</t>
         </is>
       </c>
-      <c r="E52" s="6" t="n">
+      <c r="E52" s="7" t="n">
         <v>19.99</v>
       </c>
-      <c r="F52" s="6" t="n">
+      <c r="F52" s="7" t="n">
         <v>21.99</v>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
           <t>795239860302</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>Mango Lemon Balm Prebiotic SuperBoost - Herbal Coffee (DISCONTINUED)</t>
         </is>
@@ -1801,10 +1801,10 @@
           <t>10oz bag</t>
         </is>
       </c>
-      <c r="E53" s="6" t="n">
+      <c r="E53" s="7" t="n">
         <v>19.99</v>
       </c>
-      <c r="F53" s="6" t="n">
+      <c r="F53" s="7" t="n">
         <v>21.99</v>
       </c>
     </row>
@@ -1829,10 +1829,10 @@
           <t>10oz bag</t>
         </is>
       </c>
-      <c r="E54" s="6" t="n">
+      <c r="E54" s="7" t="n">
         <v>19.99</v>
       </c>
-      <c r="F54" s="6" t="n">
+      <c r="F54" s="7" t="n">
         <v>21.99</v>
       </c>
     </row>
@@ -1857,10 +1857,10 @@
           <t>10oz bag</t>
         </is>
       </c>
-      <c r="E55" s="6" t="n">
+      <c r="E55" s="7" t="n">
         <v>21.99</v>
       </c>
-      <c r="F55" s="6" t="n">
+      <c r="F55" s="7" t="n">
         <v>23.99</v>
       </c>
     </row>
@@ -1885,10 +1885,10 @@
           <t>10oz bag</t>
         </is>
       </c>
-      <c r="E56" s="6" t="n">
+      <c r="E56" s="7" t="n">
         <v>21.99</v>
       </c>
-      <c r="F56" s="6" t="n">
+      <c r="F56" s="7" t="n">
         <v>23.99</v>
       </c>
     </row>
@@ -1945,10 +1945,10 @@
           <t>500g</t>
         </is>
       </c>
-      <c r="E59" s="6" t="n">
+      <c r="E59" s="7" t="n">
         <v>27.99</v>
       </c>
-      <c r="F59" s="6" t="n">
+      <c r="F59" s="7" t="n">
         <v>30.99</v>
       </c>
     </row>
@@ -1973,10 +1973,10 @@
           <t>500g</t>
         </is>
       </c>
-      <c r="E60" s="6" t="n">
+      <c r="E60" s="7" t="n">
         <v>27.99</v>
       </c>
-      <c r="F60" s="6" t="n">
+      <c r="F60" s="7" t="n">
         <v>30.49</v>
       </c>
     </row>
@@ -2001,10 +2001,10 @@
           <t>500g</t>
         </is>
       </c>
-      <c r="E61" s="6" t="n">
+      <c r="E61" s="7" t="n">
         <v>27.99</v>
       </c>
-      <c r="F61" s="6" t="n">
+      <c r="F61" s="7" t="n">
         <v>30.99</v>
       </c>
     </row>
@@ -2029,10 +2029,10 @@
           <t>500g</t>
         </is>
       </c>
-      <c r="E62" s="6" t="n">
+      <c r="E62" s="7" t="n">
         <v>27.99</v>
       </c>
-      <c r="F62" s="6" t="n">
+      <c r="F62" s="7" t="n">
         <v>30.99</v>
       </c>
     </row>
@@ -2057,10 +2057,10 @@
           <t>500g</t>
         </is>
       </c>
-      <c r="E63" s="6" t="n">
+      <c r="E63" s="7" t="n">
         <v>34.99</v>
       </c>
-      <c r="F63" s="6" t="n">
+      <c r="F63" s="7" t="n">
         <v>38.49</v>
       </c>
     </row>
@@ -2085,10 +2085,10 @@
           <t>500g</t>
         </is>
       </c>
-      <c r="E64" s="6" t="n">
+      <c r="E64" s="7" t="n">
         <v>34.99</v>
       </c>
-      <c r="F64" s="6" t="n">
+      <c r="F64" s="7" t="n">
         <v>38.49</v>
       </c>
     </row>
@@ -2145,10 +2145,10 @@
           <t>5lb bag</t>
         </is>
       </c>
-      <c r="E67" s="6" t="n">
+      <c r="E67" s="7" t="n">
         <v>89.98999999999999</v>
       </c>
-      <c r="F67" s="6" t="n">
+      <c r="F67" s="7" t="n">
         <v>98.98999999999999</v>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
           <t>795239600403</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr">
+      <c r="C68" s="6" t="inlineStr">
         <is>
           <t>Blood Orange - Herbal Coffee (DISCONTINUED)</t>
         </is>
@@ -2173,10 +2173,10 @@
           <t>5lb bag</t>
         </is>
       </c>
-      <c r="E68" s="6" t="n">
+      <c r="E68" s="7" t="n">
         <v>89.98999999999999</v>
       </c>
-      <c r="F68" s="6" t="n">
+      <c r="F68" s="7" t="n">
         <v>98.98999999999999</v>
       </c>
     </row>
@@ -2201,10 +2201,10 @@
           <t>5lb bag</t>
         </is>
       </c>
-      <c r="E69" s="6" t="n">
+      <c r="E69" s="7" t="n">
         <v>89.98999999999999</v>
       </c>
-      <c r="F69" s="6" t="n">
+      <c r="F69" s="7" t="n">
         <v>98.98999999999999</v>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
           <t>795239620203</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr">
+      <c r="C70" s="6" t="inlineStr">
         <is>
           <t>Caramel Nut - Herbal Coffee (DISCONTINUED)</t>
         </is>
@@ -2229,10 +2229,10 @@
           <t>5lb bag</t>
         </is>
       </c>
-      <c r="E70" s="6" t="n">
+      <c r="E70" s="7" t="n">
         <v>89.98999999999999</v>
       </c>
-      <c r="F70" s="6" t="n">
+      <c r="F70" s="7" t="n">
         <v>98.98999999999999</v>
       </c>
     </row>
@@ -2257,10 +2257,10 @@
           <t>5lb bag</t>
         </is>
       </c>
-      <c r="E71" s="6" t="n">
+      <c r="E71" s="7" t="n">
         <v>89.98999999999999</v>
       </c>
-      <c r="F71" s="6" t="n">
+      <c r="F71" s="7" t="n">
         <v>98.98999999999999</v>
       </c>
     </row>
@@ -2285,10 +2285,10 @@
           <t>5lb bag</t>
         </is>
       </c>
-      <c r="E72" s="6" t="n">
+      <c r="E72" s="7" t="n">
         <v>89.98999999999999</v>
       </c>
-      <c r="F72" s="6" t="n">
+      <c r="F72" s="7" t="n">
         <v>98.98999999999999</v>
       </c>
     </row>
@@ -2313,10 +2313,10 @@
           <t>5lb bag</t>
         </is>
       </c>
-      <c r="E73" s="6" t="n">
+      <c r="E73" s="7" t="n">
         <v>89.98999999999999</v>
       </c>
-      <c r="F73" s="6" t="n">
+      <c r="F73" s="7" t="n">
         <v>98.98999999999999</v>
       </c>
     </row>
@@ -2341,10 +2341,10 @@
           <t>5lb bag</t>
         </is>
       </c>
-      <c r="E74" s="6" t="n">
+      <c r="E74" s="7" t="n">
         <v>89.98999999999999</v>
       </c>
-      <c r="F74" s="6" t="n">
+      <c r="F74" s="7" t="n">
         <v>98.98999999999999</v>
       </c>
     </row>
@@ -2369,10 +2369,10 @@
           <t>5lb bag</t>
         </is>
       </c>
-      <c r="E75" s="6" t="n">
+      <c r="E75" s="7" t="n">
         <v>89.98999999999999</v>
       </c>
-      <c r="F75" s="6" t="n">
+      <c r="F75" s="7" t="n">
         <v>98.98999999999999</v>
       </c>
     </row>
@@ -2397,10 +2397,10 @@
           <t>5lb bag</t>
         </is>
       </c>
-      <c r="E76" s="6" t="n">
+      <c r="E76" s="7" t="n">
         <v>89.98999999999999</v>
       </c>
-      <c r="F76" s="6" t="n">
+      <c r="F76" s="7" t="n">
         <v>98.98999999999999</v>
       </c>
     </row>
@@ -2425,10 +2425,10 @@
           <t>5lb bag</t>
         </is>
       </c>
-      <c r="E77" s="6" t="n">
+      <c r="E77" s="7" t="n">
         <v>89.98999999999999</v>
       </c>
-      <c r="F77" s="6" t="n">
+      <c r="F77" s="7" t="n">
         <v>98.98999999999999</v>
       </c>
     </row>
@@ -2453,10 +2453,10 @@
           <t>5lb bag</t>
         </is>
       </c>
-      <c r="E78" s="6" t="n">
+      <c r="E78" s="7" t="n">
         <v>89.98999999999999</v>
       </c>
-      <c r="F78" s="6" t="n">
+      <c r="F78" s="7" t="n">
         <v>98.98999999999999</v>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
           <t>795239601202</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
+      <c r="C79" s="6" t="inlineStr">
         <is>
           <t>Maya Chai - Herbal Coffee (DISCONTINUED)</t>
         </is>
@@ -2481,10 +2481,10 @@
           <t>5lb bag</t>
         </is>
       </c>
-      <c r="E79" s="6" t="n">
+      <c r="E79" s="7" t="n">
         <v>89.98999999999999</v>
       </c>
-      <c r="F79" s="6" t="n">
+      <c r="F79" s="7" t="n">
         <v>98.98999999999999</v>
       </c>
     </row>
@@ -2509,10 +2509,10 @@
           <t>5lb bag</t>
         </is>
       </c>
-      <c r="E80" s="6" t="n">
+      <c r="E80" s="7" t="n">
         <v>89.98999999999999</v>
       </c>
-      <c r="F80" s="6" t="n">
+      <c r="F80" s="7" t="n">
         <v>98.98999999999999</v>
       </c>
     </row>
@@ -2537,10 +2537,10 @@
           <t>5lb bag</t>
         </is>
       </c>
-      <c r="E81" s="6" t="n">
+      <c r="E81" s="7" t="n">
         <v>89.98999999999999</v>
       </c>
-      <c r="F81" s="6" t="n">
+      <c r="F81" s="7" t="n">
         <v>98.98999999999999</v>
       </c>
     </row>
@@ -2565,10 +2565,10 @@
           <t>5lb bag</t>
         </is>
       </c>
-      <c r="E82" s="6" t="n">
+      <c r="E82" s="7" t="n">
         <v>89.98999999999999</v>
       </c>
-      <c r="F82" s="6" t="n">
+      <c r="F82" s="7" t="n">
         <v>98.98999999999999</v>
       </c>
     </row>
@@ -2593,10 +2593,10 @@
           <t>5lb bag</t>
         </is>
       </c>
-      <c r="E83" s="6" t="n">
+      <c r="E83" s="7" t="n">
         <v>89.98999999999999</v>
       </c>
-      <c r="F83" s="6" t="n">
+      <c r="F83" s="7" t="n">
         <v>98.98999999999999</v>
       </c>
     </row>
@@ -2621,10 +2621,10 @@
           <t>5lb bag</t>
         </is>
       </c>
-      <c r="E84" s="6" t="n">
+      <c r="E84" s="7" t="n">
         <v>114.99</v>
       </c>
-      <c r="F84" s="6" t="n">
+      <c r="F84" s="7" t="n">
         <v>126.49</v>
       </c>
     </row>
@@ -2649,10 +2649,10 @@
           <t>5lb bag</t>
         </is>
       </c>
-      <c r="E85" s="6" t="n">
+      <c r="E85" s="7" t="n">
         <v>114.99</v>
       </c>
-      <c r="F85" s="6" t="n">
+      <c r="F85" s="7" t="n">
         <v>126.49</v>
       </c>
     </row>
@@ -2677,10 +2677,10 @@
           <t>5lb bag</t>
         </is>
       </c>
-      <c r="E86" s="6" t="n">
+      <c r="E86" s="7" t="n">
         <v>114.99</v>
       </c>
-      <c r="F86" s="6" t="n">
+      <c r="F86" s="7" t="n">
         <v>126.49</v>
       </c>
     </row>
@@ -2705,10 +2705,10 @@
           <t>5lb bag</t>
         </is>
       </c>
-      <c r="E87" s="6" t="n">
+      <c r="E87" s="7" t="n">
         <v>114.99</v>
       </c>
-      <c r="F87" s="6" t="n">
+      <c r="F87" s="7" t="n">
         <v>126.49</v>
       </c>
     </row>
@@ -2733,10 +2733,10 @@
           <t>5lb bag</t>
         </is>
       </c>
-      <c r="E88" s="6" t="n">
+      <c r="E88" s="7" t="n">
         <v>114.99</v>
       </c>
-      <c r="F88" s="6" t="n">
+      <c r="F88" s="7" t="n">
         <v>126.49</v>
       </c>
     </row>
@@ -2761,10 +2761,10 @@
           <t>5lb bag</t>
         </is>
       </c>
-      <c r="E89" s="6" t="n">
+      <c r="E89" s="7" t="n">
         <v>114.99</v>
       </c>
-      <c r="F89" s="6" t="n">
+      <c r="F89" s="7" t="n">
         <v>126.49</v>
       </c>
     </row>
@@ -2789,10 +2789,10 @@
           <t>5lb bag</t>
         </is>
       </c>
-      <c r="E90" s="6" t="n">
+      <c r="E90" s="7" t="n">
         <v>114.99</v>
       </c>
-      <c r="F90" s="6" t="n">
+      <c r="F90" s="7" t="n">
         <v>126.49</v>
       </c>
     </row>
@@ -2817,10 +2817,10 @@
           <t>5lb bag</t>
         </is>
       </c>
-      <c r="E91" s="6" t="n">
+      <c r="E91" s="7" t="n">
         <v>114.99</v>
       </c>
-      <c r="F91" s="6" t="n">
+      <c r="F91" s="7" t="n">
         <v>126.49</v>
       </c>
     </row>
@@ -2845,10 +2845,10 @@
           <t>5lb bag</t>
         </is>
       </c>
-      <c r="E92" s="6" t="n">
+      <c r="E92" s="7" t="n">
         <v>114.99</v>
       </c>
-      <c r="F92" s="6" t="n">
+      <c r="F92" s="7" t="n">
         <v>126.49</v>
       </c>
     </row>
@@ -2873,10 +2873,10 @@
           <t>5lb bag</t>
         </is>
       </c>
-      <c r="E93" s="6" t="n">
+      <c r="E93" s="7" t="n">
         <v>139.99</v>
       </c>
-      <c r="F93" s="6" t="n">
+      <c r="F93" s="7" t="n">
         <v>153.99</v>
       </c>
     </row>
@@ -2933,10 +2933,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E96" s="6" t="n">
+      <c r="E96" s="7" t="n">
         <v>1.43</v>
       </c>
-      <c r="F96" s="6" t="n">
+      <c r="F96" s="7" t="n">
         <v>1.99</v>
       </c>
     </row>
@@ -2961,10 +2961,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E97" s="6" t="n">
+      <c r="E97" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="F97" s="6" t="n">
+      <c r="F97" s="7" t="n">
         <v>3.99</v>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
           <t>795239500406</t>
         </is>
       </c>
-      <c r="C98" s="7" t="inlineStr">
+      <c r="C98" s="6" t="inlineStr">
         <is>
           <t>Blood Orange - Herbal Coffee (DISCONTINUED)</t>
         </is>
@@ -2989,10 +2989,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E98" s="6" t="n">
+      <c r="E98" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="F98" s="6" t="n">
+      <c r="F98" s="7" t="n">
         <v>3.99</v>
       </c>
     </row>
@@ -3007,7 +3007,7 @@
           <t>795239520206</t>
         </is>
       </c>
-      <c r="C99" s="7" t="inlineStr">
+      <c r="C99" s="6" t="inlineStr">
         <is>
           <t>Caramel Nut - Herbal Coffee (DISCONTINUED)</t>
         </is>
@@ -3017,10 +3017,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E99" s="6" t="n">
+      <c r="E99" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="F99" s="6" t="n">
+      <c r="F99" s="7" t="n">
         <v>3.99</v>
       </c>
     </row>
@@ -3045,10 +3045,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E100" s="6" t="n">
+      <c r="E100" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="F100" s="6" t="n">
+      <c r="F100" s="7" t="n">
         <v>3.99</v>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
           <t>795239521203</t>
         </is>
       </c>
-      <c r="C101" s="7" t="inlineStr">
+      <c r="C101" s="6" t="inlineStr">
         <is>
           <t>Chocolate Raspberry Chicory - Sampler (APG) (DISCONTINUED)</t>
         </is>
@@ -3073,10 +3073,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E101" s="6" t="n">
+      <c r="E101" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="F101" s="6" t="n">
+      <c r="F101" s="7" t="n">
         <v>3.99</v>
       </c>
     </row>
@@ -3101,10 +3101,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E102" s="6" t="n">
+      <c r="E102" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="F102" s="6" t="n">
+      <c r="F102" s="7" t="n">
         <v>3.99</v>
       </c>
     </row>
@@ -3119,7 +3119,7 @@
           <t>795239521104</t>
         </is>
       </c>
-      <c r="C103" s="7" t="inlineStr">
+      <c r="C103" s="6" t="inlineStr">
         <is>
           <t>French Vanilla Chicory - Sampler (APG) (DISCONTINUED)</t>
         </is>
@@ -3129,10 +3129,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E103" s="6" t="n">
+      <c r="E103" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="F103" s="6" t="n">
+      <c r="F103" s="7" t="n">
         <v>3.99</v>
       </c>
     </row>
@@ -3157,10 +3157,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E104" s="6" t="n">
+      <c r="E104" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="F104" s="6" t="n">
+      <c r="F104" s="7" t="n">
         <v>3.99</v>
       </c>
     </row>
@@ -3185,10 +3185,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E105" s="6" t="n">
+      <c r="E105" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="F105" s="6" t="n">
+      <c r="F105" s="7" t="n">
         <v>3.99</v>
       </c>
     </row>
@@ -3213,10 +3213,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E106" s="6" t="n">
+      <c r="E106" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="F106" s="6" t="n">
+      <c r="F106" s="7" t="n">
         <v>3.99</v>
       </c>
     </row>
@@ -3241,10 +3241,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E107" s="6" t="n">
+      <c r="E107" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="F107" s="6" t="n">
+      <c r="F107" s="7" t="n">
         <v>3.99</v>
       </c>
     </row>
@@ -3269,10 +3269,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E108" s="6" t="n">
+      <c r="E108" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="F108" s="6" t="n">
+      <c r="F108" s="7" t="n">
         <v>3.99</v>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
           <t>795239501205</t>
         </is>
       </c>
-      <c r="C109" s="7" t="inlineStr">
+      <c r="C109" s="6" t="inlineStr">
         <is>
           <t>Maya Chai Chicory - Sampler (APG) (DISCONTINUED)</t>
         </is>
@@ -3297,10 +3297,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E109" s="6" t="n">
+      <c r="E109" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="F109" s="6" t="n">
+      <c r="F109" s="7" t="n">
         <v>3.99</v>
       </c>
     </row>
@@ -3325,10 +3325,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E110" s="6" t="n">
+      <c r="E110" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="F110" s="6" t="n">
+      <c r="F110" s="7" t="n">
         <v>3.99</v>
       </c>
     </row>
@@ -3343,7 +3343,7 @@
           <t>795239501403</t>
         </is>
       </c>
-      <c r="C111" s="7" t="inlineStr">
+      <c r="C111" s="6" t="inlineStr">
         <is>
           <t>Original - Herbal Coffee (DISCONTINUED)</t>
         </is>
@@ -3353,10 +3353,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E111" s="6" t="n">
+      <c r="E111" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="F111" s="6" t="n">
+      <c r="F111" s="7" t="n">
         <v>3.99</v>
       </c>
     </row>
@@ -3381,10 +3381,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E112" s="6" t="n">
+      <c r="E112" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="F112" s="6" t="n">
+      <c r="F112" s="7" t="n">
         <v>3.99</v>
       </c>
     </row>
@@ -3409,10 +3409,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E113" s="6" t="n">
+      <c r="E113" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="F113" s="6" t="n">
+      <c r="F113" s="7" t="n">
         <v>3.99</v>
       </c>
     </row>
@@ -3437,10 +3437,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E114" s="6" t="n">
+      <c r="E114" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="F114" s="6" t="n">
+      <c r="F114" s="7" t="n">
         <v>3.99</v>
       </c>
     </row>
@@ -3465,10 +3465,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E115" s="6" t="n">
+      <c r="E115" s="7" t="n">
         <v>3.99</v>
       </c>
-      <c r="F115" s="6" t="n">
+      <c r="F115" s="7" t="n">
         <v>4.49</v>
       </c>
     </row>
@@ -3493,10 +3493,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E116" s="6" t="n">
+      <c r="E116" s="7" t="n">
         <v>3.99</v>
       </c>
-      <c r="F116" s="6" t="n">
+      <c r="F116" s="7" t="n">
         <v>4.49</v>
       </c>
     </row>
@@ -3521,10 +3521,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E117" s="6" t="n">
+      <c r="E117" s="7" t="n">
         <v>3.99</v>
       </c>
-      <c r="F117" s="6" t="n">
+      <c r="F117" s="7" t="n">
         <v>4.49</v>
       </c>
     </row>
@@ -3549,10 +3549,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E118" s="6" t="n">
+      <c r="E118" s="7" t="n">
         <v>3.99</v>
       </c>
-      <c r="F118" s="6" t="n">
+      <c r="F118" s="7" t="n">
         <v>4.49</v>
       </c>
     </row>
@@ -3577,10 +3577,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E119" s="6" t="n">
+      <c r="E119" s="7" t="n">
         <v>3.99</v>
       </c>
-      <c r="F119" s="6" t="n">
+      <c r="F119" s="7" t="n">
         <v>4.49</v>
       </c>
     </row>
@@ -3595,7 +3595,7 @@
           <t>795239533503</t>
         </is>
       </c>
-      <c r="C120" s="7" t="inlineStr">
+      <c r="C120" s="6" t="inlineStr">
         <is>
           <t>Dandelion Passionfruit Peach - Sampler (APG) (DISCONTINUED)</t>
         </is>
@@ -3605,10 +3605,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E120" s="6" t="n">
+      <c r="E120" s="7" t="n">
         <v>3.99</v>
       </c>
-      <c r="F120" s="6" t="n">
+      <c r="F120" s="7" t="n">
         <v>4.49</v>
       </c>
     </row>
@@ -3623,7 +3623,7 @@
           <t>795239533206</t>
         </is>
       </c>
-      <c r="C121" s="7" t="inlineStr">
+      <c r="C121" s="6" t="inlineStr">
         <is>
           <t>Dandelion Red Chai - Sampler (APG) (DISCONTINUED)</t>
         </is>
@@ -3633,10 +3633,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E121" s="6" t="n">
+      <c r="E121" s="7" t="n">
         <v>3.99</v>
       </c>
-      <c r="F121" s="6" t="n">
+      <c r="F121" s="7" t="n">
         <v>4.49</v>
       </c>
     </row>
@@ -3661,10 +3661,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E122" s="6" t="n">
+      <c r="E122" s="7" t="n">
         <v>3.99</v>
       </c>
-      <c r="F122" s="6" t="n">
+      <c r="F122" s="7" t="n">
         <v>4.49</v>
       </c>
     </row>
@@ -3689,10 +3689,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E123" s="6" t="n">
+      <c r="E123" s="7" t="n">
         <v>3.99</v>
       </c>
-      <c r="F123" s="6" t="n">
+      <c r="F123" s="7" t="n">
         <v>4.49</v>
       </c>
     </row>
@@ -3717,10 +3717,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E124" s="6" t="n">
+      <c r="E124" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F124" s="6" t="n">
+      <c r="F124" s="7" t="n">
         <v>4.49</v>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
           <t>795239550401</t>
         </is>
       </c>
-      <c r="C125" s="7" t="inlineStr">
+      <c r="C125" s="6" t="inlineStr">
         <is>
           <t>Cordyceps Schisandra Cinnamon Berry Mushroom - Herbal Coffee (DISCONTINUED)</t>
         </is>
@@ -3745,10 +3745,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E125" s="6" t="n">
+      <c r="E125" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F125" s="6" t="n">
+      <c r="F125" s="7" t="n">
         <v>4.49</v>
       </c>
     </row>
@@ -3773,10 +3773,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E126" s="6" t="n">
+      <c r="E126" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F126" s="6" t="n">
+      <c r="F126" s="7" t="n">
         <v>4.49</v>
       </c>
     </row>
@@ -3801,10 +3801,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E127" s="6" t="n">
+      <c r="E127" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F127" s="6" t="n">
+      <c r="F127" s="7" t="n">
         <v>4.49</v>
       </c>
     </row>
@@ -3819,7 +3819,7 @@
           <t>795239560202</t>
         </is>
       </c>
-      <c r="C128" s="7" t="inlineStr">
+      <c r="C128" s="6" t="inlineStr">
         <is>
           <t>Macadamia Nut Prebiotic SuperBoost - Herbal Coffee (DISCONTINUED)</t>
         </is>
@@ -3829,10 +3829,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E128" s="6" t="n">
+      <c r="E128" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F128" s="6" t="n">
+      <c r="F128" s="7" t="n">
         <v>4.49</v>
       </c>
     </row>
@@ -3847,7 +3847,7 @@
           <t>795239560301</t>
         </is>
       </c>
-      <c r="C129" s="7" t="inlineStr">
+      <c r="C129" s="6" t="inlineStr">
         <is>
           <t>Mango Lemon Balm Prebiotic SuperBoost - Herbal Coffee (DISCONTINUED)</t>
         </is>
@@ -3857,10 +3857,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E129" s="6" t="n">
+      <c r="E129" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F129" s="6" t="n">
+      <c r="F129" s="7" t="n">
         <v>4.49</v>
       </c>
     </row>
@@ -3885,10 +3885,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E130" s="6" t="n">
+      <c r="E130" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F130" s="6" t="n">
+      <c r="F130" s="7" t="n">
         <v>4.49</v>
       </c>
     </row>
@@ -3903,7 +3903,7 @@
           <t>795239550609</t>
         </is>
       </c>
-      <c r="C131" s="7" t="inlineStr">
+      <c r="C131" s="6" t="inlineStr">
         <is>
           <t>Tremella Tulsi Cardamom Mushroom - Herbal Coffee (DISCONTINUED)</t>
         </is>
@@ -3913,10 +3913,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E131" s="6" t="n">
+      <c r="E131" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F131" s="6" t="n">
+      <c r="F131" s="7" t="n">
         <v>4.49</v>
       </c>
     </row>
@@ -3941,10 +3941,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E132" s="6" t="n">
+      <c r="E132" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F132" s="6" t="n">
+      <c r="F132" s="7" t="n">
         <v>4.49</v>
       </c>
     </row>
@@ -3969,10 +3969,10 @@
           <t>1.05oz packet</t>
         </is>
       </c>
-      <c r="E133" s="6" t="n">
+      <c r="E133" s="7" t="n">
         <v>17.99</v>
       </c>
-      <c r="F133" s="6" t="n">
+      <c r="F133" s="7" t="n">
         <v>19.99</v>
       </c>
     </row>
@@ -4029,10 +4029,10 @@
           <t>3.53oz bag</t>
         </is>
       </c>
-      <c r="E136" s="6" t="n">
+      <c r="E136" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="F136" s="6" t="n">
+      <c r="F136" s="7" t="n">
         <v>18.49</v>
       </c>
     </row>
@@ -4057,10 +4057,10 @@
           <t>3.53oz bag</t>
         </is>
       </c>
-      <c r="E137" s="6" t="n">
+      <c r="E137" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="F137" s="6" t="n">
+      <c r="F137" s="7" t="n">
         <v>18.49</v>
       </c>
     </row>
@@ -4085,10 +4085,10 @@
           <t>3.53oz bag</t>
         </is>
       </c>
-      <c r="E138" s="6" t="n">
+      <c r="E138" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="F138" s="6" t="n">
+      <c r="F138" s="7" t="n">
         <v>18.49</v>
       </c>
     </row>
@@ -4113,10 +4113,10 @@
           <t>3.53oz bag</t>
         </is>
       </c>
-      <c r="E139" s="6" t="n">
+      <c r="E139" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="F139" s="6" t="n">
+      <c r="F139" s="7" t="n">
         <v>18.49</v>
       </c>
     </row>
@@ -4141,10 +4141,10 @@
           <t>3.95oz bag</t>
         </is>
       </c>
-      <c r="E140" s="6" t="n">
+      <c r="E140" s="7" t="n">
         <v>22.99</v>
       </c>
-      <c r="F140" s="6" t="n">
+      <c r="F140" s="7" t="n">
         <v>25.49</v>
       </c>
     </row>
@@ -4169,10 +4169,10 @@
           <t>3.53oz bag</t>
         </is>
       </c>
-      <c r="E141" s="6" t="n">
+      <c r="E141" s="7" t="n">
         <v>29.99</v>
       </c>
-      <c r="F141" s="6" t="n">
+      <c r="F141" s="7" t="n">
         <v>32.99</v>
       </c>
     </row>
@@ -4229,10 +4229,10 @@
           <t>7.9oz bag</t>
         </is>
       </c>
-      <c r="E144" s="6" t="n">
+      <c r="E144" s="7" t="n">
         <v>21.99</v>
       </c>
-      <c r="F144" s="6" t="n">
+      <c r="F144" s="7" t="n">
         <v>23.99</v>
       </c>
     </row>
@@ -4257,10 +4257,10 @@
           <t>7.9oz bag</t>
         </is>
       </c>
-      <c r="E145" s="6" t="n">
+      <c r="E145" s="7" t="n">
         <v>21.99</v>
       </c>
-      <c r="F145" s="6" t="n">
+      <c r="F145" s="7" t="n">
         <v>23.99</v>
       </c>
     </row>
@@ -4285,10 +4285,10 @@
           <t>7.9oz bag</t>
         </is>
       </c>
-      <c r="E146" s="6" t="n">
+      <c r="E146" s="7" t="n">
         <v>21.99</v>
       </c>
-      <c r="F146" s="6" t="n">
+      <c r="F146" s="7" t="n">
         <v>23.99</v>
       </c>
     </row>
@@ -4313,10 +4313,10 @@
           <t>7.9oz bag</t>
         </is>
       </c>
-      <c r="E147" s="6" t="n">
+      <c r="E147" s="7" t="n">
         <v>21.99</v>
       </c>
-      <c r="F147" s="6" t="n">
+      <c r="F147" s="7" t="n">
         <v>23.99</v>
       </c>
     </row>
@@ -4341,10 +4341,10 @@
           <t>4.76oz bag</t>
         </is>
       </c>
-      <c r="E148" s="6" t="n">
+      <c r="E148" s="7" t="n">
         <v>22.99</v>
       </c>
-      <c r="F148" s="6" t="n">
+      <c r="F148" s="7" t="n">
         <v>25.49</v>
       </c>
     </row>
@@ -4369,10 +4369,10 @@
           <t>7.9oz bag</t>
         </is>
       </c>
-      <c r="E149" s="6" t="n">
+      <c r="E149" s="7" t="n">
         <v>24.99</v>
       </c>
-      <c r="F149" s="6" t="n">
+      <c r="F149" s="7" t="n">
         <v>27.49</v>
       </c>
     </row>
@@ -4397,10 +4397,10 @@
           <t>7.9oz bag</t>
         </is>
       </c>
-      <c r="E150" s="6" t="n">
+      <c r="E150" s="7" t="n">
         <v>24.99</v>
       </c>
-      <c r="F150" s="6" t="n">
+      <c r="F150" s="7" t="n">
         <v>27.49</v>
       </c>
     </row>
@@ -4425,10 +4425,10 @@
           <t>8.9oz bag</t>
         </is>
       </c>
-      <c r="E151" s="6" t="n">
+      <c r="E151" s="7" t="n">
         <v>29.99</v>
       </c>
-      <c r="F151" s="6" t="n">
+      <c r="F151" s="7" t="n">
         <v>35.49</v>
       </c>
     </row>
@@ -4566,10 +4566,10 @@
           <t>10ct box</t>
         </is>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="7" t="n">
         <v>8.99</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="7" t="n">
         <v>9.99</v>
       </c>
     </row>
@@ -4594,10 +4594,10 @@
           <t>10ct box</t>
         </is>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="7" t="n">
         <v>8.99</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="7" t="n">
         <v>9.99</v>
       </c>
     </row>
@@ -4622,10 +4622,10 @@
           <t>10ct box</t>
         </is>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="7" t="n">
         <v>8.99</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="7" t="n">
         <v>9.99</v>
       </c>
     </row>
@@ -4650,10 +4650,10 @@
           <t>10ct box</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="7" t="n">
         <v>8.99</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F14" s="7" t="n">
         <v>9.99</v>
       </c>
     </row>
@@ -4678,10 +4678,10 @@
           <t>10ct box</t>
         </is>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="7" t="n">
         <v>8.99</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="7" t="n">
         <v>9.99</v>
       </c>
     </row>
@@ -4706,10 +4706,10 @@
           <t>10ct box</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="7" t="n">
         <v>8.99</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F16" s="7" t="n">
         <v>9.99</v>
       </c>
     </row>
@@ -4734,10 +4734,10 @@
           <t>10ct box</t>
         </is>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="E17" s="7" t="n">
         <v>8.99</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="7" t="n">
         <v>10.99</v>
       </c>
     </row>
@@ -4762,10 +4762,10 @@
           <t>10ct box</t>
         </is>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="7" t="n">
         <v>9.99</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F18" s="7" t="n">
         <v>10.99</v>
       </c>
     </row>
@@ -4790,7 +4790,7 @@
           <t>10ct box</t>
         </is>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E19" s="7" t="n">
         <v>9.99</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -4820,10 +4820,10 @@
           <t>10ct box</t>
         </is>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E20" s="7" t="n">
         <v>9.99</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F20" s="7" t="n">
         <v>10.99</v>
       </c>
     </row>
@@ -4848,10 +4848,10 @@
           <t>10ct box</t>
         </is>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E21" s="7" t="n">
         <v>9.99</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F21" s="7" t="n">
         <v>10.99</v>
       </c>
     </row>
@@ -4876,10 +4876,10 @@
           <t>10ct box</t>
         </is>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="7" t="n">
         <v>9.99</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F22" s="7" t="n">
         <v>10.99</v>
       </c>
     </row>
@@ -4904,10 +4904,10 @@
           <t>10ct box</t>
         </is>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E23" s="7" t="n">
         <v>9.99</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="F23" s="7" t="n">
         <v>10.99</v>
       </c>
     </row>
@@ -4932,10 +4932,10 @@
           <t>10ct</t>
         </is>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E24" s="7" t="n">
         <v>9.99</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="F24" s="7" t="n">
         <v>10.99</v>
       </c>
     </row>
@@ -4960,10 +4960,10 @@
           <t>10ct</t>
         </is>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="E25" s="7" t="n">
         <v>9.99</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="F25" s="7" t="n">
         <v>10.99</v>
       </c>
     </row>
@@ -4988,10 +4988,10 @@
           <t>10ct box</t>
         </is>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E26" s="7" t="n">
         <v>9.99</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="F26" s="7" t="n">
         <v>10.99</v>
       </c>
     </row>
@@ -5016,10 +5016,10 @@
           <t>10ct box</t>
         </is>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="E27" s="7" t="n">
         <v>9.99</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="F27" s="7" t="n">
         <v>10.99</v>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
           <t>795239450602</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>Tremella Tulsi Cardamom Mushroom - Herbal Tea (DISCONTINUED)</t>
         </is>
@@ -5044,10 +5044,10 @@
           <t>10ct box</t>
         </is>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E28" s="7" t="n">
         <v>9.99</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F28" s="7" t="n">
         <v>10.99</v>
       </c>
     </row>
@@ -5072,10 +5072,10 @@
           <t>10ct box</t>
         </is>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="E29" s="7" t="n">
         <v>9.99</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="F29" s="7" t="n">
         <v>10.99</v>
       </c>
     </row>
@@ -5100,7 +5100,7 @@
           <t>10ct box</t>
         </is>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="E30" s="7" t="n">
         <v>10.49</v>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -5130,10 +5130,10 @@
           <t>10ct box</t>
         </is>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="E31" s="7" t="n">
         <v>10.99</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="F31" s="7" t="n">
         <v>11.99</v>
       </c>
     </row>
@@ -5158,10 +5158,10 @@
           <t>10ct box</t>
         </is>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="E32" s="7" t="n">
         <v>10.99</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="F32" s="7" t="n">
         <v>11.99</v>
       </c>
     </row>
@@ -5176,7 +5176,7 @@
           <t>795239460304</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>Mango Lemon Balm Prebiotic SuperBoost - Herbal Tea (DISCONTINUED)</t>
         </is>
@@ -5186,10 +5186,10 @@
           <t>10ct box</t>
         </is>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="E33" s="7" t="n">
         <v>10.99</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="F33" s="7" t="n">
         <v>11.99</v>
       </c>
     </row>
@@ -5246,10 +5246,10 @@
           <t>12ct box</t>
         </is>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="E36" s="7" t="n">
         <v>11.99</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="F36" s="7" t="n">
         <v>12.99</v>
       </c>
     </row>
@@ -5274,10 +5274,10 @@
           <t>12ct box</t>
         </is>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="E37" s="7" t="n">
         <v>11.99</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="F37" s="7" t="n">
         <v>13.49</v>
       </c>
     </row>
@@ -5302,10 +5302,10 @@
           <t>12ct box</t>
         </is>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="E38" s="7" t="n">
         <v>12.99</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="F38" s="7" t="n">
         <v>13.99</v>
       </c>
     </row>
@@ -5330,10 +5330,10 @@
           <t>12ct box</t>
         </is>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="E39" s="7" t="n">
         <v>12.99</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="F39" s="7" t="n">
         <v>13.99</v>
       </c>
     </row>
@@ -5358,10 +5358,10 @@
           <t>12ct</t>
         </is>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="E40" s="7" t="n">
         <v>12.99</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="F40" s="7" t="n">
         <v>14.49</v>
       </c>
     </row>
@@ -5418,10 +5418,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="E43" s="7" t="n">
         <v>15.99</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="F43" s="7" t="n">
         <v>16.49</v>
       </c>
     </row>
@@ -5446,10 +5446,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="E44" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="F44" s="7" t="n">
         <v>18.49</v>
       </c>
     </row>
@@ -5474,10 +5474,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="E45" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="F45" s="7" t="n">
         <v>18.49</v>
       </c>
     </row>
@@ -5492,7 +5492,7 @@
           <t>795239420216</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>Caramel Nut - Herbal Tea (DISCONTINUED)</t>
         </is>
@@ -5502,10 +5502,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E46" s="6" t="n">
+      <c r="E46" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="F46" s="6" t="n">
+      <c r="F46" s="7" t="n">
         <v>18.49</v>
       </c>
     </row>
@@ -5530,10 +5530,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E47" s="6" t="n">
+      <c r="E47" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="F47" s="6" t="n">
+      <c r="F47" s="7" t="n">
         <v>18.49</v>
       </c>
     </row>
@@ -5558,10 +5558,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E48" s="6" t="n">
+      <c r="E48" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="F48" s="6" t="n">
+      <c r="F48" s="7" t="n">
         <v>18.49</v>
       </c>
     </row>
@@ -5586,10 +5586,10 @@
           <t>25ct</t>
         </is>
       </c>
-      <c r="E49" s="6" t="n">
+      <c r="E49" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="F49" s="6" t="n">
+      <c r="F49" s="7" t="n">
         <v>18.49</v>
       </c>
     </row>
@@ -5614,10 +5614,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E50" s="6" t="n">
+      <c r="E50" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="F50" s="6" t="n">
+      <c r="F50" s="7" t="n">
         <v>18.49</v>
       </c>
     </row>
@@ -5642,10 +5642,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E51" s="6" t="n">
+      <c r="E51" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="F51" s="6" t="n">
+      <c r="F51" s="7" t="n">
         <v>18.49</v>
       </c>
     </row>
@@ -5670,10 +5670,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E52" s="6" t="n">
+      <c r="E52" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="F52" s="6" t="n">
+      <c r="F52" s="7" t="n">
         <v>18.49</v>
       </c>
     </row>
@@ -5688,9 +5688,9 @@
           <t>795239401215</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Maya Chai - Herbal Tea</t>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Maya Chai - Herbal Tea (DISCONTINUED)</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -5698,10 +5698,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E53" s="6" t="n">
+      <c r="E53" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="F53" s="6" t="n">
+      <c r="F53" s="7" t="n">
         <v>18.49</v>
       </c>
     </row>
@@ -5726,10 +5726,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E54" s="6" t="n">
+      <c r="E54" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="F54" s="6" t="n">
+      <c r="F54" s="7" t="n">
         <v>18.49</v>
       </c>
     </row>
@@ -5744,7 +5744,7 @@
           <t>795239401413</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>Original - Herbal Tea (DISCONTINUED)</t>
         </is>
@@ -5754,10 +5754,10 @@
           <t>25ct</t>
         </is>
       </c>
-      <c r="E55" s="6" t="n">
+      <c r="E55" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="F55" s="6" t="n">
+      <c r="F55" s="7" t="n">
         <v>18.49</v>
       </c>
     </row>
@@ -5782,10 +5782,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E56" s="6" t="n">
+      <c r="E56" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="F56" s="6" t="n">
+      <c r="F56" s="7" t="n">
         <v>18.49</v>
       </c>
     </row>
@@ -5810,10 +5810,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E57" s="6" t="n">
+      <c r="E57" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="F57" s="6" t="n">
+      <c r="F57" s="7" t="n">
         <v>18.49</v>
       </c>
     </row>
@@ -5838,10 +5838,10 @@
           <t>25ct</t>
         </is>
       </c>
-      <c r="E58" s="6" t="n">
+      <c r="E58" s="7" t="n">
         <v>17.99</v>
       </c>
-      <c r="F58" s="6" t="n">
+      <c r="F58" s="7" t="n">
         <v>19.49</v>
       </c>
     </row>
@@ -5866,10 +5866,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E59" s="6" t="n">
+      <c r="E59" s="7" t="n">
         <v>17.99</v>
       </c>
-      <c r="F59" s="6" t="n">
+      <c r="F59" s="7" t="n">
         <v>19.49</v>
       </c>
     </row>
@@ -5894,10 +5894,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E60" s="6" t="n">
+      <c r="E60" s="7" t="n">
         <v>17.99</v>
       </c>
-      <c r="F60" s="6" t="n">
+      <c r="F60" s="7" t="n">
         <v>19.49</v>
       </c>
     </row>
@@ -5922,10 +5922,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E61" s="6" t="n">
+      <c r="E61" s="7" t="n">
         <v>17.99</v>
       </c>
-      <c r="F61" s="6" t="n">
+      <c r="F61" s="7" t="n">
         <v>19.49</v>
       </c>
     </row>
@@ -5950,10 +5950,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E62" s="6" t="n">
+      <c r="E62" s="7" t="n">
         <v>17.99</v>
       </c>
-      <c r="F62" s="6" t="n">
+      <c r="F62" s="7" t="n">
         <v>19.49</v>
       </c>
     </row>
@@ -5978,10 +5978,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E63" s="6" t="n">
+      <c r="E63" s="7" t="n">
         <v>17.99</v>
       </c>
-      <c r="F63" s="6" t="n">
+      <c r="F63" s="7" t="n">
         <v>19.49</v>
       </c>
     </row>
@@ -6006,10 +6006,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E64" s="6" t="n">
+      <c r="E64" s="7" t="n">
         <v>17.99</v>
       </c>
-      <c r="F64" s="6" t="n">
+      <c r="F64" s="7" t="n">
         <v>19.99</v>
       </c>
     </row>
@@ -6034,10 +6034,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E65" s="6" t="n">
+      <c r="E65" s="7" t="n">
         <v>17.99</v>
       </c>
-      <c r="F65" s="6" t="n">
+      <c r="F65" s="7" t="n">
         <v>19.49</v>
       </c>
     </row>
@@ -6062,10 +6062,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E66" s="6" t="n">
+      <c r="E66" s="7" t="n">
         <v>18.49</v>
       </c>
-      <c r="F66" s="6" t="n">
+      <c r="F66" s="7" t="n">
         <v>20.49</v>
       </c>
     </row>
@@ -6090,10 +6090,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E67" s="6" t="n">
+      <c r="E67" s="7" t="n">
         <v>18.99</v>
       </c>
-      <c r="F67" s="6" t="n">
+      <c r="F67" s="7" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -6108,7 +6108,7 @@
           <t>795239450411</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr">
+      <c r="C68" s="6" t="inlineStr">
         <is>
           <t>Cordyceps Schisandra Cinnamon Berry Mushroom - Herbal Tea (DISCONTINUED)</t>
         </is>
@@ -6118,10 +6118,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E68" s="6" t="n">
+      <c r="E68" s="7" t="n">
         <v>18.99</v>
       </c>
-      <c r="F68" s="6" t="n">
+      <c r="F68" s="7" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -6146,10 +6146,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E69" s="6" t="n">
+      <c r="E69" s="7" t="n">
         <v>18.99</v>
       </c>
-      <c r="F69" s="6" t="n">
+      <c r="F69" s="7" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -6174,10 +6174,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E70" s="6" t="n">
+      <c r="E70" s="7" t="n">
         <v>18.99</v>
       </c>
-      <c r="F70" s="6" t="n">
+      <c r="F70" s="7" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -6202,10 +6202,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E71" s="6" t="n">
+      <c r="E71" s="7" t="n">
         <v>18.99</v>
       </c>
-      <c r="F71" s="6" t="n">
+      <c r="F71" s="7" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -6230,10 +6230,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E72" s="6" t="n">
+      <c r="E72" s="7" t="n">
         <v>18.99</v>
       </c>
-      <c r="F72" s="6" t="n">
+      <c r="F72" s="7" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -6258,10 +6258,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E73" s="6" t="n">
+      <c r="E73" s="7" t="n">
         <v>18.99</v>
       </c>
-      <c r="F73" s="6" t="n">
+      <c r="F73" s="7" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -6286,10 +6286,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E74" s="6" t="n">
+      <c r="E74" s="7" t="n">
         <v>18.99</v>
       </c>
-      <c r="F74" s="6" t="n">
+      <c r="F74" s="7" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -6314,10 +6314,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E75" s="6" t="n">
+      <c r="E75" s="7" t="n">
         <v>18.99</v>
       </c>
-      <c r="F75" s="6" t="n">
+      <c r="F75" s="7" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -6342,10 +6342,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E76" s="6" t="n">
+      <c r="E76" s="7" t="n">
         <v>18.99</v>
       </c>
-      <c r="F76" s="6" t="n">
+      <c r="F76" s="7" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -6370,10 +6370,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E77" s="6" t="n">
+      <c r="E77" s="7" t="n">
         <v>18.99</v>
       </c>
-      <c r="F77" s="6" t="n">
+      <c r="F77" s="7" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -6398,10 +6398,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E78" s="6" t="n">
+      <c r="E78" s="7" t="n">
         <v>19.99</v>
       </c>
-      <c r="F78" s="6" t="n">
+      <c r="F78" s="7" t="n">
         <v>21.99</v>
       </c>
     </row>
@@ -6426,10 +6426,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E79" s="6" t="n">
+      <c r="E79" s="7" t="n">
         <v>19.99</v>
       </c>
-      <c r="F79" s="6" t="n">
+      <c r="F79" s="7" t="n">
         <v>21.99</v>
       </c>
     </row>
@@ -6454,10 +6454,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E80" s="6" t="n">
+      <c r="E80" s="7" t="n">
         <v>19.99</v>
       </c>
-      <c r="F80" s="6" t="n">
+      <c r="F80" s="7" t="n">
         <v>21.99</v>
       </c>
     </row>
@@ -6482,10 +6482,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E81" s="6" t="n">
+      <c r="E81" s="7" t="n">
         <v>19.99</v>
       </c>
-      <c r="F81" s="6" t="n">
+      <c r="F81" s="7" t="n">
         <v>21.99</v>
       </c>
     </row>
@@ -6510,10 +6510,10 @@
           <t>25ct</t>
         </is>
       </c>
-      <c r="E82" s="6" t="n">
+      <c r="E82" s="7" t="n">
         <v>19.99</v>
       </c>
-      <c r="F82" s="6" t="n">
+      <c r="F82" s="7" t="n">
         <v>21.99</v>
       </c>
     </row>
@@ -6538,10 +6538,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E83" s="6" t="n">
+      <c r="E83" s="7" t="n">
         <v>19.99</v>
       </c>
-      <c r="F83" s="6" t="n">
+      <c r="F83" s="7" t="n">
         <v>21.99</v>
       </c>
     </row>
@@ -6556,7 +6556,7 @@
           <t>795239460212</t>
         </is>
       </c>
-      <c r="C84" s="7" t="inlineStr">
+      <c r="C84" s="6" t="inlineStr">
         <is>
           <t>Macadamia Nut Prebiotic SuperBoost - Herbal Tea (DISCONTINUED)</t>
         </is>
@@ -6566,10 +6566,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E84" s="6" t="n">
+      <c r="E84" s="7" t="n">
         <v>19.99</v>
       </c>
-      <c r="F84" s="6" t="n">
+      <c r="F84" s="7" t="n">
         <v>21.99</v>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
           <t>795239460311</t>
         </is>
       </c>
-      <c r="C85" s="7" t="inlineStr">
+      <c r="C85" s="6" t="inlineStr">
         <is>
           <t>Mango Lemon Balm Prebiotic SuperBoost - Herbal Tea (DISCONTINUED)</t>
         </is>
@@ -6594,10 +6594,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E85" s="6" t="n">
+      <c r="E85" s="7" t="n">
         <v>19.99</v>
       </c>
-      <c r="F85" s="6" t="n">
+      <c r="F85" s="7" t="n">
         <v>21.99</v>
       </c>
     </row>
@@ -6622,10 +6622,10 @@
           <t>25ct box</t>
         </is>
       </c>
-      <c r="E86" s="6" t="n">
+      <c r="E86" s="7" t="n">
         <v>19.99</v>
       </c>
-      <c r="F86" s="6" t="n">
+      <c r="F86" s="7" t="n">
         <v>21.99</v>
       </c>
     </row>
@@ -6650,10 +6650,10 @@
           <t>25ct</t>
         </is>
       </c>
-      <c r="E87" s="6" t="n">
+      <c r="E87" s="7" t="n">
         <v>21.99</v>
       </c>
-      <c r="F87" s="6" t="n">
+      <c r="F87" s="7" t="n">
         <v>23.99</v>
       </c>
     </row>
@@ -6710,10 +6710,10 @@
           <t>50ct</t>
         </is>
       </c>
-      <c r="E90" s="6" t="n">
+      <c r="E90" s="7" t="n">
         <v>23.99</v>
       </c>
-      <c r="F90" s="6" t="n">
+      <c r="F90" s="7" t="n">
         <v>25.99</v>
       </c>
     </row>
@@ -6738,10 +6738,10 @@
           <t>50ct</t>
         </is>
       </c>
-      <c r="E91" s="6" t="n">
+      <c r="E91" s="7" t="n">
         <v>23.99</v>
       </c>
-      <c r="F91" s="6" t="n">
+      <c r="F91" s="7" t="n">
         <v>25.99</v>
       </c>
     </row>
@@ -6766,10 +6766,10 @@
           <t>50ct</t>
         </is>
       </c>
-      <c r="E92" s="6" t="n">
+      <c r="E92" s="7" t="n">
         <v>23.99</v>
       </c>
-      <c r="F92" s="6" t="n">
+      <c r="F92" s="7" t="n">
         <v>25.99</v>
       </c>
     </row>
@@ -6794,10 +6794,10 @@
           <t>50ct</t>
         </is>
       </c>
-      <c r="E93" s="6" t="n">
+      <c r="E93" s="7" t="n">
         <v>23.99</v>
       </c>
-      <c r="F93" s="6" t="n">
+      <c r="F93" s="7" t="n">
         <v>25.99</v>
       </c>
     </row>
@@ -6822,10 +6822,10 @@
           <t>50ct</t>
         </is>
       </c>
-      <c r="E94" s="6" t="n">
+      <c r="E94" s="7" t="n">
         <v>32.99</v>
       </c>
-      <c r="F94" s="6" t="n">
+      <c r="F94" s="7" t="n">
         <v>36.49</v>
       </c>
     </row>
@@ -6850,10 +6850,10 @@
           <t>50ct</t>
         </is>
       </c>
-      <c r="E95" s="6" t="n">
+      <c r="E95" s="7" t="n">
         <v>32.99</v>
       </c>
-      <c r="F95" s="6" t="n">
+      <c r="F95" s="7" t="n">
         <v>36.49</v>
       </c>
     </row>
@@ -6987,10 +6987,10 @@
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="7" t="n">
         <v>6.49</v>
       </c>
     </row>
@@ -7011,10 +7011,10 @@
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="7" t="n">
         <v>8.99</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="7" t="n">
         <v>11.99</v>
       </c>
     </row>
@@ -7035,10 +7035,10 @@
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="7" t="n">
         <v>9.08</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="7" t="n">
         <v>9.99</v>
       </c>
     </row>
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="7" t="n">
         <v>9.99</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F14" s="7" t="n">
         <v>10.99</v>
       </c>
     </row>
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="7" t="n">
         <v>9.99</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="7" t="n">
         <v>10.99</v>
       </c>
     </row>
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="7" t="n">
         <v>9.99</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F16" s="7" t="n">
         <v>10.99</v>
       </c>
     </row>
@@ -7131,7 +7131,7 @@
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="6" t="n">
+      <c r="E17" s="7" t="n">
         <v>9.99</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="7" t="n">
         <v>10.52</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -7183,10 +7183,10 @@
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="6" t="n">
+      <c r="E19" s="7" t="n">
         <v>14.99</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="F19" s="7" t="n">
         <v>16.49</v>
       </c>
     </row>
@@ -7207,10 +7207,10 @@
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="6" t="n">
+      <c r="E20" s="7" t="n">
         <v>15.99</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F20" s="7" t="n">
         <v>17.49</v>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="6" t="n">
+      <c r="E21" s="7" t="n">
         <v>15.99</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -7257,10 +7257,10 @@
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="7" t="n">
         <v>15.99</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F22" s="7" t="n">
         <v>19.99</v>
       </c>
     </row>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="6" t="n">
+      <c r="E23" s="7" t="n">
         <v>15.99</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="F23" s="7" t="n">
         <v>19.99</v>
       </c>
     </row>
@@ -7305,10 +7305,10 @@
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="6" t="n">
+      <c r="E24" s="7" t="n">
         <v>17.99</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="F24" s="7" t="n">
         <v>19.99</v>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr"/>
-      <c r="E25" s="6" t="n">
+      <c r="E25" s="7" t="n">
         <v>19.99</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -7355,10 +7355,10 @@
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr"/>
-      <c r="E26" s="6" t="n">
+      <c r="E26" s="7" t="n">
         <v>19.99</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="F26" s="7" t="n">
         <v>21.99</v>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr"/>
-      <c r="E27" s="6" t="n">
+      <c r="E27" s="7" t="n">
         <v>19.99</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -7405,10 +7405,10 @@
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="6" t="n">
+      <c r="E28" s="7" t="n">
         <v>19.99</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F28" s="7" t="n">
         <v>21.99</v>
       </c>
     </row>
@@ -7429,10 +7429,10 @@
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="6" t="n">
+      <c r="E29" s="7" t="n">
         <v>19.99</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="F29" s="7" t="n">
         <v>21.99</v>
       </c>
     </row>
@@ -7453,10 +7453,10 @@
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="6" t="n">
+      <c r="E30" s="7" t="n">
         <v>36.99</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="F30" s="7" t="n">
         <v>40.49</v>
       </c>
     </row>
@@ -7477,10 +7477,10 @@
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr"/>
-      <c r="E31" s="6" t="n">
+      <c r="E31" s="7" t="n">
         <v>39.99</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="F31" s="7" t="n">
         <v>45.99</v>
       </c>
     </row>
@@ -7533,10 +7533,10 @@
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr"/>
-      <c r="E34" s="6" t="n">
+      <c r="E34" s="7" t="n">
         <v>9.99</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="F34" s="7" t="n">
         <v>10.49</v>
       </c>
     </row>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr"/>
-      <c r="E35" s="6" t="n">
+      <c r="E35" s="7" t="n">
         <v>9.99</v>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -7583,7 +7583,7 @@
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr"/>
-      <c r="E36" s="6" t="n">
+      <c r="E36" s="7" t="n">
         <v>10.95</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -7609,7 +7609,7 @@
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr"/>
-      <c r="E37" s="6" t="n">
+      <c r="E37" s="7" t="n">
         <v>10.95</v>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -7635,7 +7635,7 @@
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr"/>
-      <c r="E38" s="6" t="n">
+      <c r="E38" s="7" t="n">
         <v>11.99</v>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr"/>
-      <c r="E39" s="6" t="n">
+      <c r="E39" s="7" t="n">
         <v>11.99</v>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -7687,10 +7687,10 @@
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr"/>
-      <c r="E40" s="6" t="n">
+      <c r="E40" s="7" t="n">
         <v>15.99</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="F40" s="7" t="n">
         <v>22.49</v>
       </c>
     </row>
@@ -7711,10 +7711,10 @@
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr"/>
-      <c r="E41" s="6" t="n">
+      <c r="E41" s="7" t="n">
         <v>20.99</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="F41" s="7" t="n">
         <v>22.99</v>
       </c>
     </row>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr"/>
-      <c r="E42" s="6" t="n">
+      <c r="E42" s="7" t="n">
         <v>20.99</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="F42" s="7" t="n">
         <v>22.99</v>
       </c>
     </row>
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr"/>
-      <c r="E43" s="6" t="n">
+      <c r="E43" s="7" t="n">
         <v>20.99</v>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr"/>
-      <c r="E44" s="6" t="n">
+      <c r="E44" s="7" t="n">
         <v>20.99</v>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -7815,10 +7815,10 @@
           <t>6ct</t>
         </is>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="E45" s="7" t="n">
         <v>23.99</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="F45" s="7" t="n">
         <v>24.99</v>
       </c>
     </row>
@@ -7843,10 +7843,10 @@
           <t>6ct</t>
         </is>
       </c>
-      <c r="E46" s="6" t="n">
+      <c r="E46" s="7" t="n">
         <v>23.99</v>
       </c>
-      <c r="F46" s="6" t="n">
+      <c r="F46" s="7" t="n">
         <v>25.99</v>
       </c>
     </row>
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr"/>
-      <c r="E47" s="6" t="n">
+      <c r="E47" s="7" t="n">
         <v>30.99</v>
       </c>
       <c r="F47" s="5" t="inlineStr">
@@ -7893,10 +7893,10 @@
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr"/>
-      <c r="E48" s="6" t="n">
+      <c r="E48" s="7" t="n">
         <v>31.99</v>
       </c>
-      <c r="F48" s="6" t="n">
+      <c r="F48" s="7" t="n">
         <v>34.99</v>
       </c>
     </row>
@@ -7917,10 +7917,10 @@
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr"/>
-      <c r="E49" s="6" t="n">
+      <c r="E49" s="7" t="n">
         <v>33.99</v>
       </c>
-      <c r="F49" s="6" t="n">
+      <c r="F49" s="7" t="n">
         <v>36.99</v>
       </c>
     </row>
@@ -7977,7 +7977,7 @@
           <t>300g</t>
         </is>
       </c>
-      <c r="E52" s="6" t="n">
+      <c r="E52" s="7" t="n">
         <v>10.99</v>
       </c>
       <c r="F52" s="5" t="inlineStr">
@@ -8007,10 +8007,10 @@
           <t>10.6oz</t>
         </is>
       </c>
-      <c r="E53" s="6" t="n">
+      <c r="E53" s="7" t="n">
         <v>13.99</v>
       </c>
-      <c r="F53" s="6" t="n">
+      <c r="F53" s="7" t="n">
         <v>15.49</v>
       </c>
     </row>
@@ -8031,10 +8031,10 @@
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr"/>
-      <c r="E54" s="6" t="n">
+      <c r="E54" s="7" t="n">
         <v>18.99</v>
       </c>
-      <c r="F54" s="6" t="n">
+      <c r="F54" s="7" t="n">
         <v>19.99</v>
       </c>
     </row>
@@ -8059,10 +8059,10 @@
           <t>5lb</t>
         </is>
       </c>
-      <c r="E55" s="6" t="n">
+      <c r="E55" s="7" t="n">
         <v>74.98999999999999</v>
       </c>
-      <c r="F55" s="6" t="n">
+      <c r="F55" s="7" t="n">
         <v>82.48999999999999</v>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr"/>
-      <c r="E58" s="6" t="n">
+      <c r="E58" s="7" t="n">
         <v>10</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr"/>
-      <c r="E59" s="6" t="n">
+      <c r="E59" s="7" t="n">
         <v>10</v>
       </c>
       <c r="F59" s="5" t="inlineStr">
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr"/>
-      <c r="E60" s="6" t="n">
+      <c r="E60" s="7" t="n">
         <v>25</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
@@ -8197,10 +8197,10 @@
           <t>24ct</t>
         </is>
       </c>
-      <c r="E61" s="6" t="n">
+      <c r="E61" s="7" t="n">
         <v>29.99</v>
       </c>
-      <c r="F61" s="6" t="n">
+      <c r="F61" s="7" t="n">
         <v>32.99</v>
       </c>
     </row>
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr"/>
-      <c r="E62" s="6" t="n">
+      <c r="E62" s="7" t="n">
         <v>34.99</v>
       </c>
-      <c r="F62" s="6" t="n">
+      <c r="F62" s="7" t="n">
         <v>36.99</v>
       </c>
     </row>
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr"/>
-      <c r="E63" s="6" t="n">
+      <c r="E63" s="7" t="n">
         <v>34.99</v>
       </c>
-      <c r="F63" s="6" t="n">
+      <c r="F63" s="7" t="n">
         <v>38.49</v>
       </c>
     </row>
@@ -8269,10 +8269,10 @@
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr"/>
-      <c r="E64" s="6" t="n">
+      <c r="E64" s="7" t="n">
         <v>36.99</v>
       </c>
-      <c r="F64" s="6" t="n">
+      <c r="F64" s="7" t="n">
         <v>38.99</v>
       </c>
     </row>
@@ -8297,10 +8297,10 @@
           <t>48ct</t>
         </is>
       </c>
-      <c r="E65" s="6" t="n">
+      <c r="E65" s="7" t="n">
         <v>37.99</v>
       </c>
-      <c r="F65" s="6" t="n">
+      <c r="F65" s="7" t="n">
         <v>41.99</v>
       </c>
     </row>
@@ -8321,7 +8321,7 @@
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr"/>
-      <c r="E66" s="6" t="n">
+      <c r="E66" s="7" t="n">
         <v>42.99</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
@@ -8347,7 +8347,7 @@
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr"/>
-      <c r="E67" s="6" t="n">
+      <c r="E67" s="7" t="n">
         <v>42.99</v>
       </c>
       <c r="F67" s="5" t="inlineStr">
@@ -8373,7 +8373,7 @@
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr"/>
-      <c r="E68" s="6" t="n">
+      <c r="E68" s="7" t="n">
         <v>42.99</v>
       </c>
       <c r="F68" s="5" t="inlineStr">
@@ -8399,10 +8399,10 @@
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr"/>
-      <c r="E69" s="6" t="n">
+      <c r="E69" s="7" t="n">
         <v>42.99</v>
       </c>
-      <c r="F69" s="6" t="n">
+      <c r="F69" s="7" t="n">
         <v>54.99</v>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr"/>
-      <c r="E70" s="6" t="n">
+      <c r="E70" s="7" t="n">
         <v>42.99</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
@@ -8449,10 +8449,10 @@
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr"/>
-      <c r="E71" s="6" t="n">
+      <c r="E71" s="7" t="n">
         <v>43.99</v>
       </c>
-      <c r="F71" s="6" t="n">
+      <c r="F71" s="7" t="n">
         <v>56.99</v>
       </c>
     </row>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr"/>
-      <c r="E72" s="6" t="n">
+      <c r="E72" s="7" t="n">
         <v>43.99</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
@@ -8499,10 +8499,10 @@
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr"/>
-      <c r="E73" s="6" t="n">
+      <c r="E73" s="7" t="n">
         <v>43.99</v>
       </c>
-      <c r="F73" s="6" t="n">
+      <c r="F73" s="7" t="n">
         <v>45.99</v>
       </c>
     </row>
@@ -8523,10 +8523,10 @@
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr"/>
-      <c r="E74" s="6" t="n">
+      <c r="E74" s="7" t="n">
         <v>44.99</v>
       </c>
-      <c r="F74" s="6" t="n">
+      <c r="F74" s="7" t="n">
         <v>46.99</v>
       </c>
     </row>
@@ -8547,10 +8547,10 @@
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr"/>
-      <c r="E75" s="6" t="n">
+      <c r="E75" s="7" t="n">
         <v>47.99</v>
       </c>
-      <c r="F75" s="6" t="n">
+      <c r="F75" s="7" t="n">
         <v>56.49</v>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr"/>
-      <c r="E76" s="6" t="n">
+      <c r="E76" s="7" t="n">
         <v>47.99</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
@@ -8597,10 +8597,10 @@
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr"/>
-      <c r="E77" s="6" t="n">
+      <c r="E77" s="7" t="n">
         <v>47.99</v>
       </c>
-      <c r="F77" s="6" t="n">
+      <c r="F77" s="7" t="n">
         <v>52.99</v>
       </c>
     </row>
@@ -8621,10 +8621,10 @@
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr"/>
-      <c r="E78" s="6" t="n">
+      <c r="E78" s="7" t="n">
         <v>47.99</v>
       </c>
-      <c r="F78" s="6" t="n">
+      <c r="F78" s="7" t="n">
         <v>60.99</v>
       </c>
     </row>
@@ -8645,7 +8645,7 @@
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr"/>
-      <c r="E79" s="6" t="n">
+      <c r="E79" s="7" t="n">
         <v>48.99</v>
       </c>
       <c r="F79" s="5" t="inlineStr">
@@ -8671,7 +8671,7 @@
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr"/>
-      <c r="E80" s="6" t="n">
+      <c r="E80" s="7" t="n">
         <v>48.99</v>
       </c>
       <c r="F80" s="5" t="inlineStr">
@@ -8697,7 +8697,7 @@
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr"/>
-      <c r="E81" s="6" t="n">
+      <c r="E81" s="7" t="n">
         <v>48.99</v>
       </c>
       <c r="F81" s="5" t="inlineStr">
@@ -8723,7 +8723,7 @@
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr"/>
-      <c r="E82" s="6" t="n">
+      <c r="E82" s="7" t="n">
         <v>50</v>
       </c>
       <c r="F82" s="5" t="inlineStr">
@@ -8749,10 +8749,10 @@
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr"/>
-      <c r="E83" s="6" t="n">
+      <c r="E83" s="7" t="n">
         <v>53.99</v>
       </c>
-      <c r="F83" s="6" t="n">
+      <c r="F83" s="7" t="n">
         <v>62.49</v>
       </c>
     </row>
@@ -8773,7 +8773,7 @@
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr"/>
-      <c r="E84" s="6" t="n">
+      <c r="E84" s="7" t="n">
         <v>53.99</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
@@ -8799,10 +8799,10 @@
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr"/>
-      <c r="E85" s="6" t="n">
+      <c r="E85" s="7" t="n">
         <v>53.99</v>
       </c>
-      <c r="F85" s="6" t="n">
+      <c r="F85" s="7" t="n">
         <v>80.98999999999999</v>
       </c>
     </row>
@@ -8823,7 +8823,7 @@
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr"/>
-      <c r="E86" s="6" t="n">
+      <c r="E86" s="7" t="n">
         <v>53.99</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr"/>
-      <c r="E87" s="6" t="n">
+      <c r="E87" s="7" t="n">
         <v>53.99</v>
       </c>
       <c r="F87" s="5" t="inlineStr">
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr"/>
-      <c r="E88" s="6" t="n">
+      <c r="E88" s="7" t="n">
         <v>53.99</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
@@ -8901,7 +8901,7 @@
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr"/>
-      <c r="E89" s="6" t="n">
+      <c r="E89" s="7" t="n">
         <v>53.99</v>
       </c>
       <c r="F89" s="5" t="inlineStr">
@@ -8927,10 +8927,10 @@
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr"/>
-      <c r="E90" s="6" t="n">
+      <c r="E90" s="7" t="n">
         <v>53.99</v>
       </c>
-      <c r="F90" s="6" t="n">
+      <c r="F90" s="7" t="n">
         <v>69.98999999999999</v>
       </c>
     </row>
@@ -8951,10 +8951,10 @@
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr"/>
-      <c r="E91" s="6" t="n">
+      <c r="E91" s="7" t="n">
         <v>53.99</v>
       </c>
-      <c r="F91" s="6" t="n">
+      <c r="F91" s="7" t="n">
         <v>65.98999999999999</v>
       </c>
     </row>
@@ -8975,10 +8975,10 @@
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr"/>
-      <c r="E92" s="6" t="n">
+      <c r="E92" s="7" t="n">
         <v>53.99</v>
       </c>
-      <c r="F92" s="6" t="n">
+      <c r="F92" s="7" t="n">
         <v>67.98999999999999</v>
       </c>
     </row>
@@ -8999,10 +8999,10 @@
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr"/>
-      <c r="E93" s="6" t="n">
+      <c r="E93" s="7" t="n">
         <v>53.99</v>
       </c>
-      <c r="F93" s="6" t="n">
+      <c r="F93" s="7" t="n">
         <v>68.98999999999999</v>
       </c>
     </row>
@@ -9019,10 +9019,10 @@
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr"/>
-      <c r="E94" s="6" t="n">
+      <c r="E94" s="7" t="n">
         <v>56.99</v>
       </c>
-      <c r="F94" s="6" t="n">
+      <c r="F94" s="7" t="n">
         <v>73.48999999999999</v>
       </c>
     </row>
@@ -9043,7 +9043,7 @@
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr"/>
-      <c r="E95" s="6" t="n">
+      <c r="E95" s="7" t="n">
         <v>56.99</v>
       </c>
       <c r="F95" s="5" t="inlineStr">
@@ -9065,10 +9065,10 @@
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr"/>
-      <c r="E96" s="6" t="n">
+      <c r="E96" s="7" t="n">
         <v>58.99</v>
       </c>
-      <c r="F96" s="6" t="n">
+      <c r="F96" s="7" t="n">
         <v>80.48999999999999</v>
       </c>
     </row>
@@ -9089,10 +9089,10 @@
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr"/>
-      <c r="E97" s="6" t="n">
+      <c r="E97" s="7" t="n">
         <v>58.99</v>
       </c>
-      <c r="F97" s="6" t="n">
+      <c r="F97" s="7" t="n">
         <v>80.48999999999999</v>
       </c>
     </row>
@@ -9113,10 +9113,10 @@
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr"/>
-      <c r="E98" s="6" t="n">
+      <c r="E98" s="7" t="n">
         <v>58.99</v>
       </c>
-      <c r="F98" s="6" t="n">
+      <c r="F98" s="7" t="n">
         <v>79.48999999999999</v>
       </c>
     </row>
@@ -9137,10 +9137,10 @@
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr"/>
-      <c r="E99" s="6" t="n">
+      <c r="E99" s="7" t="n">
         <v>59</v>
       </c>
-      <c r="F99" s="6" t="n">
+      <c r="F99" s="7" t="n">
         <v>64.98999999999999</v>
       </c>
     </row>
@@ -9161,10 +9161,10 @@
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr"/>
-      <c r="E100" s="6" t="n">
+      <c r="E100" s="7" t="n">
         <v>59.99</v>
       </c>
-      <c r="F100" s="6" t="n">
+      <c r="F100" s="7" t="n">
         <v>62.99</v>
       </c>
     </row>
@@ -9185,10 +9185,10 @@
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr"/>
-      <c r="E101" s="6" t="n">
+      <c r="E101" s="7" t="n">
         <v>60.99</v>
       </c>
-      <c r="F101" s="6" t="n">
+      <c r="F101" s="7" t="n">
         <v>66.98999999999999</v>
       </c>
     </row>
@@ -9209,10 +9209,10 @@
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr"/>
-      <c r="E102" s="6" t="n">
+      <c r="E102" s="7" t="n">
         <v>63.99</v>
       </c>
-      <c r="F102" s="6" t="n">
+      <c r="F102" s="7" t="n">
         <v>86.48999999999999</v>
       </c>
     </row>
@@ -9233,10 +9233,10 @@
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr"/>
-      <c r="E103" s="6" t="n">
+      <c r="E103" s="7" t="n">
         <v>68.98999999999999</v>
       </c>
-      <c r="F103" s="6" t="n">
+      <c r="F103" s="7" t="n">
         <v>75.98999999999999</v>
       </c>
     </row>
@@ -9257,10 +9257,10 @@
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr"/>
-      <c r="E104" s="6" t="n">
+      <c r="E104" s="7" t="n">
         <v>74.98999999999999</v>
       </c>
-      <c r="F104" s="6" t="n">
+      <c r="F104" s="7" t="n">
         <v>101.99</v>
       </c>
     </row>
@@ -9281,7 +9281,7 @@
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr"/>
-      <c r="E105" s="6" t="n">
+      <c r="E105" s="7" t="n">
         <v>75</v>
       </c>
       <c r="F105" s="5" t="inlineStr">
@@ -9307,7 +9307,7 @@
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr"/>
-      <c r="E106" s="6" t="n">
+      <c r="E106" s="7" t="n">
         <v>100</v>
       </c>
       <c r="F106" s="5" t="inlineStr">
@@ -9333,10 +9333,10 @@
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr"/>
-      <c r="E107" s="6" t="n">
+      <c r="E107" s="7" t="n">
         <v>128.99</v>
       </c>
-      <c r="F107" s="6" t="n">
+      <c r="F107" s="7" t="n">
         <v>141.99</v>
       </c>
     </row>
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr"/>
-      <c r="E108" s="6" t="n">
+      <c r="E108" s="7" t="n">
         <v>139.99</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
@@ -9383,7 +9383,7 @@
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr"/>
-      <c r="E109" s="6" t="n">
+      <c r="E109" s="7" t="n">
         <v>139.99</v>
       </c>
       <c r="F109" s="5" t="inlineStr">
@@ -9409,7 +9409,7 @@
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr"/>
-      <c r="E110" s="6" t="n">
+      <c r="E110" s="7" t="n">
         <v>139.99</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
@@ -9435,7 +9435,7 @@
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr"/>
-      <c r="E111" s="6" t="n">
+      <c r="E111" s="7" t="n">
         <v>139.99</v>
       </c>
       <c r="F111" s="5" t="inlineStr">
